--- a/QC inspections suppliers/Pelvic_Blocks_Quality_062626.xlsx
+++ b/QC inspections suppliers/Pelvic_Blocks_Quality_062626.xlsx
@@ -6059,7 +6059,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L102"/>
+  <dimension ref="A1:L109"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16.78"/>
@@ -6572,134 +6572,152 @@
         </is>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="3" t="s">
+    <row r="18" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Visit 13</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-22</t>
+        </is>
+      </c>
+      <c r="C18" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Parks Family Meats</t>
+        </is>
+      </c>
+      <c r="D18" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rasmin Mujanovic</t>
+        </is>
+      </c>
+      <c r="E18" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Natalie</t>
+        </is>
+      </c>
+      <c r="F18" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(no batch data)</t>
+        </is>
+      </c>
+      <c r="G18" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="H18" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">666518</t>
+        </is>
+      </c>
+      <c r="I18" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Visit 14</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-25</t>
+        </is>
+      </c>
+      <c r="C19" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Parks Family Meats</t>
+        </is>
+      </c>
+      <c r="D19" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rasmin Mujanovic</t>
+        </is>
+      </c>
+      <c r="E19" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Natalie</t>
+        </is>
+      </c>
+      <c r="F19" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(no batch data)</t>
+        </is>
+      </c>
+      <c r="G19" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="H19" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">666518</t>
+        </is>
+      </c>
+      <c r="I19" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
-      <c r="J19" s="3"/>
-      <c r="K19" s="3"/>
-      <c r="L19" s="3"/>
-    </row>
-    <row r="20" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="11" t="s">
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="3"/>
+      <c r="I21" s="3"/>
+      <c r="J21" s="3"/>
+      <c r="K21" s="3"/>
+      <c r="L21" s="3"/>
+    </row>
+    <row r="22" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="B20" s="11" t="s">
+      <c r="B22" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="C20" s="11" t="s">
+      <c r="C22" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="D20" s="11" t="s">
+      <c r="D22" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="E20" s="11" t="s">
+      <c r="E22" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="F20" s="11" t="s">
+      <c r="F22" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="G20" s="11" t="s">
+      <c r="G22" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="H20" s="11" t="s">
+      <c r="H22" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="I20" s="11" t="s">
+      <c r="I22" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="J20" s="11" t="s">
+      <c r="J22" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="K20" s="11" t="s">
+      <c r="K22" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="L20" s="11" t="s">
+      <c r="L22" s="11" t="s">
         <v>99</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="F21" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="G21" s="6" t="n">
-        <v>48</v>
-      </c>
-      <c r="H21" s="6" t="n">
-        <v>47</v>
-      </c>
-      <c r="I21" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J21" s="15" t="n">
-        <f aca="false">IFERROR(H21/G21,0)</f>
-      </c>
-      <c r="K21" s="16" t="s">
-        <v>102</v>
-      </c>
-      <c r="L21" s="5" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="F22" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="G22" s="6" t="n">
-        <v>17</v>
-      </c>
-      <c r="H22" s="6" t="n">
-        <v>13</v>
-      </c>
-      <c r="I22" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="J22" s="15" t="n">
-        <f aca="false">IFERROR(H22/G22,0)</f>
-      </c>
-      <c r="K22" s="16" t="s">
-        <v>105</v>
-      </c>
-      <c r="L22" s="5" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6710,37 +6728,37 @@
         <v>53</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>3</v>
+        <v>48</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>3</v>
+        <v>47</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23" s="15" t="n">
         <f aca="false">IFERROR(H23/G23,0)</f>
       </c>
       <c r="K23" s="16" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="L23" s="5" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
         <v>104</v>
       </c>
@@ -6748,58 +6766,60 @@
         <v>53</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="G24" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="I24" s="6" t="n">
         <v>4</v>
-      </c>
-      <c r="H24" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="I24" s="6" t="n">
-        <v>0</v>
       </c>
       <c r="J24" s="15" t="n">
         <f aca="false">IFERROR(H24/G24,0)</f>
       </c>
-      <c r="K24" s="16"/>
+      <c r="K24" s="16" t="s">
+        <v>105</v>
+      </c>
       <c r="L24" s="5" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>53</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I25" s="6" t="n">
         <v>0</v>
@@ -6808,7 +6828,7 @@
         <f aca="false">IFERROR(H25/G25,0)</f>
       </c>
       <c r="K25" s="16" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L25" s="5" t="s">
         <v>103</v>
@@ -6816,43 +6836,41 @@
     </row>
     <row r="26" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>53</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>57</v>
+        <v>4</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>56</v>
+        <v>4</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J26" s="15" t="n">
         <f aca="false">IFERROR(H26/G26,0)</f>
       </c>
-      <c r="K26" s="16" t="s">
-        <v>111</v>
-      </c>
+      <c r="K26" s="16"/>
       <c r="L26" s="5" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
         <v>13</v>
       </c>
@@ -6860,31 +6878,31 @@
         <v>53</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J27" s="15" t="n">
         <f aca="false">IFERROR(H27/G27,0)</f>
       </c>
       <c r="K27" s="16" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="L27" s="5" t="s">
         <v>103</v>
@@ -6898,31 +6916,31 @@
         <v>53</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J28" s="15" t="n">
         <f aca="false">IFERROR(H28/G28,0)</f>
       </c>
       <c r="K28" s="16" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="L28" s="5" t="s">
         <v>103</v>
@@ -6930,37 +6948,37 @@
     </row>
     <row r="29" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>53</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J29" s="15" t="n">
         <f aca="false">IFERROR(H29/G29,0)</f>
       </c>
       <c r="K29" s="16" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="L29" s="5" t="s">
         <v>103</v>
@@ -6968,37 +6986,37 @@
     </row>
     <row r="30" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>53</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J30" s="15" t="n">
         <f aca="false">IFERROR(H30/G30,0)</f>
       </c>
       <c r="K30" s="16" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="L30" s="5" t="s">
         <v>103</v>
@@ -7012,31 +7030,31 @@
         <v>53</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J31" s="15" t="n">
         <f aca="false">IFERROR(H31/G31,0)</f>
       </c>
       <c r="K31" s="16" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="L31" s="5" t="s">
         <v>103</v>
@@ -7050,31 +7068,31 @@
         <v>53</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J32" s="15" t="n">
         <f aca="false">IFERROR(H32/G32,0)</f>
       </c>
       <c r="K32" s="16" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="L32" s="5" t="s">
         <v>103</v>
@@ -7082,37 +7100,37 @@
     </row>
     <row r="33" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="5" t="s">
-        <v>118</v>
+        <v>14</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>53</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>62</v>
+        <v>16</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>58</v>
+        <v>13</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J33" s="15" t="n">
         <f aca="false">IFERROR(H33/G33,0)</f>
       </c>
       <c r="K33" s="16" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="L33" s="5" t="s">
         <v>103</v>
@@ -7120,43 +7138,43 @@
     </row>
     <row r="34" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="5" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>53</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J34" s="15" t="n">
         <f aca="false">IFERROR(H34/G34,0)</f>
       </c>
       <c r="K34" s="16" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="L34" s="5" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="5" t="s">
         <v>118</v>
       </c>
@@ -7164,31 +7182,31 @@
         <v>53</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="I35" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J35" s="15" t="n">
         <f aca="false">IFERROR(H35/G35,0)</f>
       </c>
       <c r="K35" s="16" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="L35" s="5" t="s">
         <v>103</v>
@@ -7202,31 +7220,31 @@
         <v>53</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H36" s="6" t="n">
         <v>29</v>
       </c>
       <c r="I36" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J36" s="15" t="n">
         <f aca="false">IFERROR(H36/G36,0)</f>
       </c>
       <c r="K36" s="16" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="L36" s="5" t="s">
         <v>103</v>
@@ -7234,89 +7252,89 @@
     </row>
     <row r="37" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="5" t="s">
-        <v>73</v>
+        <v>118</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>53</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J37" s="15" t="n">
         <f aca="false">IFERROR(H37/G37,0)</f>
       </c>
       <c r="K37" s="16" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="L37" s="5" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="5" t="s">
-        <v>16</v>
+        <v>120</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>81</v>
+        <v>59</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J38" s="15" t="n">
         <f aca="false">IFERROR(H38/G38,0)</f>
       </c>
       <c r="K38" s="16" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="L38" s="5" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="5" t="s">
-        <v>128</v>
+        <v>73</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>53</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="D39" s="5" t="s">
         <v>58</v>
@@ -7328,58 +7346,60 @@
         <v>101</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J39" s="15" t="n">
         <f aca="false">IFERROR(H39/G39,0)</f>
       </c>
-      <c r="K39" s="16"/>
+      <c r="K39" s="16" t="s">
+        <v>124</v>
+      </c>
       <c r="L39" s="5" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="5" t="s">
-        <v>129</v>
+        <v>16</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>58</v>
+        <v>81</v>
       </c>
       <c r="E40" s="5" t="s">
         <v>100</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>101</v>
+        <v>125</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="H40" s="6" t="n">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="I40" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J40" s="15" t="n">
         <f aca="false">IFERROR(H40/G40,0)</f>
       </c>
       <c r="K40" s="16" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="L40" s="5" t="s">
-        <v>103</v>
+        <v>127</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7390,22 +7410,22 @@
         <v>53</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H41" s="6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I41" s="6" t="n">
         <v>0</v>
@@ -7426,52 +7446,54 @@
         <v>53</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="G42" s="6" t="n">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="H42" s="6" t="n">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="I42" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J42" s="15" t="n">
         <f aca="false">IFERROR(H42/G42,0)</f>
       </c>
-      <c r="K42" s="16"/>
+      <c r="K42" s="16" t="s">
+        <v>130</v>
+      </c>
       <c r="L42" s="5" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="5" t="s">
-        <v>87</v>
+        <v>128</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>81</v>
+        <v>59</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="G43" s="6" t="n">
         <v>7</v>
@@ -7487,121 +7509,85 @@
       </c>
       <c r="K43" s="16"/>
       <c r="L43" s="5" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-08</t>
-        </is>
-      </c>
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Martins</t>
-        </is>
-      </c>
-      <c r="C44" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5502428786</t>
-        </is>
-      </c>
-      <c r="D44" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">666541</t>
-        </is>
-      </c>
-      <c r="E44" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Intact</t>
-        </is>
-      </c>
-      <c r="F44" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tiss, porcine, fem, Pelvic block, intact</t>
-        </is>
+        <v>103</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="E44" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="F44" s="5" t="s">
+        <v>107</v>
       </c>
       <c r="G44" s="6" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="H44" s="6" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="I44" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J44" s="15" t="n">
         <f aca="false">IFERROR(H44/G44,0)</f>
       </c>
-      <c r="K44" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 cut urethra</t>
-        </is>
-      </c>
-      <c r="L44" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Toni Cruz / Jesus</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-08</t>
-        </is>
-      </c>
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Martins</t>
-        </is>
-      </c>
-      <c r="C45" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5502428782</t>
-        </is>
-      </c>
-      <c r="D45" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">666506</t>
-        </is>
-      </c>
-      <c r="E45" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Non-intact</t>
-        </is>
-      </c>
-      <c r="F45" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tiss, porcine, fem, Pelvic block, non-intact</t>
-        </is>
+      <c r="K44" s="16"/>
+      <c r="L44" s="5" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="E45" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="F45" s="5" t="s">
+        <v>125</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J45" s="15" t="n">
         <f aca="false">IFERROR(H45/G45,0)</f>
       </c>
-      <c r="K45" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 short block</t>
-        </is>
-      </c>
-      <c r="L45" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Toni Cruz / Jesus</t>
-        </is>
+      <c r="K45" s="16"/>
+      <c r="L45" s="5" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="46" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-15</t>
+          <t xml:space="preserve">2026-06-08</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
@@ -7611,7 +7597,7 @@
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">5502462845</t>
+          <t xml:space="preserve">5502428786</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
@@ -7630,10 +7616,10 @@
         </is>
       </c>
       <c r="G46" s="6" t="n">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="H46" s="6" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="I46" s="6" t="n">
         <v>1</v>
@@ -7643,7 +7629,7 @@
       </c>
       <c r="K46" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 damaged bowel (source had two intact tally lines: 13/12/1 + 18/18/0, combined here)</t>
+          <t xml:space="preserve">1 cut urethra</t>
         </is>
       </c>
       <c r="L46" s="5" t="inlineStr">
@@ -7655,61 +7641,61 @@
     <row r="47" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-16</t>
+          <t xml:space="preserve">2026-06-08</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parks Family Meats</t>
+          <t xml:space="preserve">Martins</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">(no batch data)</t>
+          <t xml:space="preserve">5502428782</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">666518</t>
+          <t xml:space="preserve">666506</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Intact</t>
+          <t xml:space="preserve">Non-intact</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tiss, porcine, fem, Pelvic block, intact, SM</t>
+          <t xml:space="preserve">Tiss, porcine, fem, Pelvic block, non-intact</t>
         </is>
       </c>
       <c r="G47" s="6" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H47" s="6" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I47" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J47" s="15" t="n">
         <f aca="false">IFERROR(H47/G47,0)</f>
       </c>
       <c r="K47" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 bladder hole; 1 ureter damage (many blocks failed upstream from miscuts during removal — see notes)</t>
+          <t xml:space="preserve">1 short block</t>
         </is>
       </c>
       <c r="L47" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rasmin Mujanovic / Natalie</t>
+          <t xml:space="preserve">Toni Cruz / Jesus</t>
         </is>
       </c>
     </row>
     <row r="48" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-24</t>
+          <t xml:space="preserve">2026-06-15</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
@@ -7738,20 +7724,20 @@
         </is>
       </c>
       <c r="G48" s="6" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H48" s="6" t="n">
         <v>30</v>
       </c>
       <c r="I48" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J48" s="15" t="n">
         <f aca="false">IFERROR(H48/G48,0)</f>
       </c>
       <c r="K48" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 damaged bladder; 3 damaged membrane</t>
+          <t xml:space="preserve">1 damaged bowel (source had two intact tally lines: 13/12/1 + 18/18/0, combined here)</t>
         </is>
       </c>
       <c r="L48" s="5" t="inlineStr">
@@ -7760,170 +7746,270 @@
         </is>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="3" t="s">
+    <row r="49" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-16</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Parks Family Meats</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(no batch data)</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">666518</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Intact</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tiss, porcine, fem, Pelvic block, intact, SM</t>
+        </is>
+      </c>
+      <c r="G49" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="H49" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="I49" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J49" s="15" t="n">
+        <f aca="false">IFERROR(H49/G49,0)</f>
+      </c>
+      <c r="K49" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 bladder hole; 1 ureter damage (many blocks failed upstream from miscuts during removal — see notes)</t>
+        </is>
+      </c>
+      <c r="L49" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rasmin Mujanovic / Natalie</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-24</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Martins</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5502462845</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">666541</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Intact</t>
+        </is>
+      </c>
+      <c r="F50" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tiss, porcine, fem, Pelvic block, intact</t>
+        </is>
+      </c>
+      <c r="G50" s="6" t="n">
+        <v>34</v>
+      </c>
+      <c r="H50" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="I50" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="J50" s="15" t="n">
+        <f aca="false">IFERROR(H50/G50,0)</f>
+      </c>
+      <c r="K50" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 damaged bladder; 3 damaged membrane</t>
+        </is>
+      </c>
+      <c r="L50" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Toni Cruz / Jesus</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-22</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Parks Family Meats</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(no batch data)</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">666518</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Intact</t>
+        </is>
+      </c>
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tiss, porcine, fem, Pelvic block, intact, SM</t>
+        </is>
+      </c>
+      <c r="G51" s="6" t="n">
+        <v>36</v>
+      </c>
+      <c r="H51" s="6" t="n">
+        <v>31</v>
+      </c>
+      <c r="I51" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="J51" s="15" t="n">
+        <f aca="false">IFERROR(H51/G51,0)</f>
+      </c>
+      <c r="K51" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 bladder hole; 2 critical-area lacerations; 2 short blocks</t>
+        </is>
+      </c>
+      <c r="L51" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rasmin Mujanovic / Natalie</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-25</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Parks Family Meats</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(no batch data)</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">666518</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Intact</t>
+        </is>
+      </c>
+      <c r="F52" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tiss, porcine, fem, Pelvic block, intact, SM</t>
+        </is>
+      </c>
+      <c r="G52" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="H52" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="I52" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J52" s="15" t="n">
+        <f aca="false">IFERROR(H52/G52,0)</f>
+      </c>
+      <c r="K52" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 bladder hole; 1 ureter laceration; 1 short block</t>
+        </is>
+      </c>
+      <c r="L52" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rasmin Mujanovic / Natalie</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="B50" s="3"/>
-      <c r="C50" s="3"/>
-      <c r="D50" s="3"/>
-      <c r="E50" s="3"/>
-      <c r="F50" s="3"/>
-      <c r="G50" s="3"/>
-      <c r="H50" s="3"/>
-      <c r="I50" s="3"/>
-      <c r="J50" s="3"/>
-      <c r="K50" s="3"/>
-      <c r="L50" s="3"/>
-    </row>
-    <row r="51" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="11" t="s">
+      <c r="B54" s="3"/>
+      <c r="C54" s="3"/>
+      <c r="D54" s="3"/>
+      <c r="E54" s="3"/>
+      <c r="F54" s="3"/>
+      <c r="G54" s="3"/>
+      <c r="H54" s="3"/>
+      <c r="I54" s="3"/>
+      <c r="J54" s="3"/>
+      <c r="K54" s="3"/>
+      <c r="L54" s="3"/>
+    </row>
+    <row r="55" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="B51" s="11" t="s">
+      <c r="B55" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="C51" s="11" t="s">
+      <c r="C55" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="D51" s="11" t="s">
+      <c r="D55" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="E51" s="11" t="s">
+      <c r="E55" s="11" t="s">
         <v>132</v>
       </c>
-      <c r="F51" s="11" t="s">
+      <c r="F55" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="G51" s="11" t="s">
+      <c r="G55" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="H51" s="11" t="s">
+      <c r="H55" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="I51" s="11" t="s">
+      <c r="I55" s="11" t="s">
         <v>97</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="B52" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="C52" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="D52" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="E52" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="F52" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="G52" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="H52" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I52" s="15" t="n">
-        <f aca="false">IFERROR(G52/F52,0)</f>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="B53" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="C53" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="D53" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="E53" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="F53" s="6" t="n">
-        <v>65</v>
-      </c>
-      <c r="G53" s="6" t="n">
-        <v>60</v>
-      </c>
-      <c r="H53" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="I53" s="15" t="n">
-        <f aca="false">IFERROR(G53/F53,0)</f>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="B54" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="C54" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="D54" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="E54" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="F54" s="6" t="n">
-        <v>52</v>
-      </c>
-      <c r="G54" s="6" t="n">
-        <v>48</v>
-      </c>
-      <c r="H54" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="I54" s="15" t="n">
-        <f aca="false">IFERROR(G54/F54,0)</f>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="B55" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="C55" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="D55" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="E55" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="F55" s="6" t="n">
-        <v>57</v>
-      </c>
-      <c r="G55" s="6" t="n">
-        <v>56</v>
-      </c>
-      <c r="H55" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I55" s="15" t="n">
-        <f aca="false">IFERROR(G55/F55,0)</f>
       </c>
     </row>
     <row r="56" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="12" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="B56" s="12" t="s">
         <v>59</v>
@@ -7935,16 +8021,16 @@
         <v>53</v>
       </c>
       <c r="E56" s="12" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="F56" s="6" t="n">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="G56" s="6" t="n">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="H56" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I56" s="15" t="n">
         <f aca="false">IFERROR(G56/F56,0)</f>
@@ -7952,7 +8038,7 @@
     </row>
     <row r="57" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="12" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="B57" s="12" t="s">
         <v>58</v>
@@ -7964,16 +8050,16 @@
         <v>53</v>
       </c>
       <c r="E57" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="F57" s="6" t="n">
         <v>65</v>
       </c>
-      <c r="F57" s="6" t="n">
-        <v>62</v>
-      </c>
       <c r="G57" s="6" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H57" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I57" s="15" t="n">
         <f aca="false">IFERROR(G57/F57,0)</f>
@@ -7981,7 +8067,7 @@
     </row>
     <row r="58" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="12" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="B58" s="12" t="s">
         <v>59</v>
@@ -7993,16 +8079,16 @@
         <v>53</v>
       </c>
       <c r="E58" s="12" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="F58" s="6" t="n">
-        <v>73</v>
+        <v>52</v>
       </c>
       <c r="G58" s="6" t="n">
-        <v>71</v>
+        <v>48</v>
       </c>
       <c r="H58" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I58" s="15" t="n">
         <f aca="false">IFERROR(G58/F58,0)</f>
@@ -8010,7 +8096,7 @@
     </row>
     <row r="59" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="12" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="B59" s="12" t="s">
         <v>58</v>
@@ -8022,16 +8108,16 @@
         <v>53</v>
       </c>
       <c r="E59" s="12" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>93</v>
+        <v>57</v>
       </c>
       <c r="G59" s="6" t="n">
-        <v>87</v>
+        <v>56</v>
       </c>
       <c r="H59" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I59" s="15" t="n">
         <f aca="false">IFERROR(G59/F59,0)</f>
@@ -8039,28 +8125,28 @@
     </row>
     <row r="60" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="12" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B60" s="12" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C60" s="12" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="D60" s="12" t="s">
         <v>53</v>
       </c>
       <c r="E60" s="12" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="F60" s="6" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="G60" s="6" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="H60" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I60" s="15" t="n">
         <f aca="false">IFERROR(G60/F60,0)</f>
@@ -8068,28 +8154,28 @@
     </row>
     <row r="61" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="12" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="B61" s="12" t="s">
-        <v>81</v>
+        <v>58</v>
       </c>
       <c r="C61" s="12" t="s">
         <v>100</v>
       </c>
       <c r="D61" s="12" t="s">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="E61" s="12" t="s">
-        <v>16</v>
+        <v>65</v>
       </c>
       <c r="F61" s="6" t="n">
-        <v>16</v>
+        <v>62</v>
       </c>
       <c r="G61" s="6" t="n">
-        <v>11</v>
+        <v>58</v>
       </c>
       <c r="H61" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I61" s="15" t="n">
         <f aca="false">IFERROR(G61/F61,0)</f>
@@ -8097,25 +8183,25 @@
     </row>
     <row r="62" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="12" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="B62" s="12" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C62" s="12" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="D62" s="12" t="s">
         <v>53</v>
       </c>
       <c r="E62" s="12" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="F62" s="6" t="n">
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="G62" s="6" t="n">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="H62" s="6" t="n">
         <v>2</v>
@@ -8126,28 +8212,28 @@
     </row>
     <row r="63" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="12" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="B63" s="12" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C63" s="12" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="D63" s="12" t="s">
         <v>53</v>
       </c>
       <c r="E63" s="12" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="F63" s="6" t="n">
-        <v>36</v>
+        <v>93</v>
       </c>
       <c r="G63" s="6" t="n">
-        <v>36</v>
+        <v>87</v>
       </c>
       <c r="H63" s="6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I63" s="15" t="n">
         <f aca="false">IFERROR(G63/F63,0)</f>
@@ -8155,198 +8241,158 @@
     </row>
     <row r="64" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="12" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="B64" s="12" t="s">
-        <v>81</v>
+        <v>58</v>
       </c>
       <c r="C64" s="12" t="s">
         <v>100</v>
       </c>
       <c r="D64" s="12" t="s">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="E64" s="12" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="F64" s="6" t="n">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="G64" s="6" t="n">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="H64" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I64" s="15" t="n">
         <f aca="false">IFERROR(G64/F64,0)</f>
       </c>
     </row>
-    <row r="65" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="12" t="inlineStr">
+    <row r="65" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="B65" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="C65" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="D65" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="E65" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="F65" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="G65" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="H65" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="I65" s="15" t="n">
+        <f aca="false">IFERROR(G65/F65,0)</f>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="B66" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="C66" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="D66" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="E66" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="F66" s="6" t="n">
+        <v>54</v>
+      </c>
+      <c r="G66" s="6" t="n">
+        <v>52</v>
+      </c>
+      <c r="H66" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I66" s="15" t="n">
+        <f aca="false">IFERROR(G66/F66,0)</f>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A67" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="B67" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="C67" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="D67" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="E67" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="F67" s="6" t="n">
+        <v>36</v>
+      </c>
+      <c r="G67" s="6" t="n">
+        <v>36</v>
+      </c>
+      <c r="H67" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" s="15" t="n">
+        <f aca="false">IFERROR(G67/F67,0)</f>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A68" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="B68" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="C68" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="D68" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="E68" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="F68" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="G68" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="H68" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I68" s="15" t="n">
+        <f aca="false">IFERROR(G68/F68,0)</f>
+      </c>
+    </row>
+    <row r="69" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">5502428786</t>
         </is>
       </c>
-      <c r="B65" s="12" t="inlineStr">
+      <c r="B69" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">666541</t>
-        </is>
-      </c>
-      <c r="C65" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Intact</t>
-        </is>
-      </c>
-      <c r="D65" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Martins</t>
-        </is>
-      </c>
-      <c r="E65" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-08</t>
-        </is>
-      </c>
-      <c r="F65" s="6" t="n">
-        <v>17</v>
-      </c>
-      <c r="G65" s="6" t="n">
-        <v>16</v>
-      </c>
-      <c r="H65" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I65" s="15" t="n">
-        <f aca="false">IFERROR(G65/F65,0)</f>
-      </c>
-    </row>
-    <row r="66" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5502428782</t>
-        </is>
-      </c>
-      <c r="B66" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">666506</t>
-        </is>
-      </c>
-      <c r="C66" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Non-intact</t>
-        </is>
-      </c>
-      <c r="D66" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Martins</t>
-        </is>
-      </c>
-      <c r="E66" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-08</t>
-        </is>
-      </c>
-      <c r="F66" s="6" t="n">
-        <v>13</v>
-      </c>
-      <c r="G66" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="H66" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I66" s="15" t="n">
-        <f aca="false">IFERROR(G66/F66,0)</f>
-      </c>
-    </row>
-    <row r="67" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5502462845</t>
-        </is>
-      </c>
-      <c r="B67" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">666541</t>
-        </is>
-      </c>
-      <c r="C67" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Intact</t>
-        </is>
-      </c>
-      <c r="D67" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Martins</t>
-        </is>
-      </c>
-      <c r="E67" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-15</t>
-        </is>
-      </c>
-      <c r="F67" s="6" t="n">
-        <v>31</v>
-      </c>
-      <c r="G67" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="H67" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I67" s="15" t="n">
-        <f aca="false">IFERROR(G67/F67,0)</f>
-      </c>
-    </row>
-    <row r="68" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5502462845</t>
-        </is>
-      </c>
-      <c r="B68" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">666541</t>
-        </is>
-      </c>
-      <c r="C68" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Intact</t>
-        </is>
-      </c>
-      <c r="D68" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Martins</t>
-        </is>
-      </c>
-      <c r="E68" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-24</t>
-        </is>
-      </c>
-      <c r="F68" s="6" t="n">
-        <v>34</v>
-      </c>
-      <c r="G68" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="H68" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="I68" s="15" t="n">
-        <f aca="false">IFERROR(G68/F68,0)</f>
-      </c>
-    </row>
-    <row r="69" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(no batch data)</t>
-        </is>
-      </c>
-      <c r="B69" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">666518</t>
         </is>
       </c>
       <c r="C69" s="12" t="inlineStr">
@@ -8356,300 +8402,342 @@
       </c>
       <c r="D69" s="12" t="inlineStr">
         <is>
+          <t xml:space="preserve">Martins</t>
+        </is>
+      </c>
+      <c r="E69" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-08</t>
+        </is>
+      </c>
+      <c r="F69" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="G69" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="H69" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I69" s="15" t="n">
+        <f aca="false">IFERROR(G69/F69,0)</f>
+      </c>
+    </row>
+    <row r="70" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5502428782</t>
+        </is>
+      </c>
+      <c r="B70" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">666506</t>
+        </is>
+      </c>
+      <c r="C70" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non-intact</t>
+        </is>
+      </c>
+      <c r="D70" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Martins</t>
+        </is>
+      </c>
+      <c r="E70" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-08</t>
+        </is>
+      </c>
+      <c r="F70" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="G70" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="H70" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I70" s="15" t="n">
+        <f aca="false">IFERROR(G70/F70,0)</f>
+      </c>
+    </row>
+    <row r="71" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5502462845</t>
+        </is>
+      </c>
+      <c r="B71" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">666541</t>
+        </is>
+      </c>
+      <c r="C71" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Intact</t>
+        </is>
+      </c>
+      <c r="D71" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Martins</t>
+        </is>
+      </c>
+      <c r="E71" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-15</t>
+        </is>
+      </c>
+      <c r="F71" s="6" t="n">
+        <v>31</v>
+      </c>
+      <c r="G71" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="H71" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I71" s="15" t="n">
+        <f aca="false">IFERROR(G71/F71,0)</f>
+      </c>
+    </row>
+    <row r="72" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5502462845</t>
+        </is>
+      </c>
+      <c r="B72" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">666541</t>
+        </is>
+      </c>
+      <c r="C72" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Intact</t>
+        </is>
+      </c>
+      <c r="D72" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Martins</t>
+        </is>
+      </c>
+      <c r="E72" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-24</t>
+        </is>
+      </c>
+      <c r="F72" s="6" t="n">
+        <v>34</v>
+      </c>
+      <c r="G72" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="H72" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="I72" s="15" t="n">
+        <f aca="false">IFERROR(G72/F72,0)</f>
+      </c>
+    </row>
+    <row r="73" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(no batch data)</t>
+        </is>
+      </c>
+      <c r="B73" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">666518</t>
+        </is>
+      </c>
+      <c r="C73" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Intact</t>
+        </is>
+      </c>
+      <c r="D73" s="12" t="inlineStr">
+        <is>
           <t xml:space="preserve">Parks Family Meats</t>
         </is>
       </c>
-      <c r="E69" s="12" t="inlineStr">
+      <c r="E73" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-06-16</t>
         </is>
       </c>
-      <c r="F69" s="6" t="n">
+      <c r="F73" s="6" t="n">
         <v>16</v>
       </c>
-      <c r="G69" s="6" t="n">
+      <c r="G73" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="H69" s="6" t="n">
+      <c r="H73" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="I69" s="15" t="n">
-        <f aca="false">IFERROR(G69/F69,0)</f>
-      </c>
-    </row>
-    <row r="70" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A70" s="17" t="s">
+      <c r="I73" s="15" t="n">
+        <f aca="false">IFERROR(G73/F73,0)</f>
+      </c>
+    </row>
+    <row r="74" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(no batch data)</t>
+        </is>
+      </c>
+      <c r="B74" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">666518</t>
+        </is>
+      </c>
+      <c r="C74" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Intact</t>
+        </is>
+      </c>
+      <c r="D74" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Parks Family Meats</t>
+        </is>
+      </c>
+      <c r="E74" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-22</t>
+        </is>
+      </c>
+      <c r="F74" s="6" t="n">
+        <v>36</v>
+      </c>
+      <c r="G74" s="6" t="n">
+        <v>31</v>
+      </c>
+      <c r="H74" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="I74" s="15" t="n">
+        <f aca="false">IFERROR(G74/F74,0)</f>
+      </c>
+    </row>
+    <row r="75" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(no batch data)</t>
+        </is>
+      </c>
+      <c r="B75" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">666518</t>
+        </is>
+      </c>
+      <c r="C75" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Intact</t>
+        </is>
+      </c>
+      <c r="D75" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Parks Family Meats</t>
+        </is>
+      </c>
+      <c r="E75" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-25</t>
+        </is>
+      </c>
+      <c r="F75" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="G75" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="H75" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I75" s="15" t="n">
+        <f aca="false">IFERROR(G75/F75,0)</f>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A76" s="17" t="s">
         <v>133</v>
       </c>
-      <c r="B70" s="17"/>
-      <c r="C70" s="17"/>
-      <c r="D70" s="17"/>
-      <c r="E70" s="17"/>
-      <c r="F70" s="8" t="n">
-        <f aca="false">SUM(F52:F69)</f>
-      </c>
-      <c r="G70" s="8" t="n">
-        <f aca="false">SUM(G52:G69)</f>
-      </c>
-      <c r="H70" s="8" t="n">
-        <f aca="false">SUM(H52:H69)</f>
-      </c>
-      <c r="I70" s="9" t="n">
-        <f aca="false">IFERROR(G70/F70,0)</f>
-      </c>
-    </row>
-    <row r="72" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A72" s="10" t="s">
+      <c r="B76" s="17"/>
+      <c r="C76" s="17"/>
+      <c r="D76" s="17"/>
+      <c r="E76" s="17"/>
+      <c r="F76" s="8" t="n">
+        <f aca="false">SUM(F56:F75)</f>
+      </c>
+      <c r="G76" s="8" t="n">
+        <f aca="false">SUM(G56:G75)</f>
+      </c>
+      <c r="H76" s="8" t="n">
+        <f aca="false">SUM(H56:H75)</f>
+      </c>
+      <c r="I76" s="9" t="n">
+        <f aca="false">IFERROR(G76/F76,0)</f>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A78" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="B72" s="10"/>
-      <c r="C72" s="10"/>
-      <c r="D72" s="10"/>
-      <c r="E72" s="10"/>
-      <c r="F72" s="10"/>
-      <c r="G72" s="10"/>
-      <c r="H72" s="10"/>
-      <c r="I72" s="10"/>
-      <c r="J72" s="10"/>
-      <c r="K72" s="10"/>
-      <c r="L72" s="10"/>
-    </row>
-    <row r="73" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A73" s="11" t="s">
+      <c r="B78" s="10"/>
+      <c r="C78" s="10"/>
+      <c r="D78" s="10"/>
+      <c r="E78" s="10"/>
+      <c r="F78" s="10"/>
+      <c r="G78" s="10"/>
+      <c r="H78" s="10"/>
+      <c r="I78" s="10"/>
+      <c r="J78" s="10"/>
+      <c r="K78" s="10"/>
+      <c r="L78" s="10"/>
+    </row>
+    <row r="79" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A79" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="B73" s="11" t="s">
+      <c r="B79" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="C73" s="11" t="s">
+      <c r="C79" s="11" t="s">
         <v>135</v>
       </c>
-      <c r="D73" s="11" t="s">
+      <c r="D79" s="11" t="s">
         <v>136</v>
       </c>
-      <c r="E73" s="11" t="s">
+      <c r="E79" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="F73" s="11" t="s">
+      <c r="F79" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="G73" s="11" t="s">
+      <c r="G79" s="11" t="s">
         <v>139</v>
       </c>
-      <c r="H73" s="11" t="s">
+      <c r="H79" s="11" t="s">
         <v>140</v>
       </c>
-      <c r="I73" s="11" t="s">
+      <c r="I79" s="11" t="s">
         <v>141</v>
       </c>
-      <c r="J73" s="11" t="s">
+      <c r="J79" s="11" t="s">
         <v>142</v>
-      </c>
-    </row>
-    <row r="74" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A74" s="18" t="s">
-        <v>56</v>
-      </c>
-      <c r="B74" s="18" t="s">
-        <v>58</v>
-      </c>
-      <c r="C74" s="6" t="n">
-        <v>65</v>
-      </c>
-      <c r="D74" s="6" t="n">
-        <v>60</v>
-      </c>
-      <c r="E74" s="15" t="n">
-        <f aca="false">IFERROR(D74/C74,0)</f>
-      </c>
-      <c r="F74" s="6" t="n">
-        <f aca="false">SUMIFS('Receipt Summary'!F:F,'Receipt Summary'!E:E,A74)</f>
-      </c>
-      <c r="G74" s="6" t="n">
-        <f aca="false">SUMIFS('Receipt Summary'!G:G,'Receipt Summary'!E:E,A74)</f>
-      </c>
-      <c r="H74" s="15" t="n">
-        <f aca="false">IFERROR(G74/F74,0)</f>
-      </c>
-      <c r="I74" s="6" t="n">
-        <f aca="false">D74-F74</f>
-      </c>
-      <c r="J74" s="16" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="75" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A75" s="18" t="s">
-        <v>57</v>
-      </c>
-      <c r="B75" s="18" t="s">
-        <v>59</v>
-      </c>
-      <c r="C75" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="D75" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="E75" s="15" t="n">
-        <f aca="false">IFERROR(D75/C75,0)</f>
-      </c>
-      <c r="F75" s="6" t="n">
-        <f aca="false">SUMIFS('Receipt Summary'!F:F,'Receipt Summary'!E:E,A75)</f>
-      </c>
-      <c r="G75" s="6" t="n">
-        <f aca="false">SUMIFS('Receipt Summary'!G:G,'Receipt Summary'!E:E,A75)</f>
-      </c>
-      <c r="H75" s="15" t="n">
-        <f aca="false">IFERROR(G75/F75,0)</f>
-      </c>
-      <c r="I75" s="6" t="n">
-        <f aca="false">D75-F75</f>
-      </c>
-      <c r="J75" s="16" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="76" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A76" s="18" t="s">
-        <v>62</v>
-      </c>
-      <c r="B76" s="18" t="s">
-        <v>58</v>
-      </c>
-      <c r="C76" s="6" t="n">
-        <v>57</v>
-      </c>
-      <c r="D76" s="6" t="n">
-        <v>56</v>
-      </c>
-      <c r="E76" s="15" t="n">
-        <f aca="false">IFERROR(D76/C76,0)</f>
-      </c>
-      <c r="F76" s="6" t="n">
-        <f aca="false">SUMIFS('Receipt Summary'!F:F,'Receipt Summary'!E:E,A76)</f>
-      </c>
-      <c r="G76" s="6" t="n">
-        <f aca="false">SUMIFS('Receipt Summary'!G:G,'Receipt Summary'!E:E,A76)</f>
-      </c>
-      <c r="H76" s="15" t="n">
-        <f aca="false">IFERROR(G76/F76,0)</f>
-      </c>
-      <c r="I76" s="6" t="n">
-        <f aca="false">D76-F76</f>
-      </c>
-      <c r="J76" s="16" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="77" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A77" s="18" t="s">
-        <v>63</v>
-      </c>
-      <c r="B77" s="18" t="s">
-        <v>59</v>
-      </c>
-      <c r="C77" s="6" t="n">
-        <v>52</v>
-      </c>
-      <c r="D77" s="6" t="n">
-        <v>48</v>
-      </c>
-      <c r="E77" s="15" t="n">
-        <f aca="false">IFERROR(D77/C77,0)</f>
-      </c>
-      <c r="F77" s="6" t="n">
-        <f aca="false">SUMIFS('Receipt Summary'!F:F,'Receipt Summary'!E:E,A77)</f>
-      </c>
-      <c r="G77" s="6" t="n">
-        <f aca="false">SUMIFS('Receipt Summary'!G:G,'Receipt Summary'!E:E,A77)</f>
-      </c>
-      <c r="H77" s="15" t="n">
-        <f aca="false">IFERROR(G77/F77,0)</f>
-      </c>
-      <c r="I77" s="6" t="n">
-        <f aca="false">D77-F77</f>
-      </c>
-      <c r="J77" s="16" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="78" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A78" s="18" t="s">
-        <v>66</v>
-      </c>
-      <c r="B78" s="18" t="s">
-        <v>58</v>
-      </c>
-      <c r="C78" s="6" t="n">
-        <v>62</v>
-      </c>
-      <c r="D78" s="6" t="n">
-        <v>58</v>
-      </c>
-      <c r="E78" s="15" t="n">
-        <f aca="false">IFERROR(D78/C78,0)</f>
-      </c>
-      <c r="F78" s="6" t="n">
-        <f aca="false">SUMIFS('Receipt Summary'!F:F,'Receipt Summary'!E:E,A78)</f>
-      </c>
-      <c r="G78" s="6" t="n">
-        <f aca="false">SUMIFS('Receipt Summary'!G:G,'Receipt Summary'!E:E,A78)</f>
-      </c>
-      <c r="H78" s="15" t="n">
-        <f aca="false">IFERROR(G78/F78,0)</f>
-      </c>
-      <c r="I78" s="6" t="n">
-        <f aca="false">D78-F78</f>
-      </c>
-      <c r="J78" s="16" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="79" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A79" s="18" t="s">
-        <v>67</v>
-      </c>
-      <c r="B79" s="18" t="s">
-        <v>59</v>
-      </c>
-      <c r="C79" s="6" t="n">
-        <v>45</v>
-      </c>
-      <c r="D79" s="6" t="n">
-        <v>41</v>
-      </c>
-      <c r="E79" s="15" t="n">
-        <f aca="false">IFERROR(D79/C79,0)</f>
-      </c>
-      <c r="F79" s="6" t="n">
-        <f aca="false">SUMIFS('Receipt Summary'!F:F,'Receipt Summary'!E:E,A79)</f>
-      </c>
-      <c r="G79" s="6" t="n">
-        <f aca="false">SUMIFS('Receipt Summary'!G:G,'Receipt Summary'!E:E,A79)</f>
-      </c>
-      <c r="H79" s="15" t="n">
-        <f aca="false">IFERROR(G79/F79,0)</f>
-      </c>
-      <c r="I79" s="6" t="n">
-        <f aca="false">D79-F79</f>
-      </c>
-      <c r="J79" s="16" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="18" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="B80" s="18" t="s">
         <v>58</v>
       </c>
       <c r="C80" s="6" t="n">
-        <v>93</v>
+        <v>65</v>
       </c>
       <c r="D80" s="6" t="n">
-        <v>87</v>
+        <v>60</v>
       </c>
       <c r="E80" s="15" t="n">
         <f aca="false">IFERROR(D80/C80,0)</f>
@@ -8667,21 +8755,21 @@
         <f aca="false">D80-F80</f>
       </c>
       <c r="J80" s="16" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="18" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="B81" s="18" t="s">
         <v>59</v>
       </c>
       <c r="C81" s="6" t="n">
-        <v>73</v>
+        <v>7</v>
       </c>
       <c r="D81" s="6" t="n">
-        <v>71</v>
+        <v>7</v>
       </c>
       <c r="E81" s="15" t="n">
         <f aca="false">IFERROR(D81/C81,0)</f>
@@ -8699,21 +8787,21 @@
         <f aca="false">D81-F81</f>
       </c>
       <c r="J81" s="16" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="18" t="s">
-        <v>84</v>
+        <v>62</v>
       </c>
       <c r="B82" s="18" t="s">
         <v>58</v>
       </c>
       <c r="C82" s="6" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D82" s="6" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="E82" s="15" t="n">
         <f aca="false">IFERROR(D82/C82,0)</f>
@@ -8731,21 +8819,21 @@
         <f aca="false">D82-F82</f>
       </c>
       <c r="J82" s="16" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="18" t="s">
-        <v>85</v>
+        <v>63</v>
       </c>
       <c r="B83" s="18" t="s">
         <v>59</v>
       </c>
       <c r="C83" s="6" t="n">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="D83" s="6" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="E83" s="15" t="n">
         <f aca="false">IFERROR(D83/C83,0)</f>
@@ -8763,177 +8851,261 @@
         <f aca="false">D83-F83</f>
       </c>
       <c r="J83" s="16" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A84" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="B84" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="C84" s="6" t="n">
+        <v>62</v>
+      </c>
+      <c r="D84" s="6" t="n">
+        <v>58</v>
+      </c>
+      <c r="E84" s="15" t="n">
+        <f aca="false">IFERROR(D84/C84,0)</f>
+      </c>
+      <c r="F84" s="6" t="n">
+        <f aca="false">SUMIFS('Receipt Summary'!F:F,'Receipt Summary'!E:E,A84)</f>
+      </c>
+      <c r="G84" s="6" t="n">
+        <f aca="false">SUMIFS('Receipt Summary'!G:G,'Receipt Summary'!E:E,A84)</f>
+      </c>
+      <c r="H84" s="15" t="n">
+        <f aca="false">IFERROR(G84/F84,0)</f>
+      </c>
+      <c r="I84" s="6" t="n">
+        <f aca="false">D84-F84</f>
+      </c>
+      <c r="J84" s="16" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A85" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="B85" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="C85" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="D85" s="6" t="n">
+        <v>41</v>
+      </c>
+      <c r="E85" s="15" t="n">
+        <f aca="false">IFERROR(D85/C85,0)</f>
+      </c>
+      <c r="F85" s="6" t="n">
+        <f aca="false">SUMIFS('Receipt Summary'!F:F,'Receipt Summary'!E:E,A85)</f>
+      </c>
+      <c r="G85" s="6" t="n">
+        <f aca="false">SUMIFS('Receipt Summary'!G:G,'Receipt Summary'!E:E,A85)</f>
+      </c>
+      <c r="H85" s="15" t="n">
+        <f aca="false">IFERROR(G85/F85,0)</f>
+      </c>
+      <c r="I85" s="6" t="n">
+        <f aca="false">D85-F85</f>
+      </c>
+      <c r="J85" s="16" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A86" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="B86" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="C86" s="6" t="n">
+        <v>93</v>
+      </c>
+      <c r="D86" s="6" t="n">
+        <v>87</v>
+      </c>
+      <c r="E86" s="15" t="n">
+        <f aca="false">IFERROR(D86/C86,0)</f>
+      </c>
+      <c r="F86" s="6" t="n">
+        <f aca="false">SUMIFS('Receipt Summary'!F:F,'Receipt Summary'!E:E,A86)</f>
+      </c>
+      <c r="G86" s="6" t="n">
+        <f aca="false">SUMIFS('Receipt Summary'!G:G,'Receipt Summary'!E:E,A86)</f>
+      </c>
+      <c r="H86" s="15" t="n">
+        <f aca="false">IFERROR(G86/F86,0)</f>
+      </c>
+      <c r="I86" s="6" t="n">
+        <f aca="false">D86-F86</f>
+      </c>
+      <c r="J86" s="16" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A87" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="B87" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="C87" s="6" t="n">
+        <v>73</v>
+      </c>
+      <c r="D87" s="6" t="n">
+        <v>71</v>
+      </c>
+      <c r="E87" s="15" t="n">
+        <f aca="false">IFERROR(D87/C87,0)</f>
+      </c>
+      <c r="F87" s="6" t="n">
+        <f aca="false">SUMIFS('Receipt Summary'!F:F,'Receipt Summary'!E:E,A87)</f>
+      </c>
+      <c r="G87" s="6" t="n">
+        <f aca="false">SUMIFS('Receipt Summary'!G:G,'Receipt Summary'!E:E,A87)</f>
+      </c>
+      <c r="H87" s="15" t="n">
+        <f aca="false">IFERROR(G87/F87,0)</f>
+      </c>
+      <c r="I87" s="6" t="n">
+        <f aca="false">D87-F87</f>
+      </c>
+      <c r="J87" s="16" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A88" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="B88" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="C88" s="6" t="n">
+        <v>54</v>
+      </c>
+      <c r="D88" s="6" t="n">
+        <v>52</v>
+      </c>
+      <c r="E88" s="15" t="n">
+        <f aca="false">IFERROR(D88/C88,0)</f>
+      </c>
+      <c r="F88" s="6" t="n">
+        <f aca="false">SUMIFS('Receipt Summary'!F:F,'Receipt Summary'!E:E,A88)</f>
+      </c>
+      <c r="G88" s="6" t="n">
+        <f aca="false">SUMIFS('Receipt Summary'!G:G,'Receipt Summary'!E:E,A88)</f>
+      </c>
+      <c r="H88" s="15" t="n">
+        <f aca="false">IFERROR(G88/F88,0)</f>
+      </c>
+      <c r="I88" s="6" t="n">
+        <f aca="false">D88-F88</f>
+      </c>
+      <c r="J88" s="16" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A89" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="B89" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="C89" s="6" t="n">
+        <v>36</v>
+      </c>
+      <c r="D89" s="6" t="n">
+        <v>36</v>
+      </c>
+      <c r="E89" s="15" t="n">
+        <f aca="false">IFERROR(D89/C89,0)</f>
+      </c>
+      <c r="F89" s="6" t="n">
+        <f aca="false">SUMIFS('Receipt Summary'!F:F,'Receipt Summary'!E:E,A89)</f>
+      </c>
+      <c r="G89" s="6" t="n">
+        <f aca="false">SUMIFS('Receipt Summary'!G:G,'Receipt Summary'!E:E,A89)</f>
+      </c>
+      <c r="H89" s="15" t="n">
+        <f aca="false">IFERROR(G89/F89,0)</f>
+      </c>
+      <c r="I89" s="6" t="n">
+        <f aca="false">D89-F89</f>
+      </c>
+      <c r="J89" s="16" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="84" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="18" t="inlineStr">
+    <row r="90" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">5502462845</t>
         </is>
       </c>
-      <c r="B84" s="18" t="inlineStr">
+      <c r="B90" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">666541</t>
         </is>
       </c>
-      <c r="C84" s="6" t="n">
+      <c r="C90" s="6" t="n">
         <v>31</v>
       </c>
-      <c r="D84" s="6" t="n">
+      <c r="D90" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="E84" s="15" t="n">
-        <f aca="false">IFERROR(D84/C84,0)</f>
-      </c>
-      <c r="F84" s="6" t="n">
-        <f aca="false">SUMIFS('Receipt Summary'!F:F,'Receipt Summary'!E:E,A84)</f>
-      </c>
-      <c r="G84" s="6" t="n">
-        <f aca="false">SUMIFS('Receipt Summary'!G:G,'Receipt Summary'!E:E,A84)</f>
-      </c>
-      <c r="H84" s="15" t="n">
-        <f aca="false">IFERROR(G84/F84,0)</f>
-      </c>
-      <c r="I84" s="6" t="n">
-        <f aca="false">D84-F84</f>
-      </c>
-      <c r="J84" s="16" t="inlineStr">
+      <c r="E90" s="15" t="n">
+        <f aca="false">IFERROR(D90/C90,0)</f>
+      </c>
+      <c r="F90" s="6" t="n">
+        <f aca="false">SUMIFS('Receipt Summary'!F:F,'Receipt Summary'!E:E,A90)</f>
+      </c>
+      <c r="G90" s="6" t="n">
+        <f aca="false">SUMIFS('Receipt Summary'!G:G,'Receipt Summary'!E:E,A90)</f>
+      </c>
+      <c r="H90" s="15" t="n">
+        <f aca="false">IFERROR(G90/F90,0)</f>
+      </c>
+      <c r="I90" s="6" t="n">
+        <f aca="false">D90-F90</f>
+      </c>
+      <c r="J90" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">Newly harvested 06/15. SH sampled 31 intact, passed 30 (96.8%). Lot # reappears on the 06/24 tally (34 inspected / 30 passed) — recorded as a separate Visit 12, likely a tally-sheet lot carry-over (see notes). Not yet at ATM; expected in coming weeks.</t>
         </is>
       </c>
     </row>
-    <row r="86" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A86" s="3" t="s">
+    <row r="92" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A92" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="B86" s="3"/>
-      <c r="C86" s="3"/>
-      <c r="D86" s="3"/>
-      <c r="E86" s="3"/>
-      <c r="F86" s="3"/>
-      <c r="G86" s="3"/>
-      <c r="H86" s="3"/>
-      <c r="I86" s="3"/>
-      <c r="J86" s="3"/>
-      <c r="K86" s="3"/>
-      <c r="L86" s="3"/>
-    </row>
-    <row r="87" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A87" s="19" t="s">
-        <v>152</v>
-      </c>
-      <c r="B87" s="20" t="s">
-        <v>153</v>
-      </c>
-      <c r="C87" s="20"/>
-      <c r="D87" s="20"/>
-      <c r="E87" s="20"/>
-      <c r="F87" s="20"/>
-      <c r="G87" s="20"/>
-      <c r="H87" s="20"/>
-      <c r="I87" s="20"/>
-      <c r="J87" s="20"/>
-      <c r="K87" s="20"/>
-      <c r="L87" s="20"/>
-    </row>
-    <row r="88" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A88" s="19" t="s">
-        <v>154</v>
-      </c>
-      <c r="B88" s="20" t="s">
-        <v>155</v>
-      </c>
-      <c r="C88" s="20"/>
-      <c r="D88" s="20"/>
-      <c r="E88" s="20"/>
-      <c r="F88" s="20"/>
-      <c r="G88" s="20"/>
-      <c r="H88" s="20"/>
-      <c r="I88" s="20"/>
-      <c r="J88" s="20"/>
-      <c r="K88" s="20"/>
-      <c r="L88" s="20"/>
-    </row>
-    <row r="89" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A89" s="19" t="s">
-        <v>156</v>
-      </c>
-      <c r="B89" s="20" t="s">
-        <v>157</v>
-      </c>
-      <c r="C89" s="20"/>
-      <c r="D89" s="20"/>
-      <c r="E89" s="20"/>
-      <c r="F89" s="20"/>
-      <c r="G89" s="20"/>
-      <c r="H89" s="20"/>
-      <c r="I89" s="20"/>
-      <c r="J89" s="20"/>
-      <c r="K89" s="20"/>
-      <c r="L89" s="20"/>
-    </row>
-    <row r="90" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A90" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="B90" s="20" t="s">
-        <v>159</v>
-      </c>
-      <c r="C90" s="20"/>
-      <c r="D90" s="20"/>
-      <c r="E90" s="20"/>
-      <c r="F90" s="20"/>
-      <c r="G90" s="20"/>
-      <c r="H90" s="20"/>
-      <c r="I90" s="20"/>
-      <c r="J90" s="20"/>
-      <c r="K90" s="20"/>
-      <c r="L90" s="20"/>
-    </row>
-    <row r="91" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A91" s="19" t="s">
-        <v>160</v>
-      </c>
-      <c r="B91" s="20" t="s">
-        <v>161</v>
-      </c>
-      <c r="C91" s="20"/>
-      <c r="D91" s="20"/>
-      <c r="E91" s="20"/>
-      <c r="F91" s="20"/>
-      <c r="G91" s="20"/>
-      <c r="H91" s="20"/>
-      <c r="I91" s="20"/>
-      <c r="J91" s="20"/>
-      <c r="K91" s="20"/>
-      <c r="L91" s="20"/>
-    </row>
-    <row r="92" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A92" s="19" t="s">
-        <v>162</v>
-      </c>
-      <c r="B92" s="20" t="s">
-        <v>163</v>
-      </c>
-      <c r="C92" s="20"/>
-      <c r="D92" s="20"/>
-      <c r="E92" s="20"/>
-      <c r="F92" s="20"/>
-      <c r="G92" s="20"/>
-      <c r="H92" s="20"/>
-      <c r="I92" s="20"/>
-      <c r="J92" s="20"/>
-      <c r="K92" s="20"/>
-      <c r="L92" s="20"/>
+      <c r="B92" s="3"/>
+      <c r="C92" s="3"/>
+      <c r="D92" s="3"/>
+      <c r="E92" s="3"/>
+      <c r="F92" s="3"/>
+      <c r="G92" s="3"/>
+      <c r="H92" s="3"/>
+      <c r="I92" s="3"/>
+      <c r="J92" s="3"/>
+      <c r="K92" s="3"/>
+      <c r="L92" s="3"/>
     </row>
     <row r="93" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="19" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="B93" s="20" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="C93" s="20"/>
       <c r="D93" s="20"/>
@@ -8948,12 +9120,10 @@
     </row>
     <row r="94" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="B94" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Twelve inspection visits so far. Nine at Martins (Visits 1–5, 7, 9, 10, 12) and three at Parks (Visits 6, 8, 11). To extend, append new visit metadata, raw-data rows, and rollup rows; the TOTAL and SH→ATM sections then need refreshing.</t>
-        </is>
+        <v>154</v>
+      </c>
+      <c r="B94" s="20" t="s">
+        <v>155</v>
       </c>
       <c r="C94" s="20"/>
       <c r="D94" s="20"/>
@@ -8968,10 +9138,10 @@
     </row>
     <row r="95" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="19" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="B95" s="20" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="C95" s="20"/>
       <c r="D95" s="20"/>
@@ -8986,10 +9156,10 @@
     </row>
     <row r="96" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="19" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="B96" s="20" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="C96" s="20"/>
       <c r="D96" s="20"/>
@@ -9004,10 +9174,10 @@
     </row>
     <row r="97" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="19" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="B97" s="20" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="C97" s="20"/>
       <c r="D97" s="20"/>
@@ -9022,10 +9192,10 @@
     </row>
     <row r="98" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="19" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="B98" s="20" t="s">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="C98" s="20"/>
       <c r="D98" s="20"/>
@@ -9038,16 +9208,12 @@
       <c r="K98" s="20"/>
       <c r="L98" s="20"/>
     </row>
-    <row r="99" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13. New visits 9–12 (06/08–06/24)</t>
-        </is>
-      </c>
-      <c r="B99" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Visit 9 = 06/08 Martins; Visit 10 = 06/15 Martins; Visit 11 = 06/16 Parks (intact-only); Visit 12 = 06/24 Martins (intact-only). Source date/kill fields on several incoming sheets are volatile =NOW() captures (e.g. the Parks sheet sent 06/17 reads 06/16); the hand-entered harvest-date fields were used as the authoritative visit dates.</t>
-        </is>
+    <row r="99" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A99" s="19" t="s">
+        <v>164</v>
+      </c>
+      <c r="B99" s="20" t="s">
+        <v>165</v>
       </c>
       <c r="C99" s="20"/>
       <c r="D99" s="20"/>
@@ -9060,15 +9226,13 @@
       <c r="K99" s="20"/>
       <c r="L99" s="20"/>
     </row>
-    <row r="100" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14. Lot-number carry-over recurs (Visits 9 &amp; 12)</t>
-        </is>
+    <row r="100" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A100" s="19" t="s">
+        <v>166</v>
       </c>
       <c r="B100" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Visit 9 (06/08) reuses Visit 7’s lots 5502428786/5502428782, and Visit 12 (06/24) reuses Visit 10’s intact lot 5502462845 — the same template carry-over pattern documented in note 9 for lot 5502421192. Each is recorded as its own visit with its own raw and rollup rows, but per the note-9 precedent only the FIRST occurrence of each lot is reconciled in the SH→ATM section, so the reused-lot inspections do not generate duplicate SH→ATM rows.</t>
+          <t xml:space="preserve">Fourteen inspection visits so far. Nine at Martins (Visits 1–5, 7, 9, 10, 12) and five at Parks (Visits 6, 8, 11, 13, 14). To extend, append new visit metadata, raw-data rows, and rollup rows; the TOTAL and SH→ATM sections then need refreshing.</t>
         </is>
       </c>
       <c r="C100" s="20"/>
@@ -9082,16 +9246,12 @@
       <c r="K100" s="20"/>
       <c r="L100" s="20"/>
     </row>
-    <row r="101" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15. Visit 10 (06/15) — two intact tally lines combined; no non-intact</t>
-        </is>
-      </c>
-      <c r="B101" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The source recorded two intact 666541 lines on 06/15 (13/12/1 and 18/18/0); they share date, lot and condition, so they are combined into a single raw row (31/30/1). No non-intact units were collected (the SH had met its non-intact quota and run low on labels), so lot 5502462842 appears in the metadata but has no raw/rollup row.</t>
-        </is>
+    <row r="101" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A101" s="19" t="s">
+        <v>168</v>
+      </c>
+      <c r="B101" s="20" t="s">
+        <v>169</v>
       </c>
       <c r="C101" s="20"/>
       <c r="D101" s="20"/>
@@ -9104,16 +9264,12 @@
       <c r="K101" s="20"/>
       <c r="L101" s="20"/>
     </row>
-    <row r="102" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16. Visit 11 (06/16 Parks) — heavy upstream miscut losses</t>
-        </is>
-      </c>
-      <c r="B102" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The inspector noted ~100 pigs slaughtered, with the majority of blocks failing BEFORE reaching IQC due to miscuts during block removal. Of the 16 that reached inspection, 14 passed (1 bladder hole, 1 ureter damage). That upstream loss is a Parks harvest-technique signal not captured in the pass/fail counts here. PN normalized 668518 → 666518 per note 10. Separately, the “PARKS0603” sheet (internal date 06/02, 7/7 intact, no batch) is the SAME inspection already recorded as Visit 8 and was not re-added.</t>
-        </is>
+    <row r="102" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A102" s="19" t="s">
+        <v>170</v>
+      </c>
+      <c r="B102" s="20" t="s">
+        <v>171</v>
       </c>
       <c r="C102" s="20"/>
       <c r="D102" s="20"/>
@@ -9126,21 +9282,171 @@
       <c r="K102" s="20"/>
       <c r="L102" s="20"/>
     </row>
+    <row r="103" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A103" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="B103" s="20" t="s">
+        <v>173</v>
+      </c>
+      <c r="C103" s="20"/>
+      <c r="D103" s="20"/>
+      <c r="E103" s="20"/>
+      <c r="F103" s="20"/>
+      <c r="G103" s="20"/>
+      <c r="H103" s="20"/>
+      <c r="I103" s="20"/>
+      <c r="J103" s="20"/>
+      <c r="K103" s="20"/>
+      <c r="L103" s="20"/>
+    </row>
+    <row r="104" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A104" s="19" t="s">
+        <v>174</v>
+      </c>
+      <c r="B104" s="20" t="s">
+        <v>175</v>
+      </c>
+      <c r="C104" s="20"/>
+      <c r="D104" s="20"/>
+      <c r="E104" s="20"/>
+      <c r="F104" s="20"/>
+      <c r="G104" s="20"/>
+      <c r="H104" s="20"/>
+      <c r="I104" s="20"/>
+      <c r="J104" s="20"/>
+      <c r="K104" s="20"/>
+      <c r="L104" s="20"/>
+    </row>
+    <row r="105" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13. New visits 9–12 (06/08–06/24)</t>
+        </is>
+      </c>
+      <c r="B105" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Visit 9 = 06/08 Martins; Visit 10 = 06/15 Martins; Visit 11 = 06/16 Parks (intact-only); Visit 12 = 06/24 Martins (intact-only). Source date/kill fields on several incoming sheets are volatile =NOW() captures (e.g. the Parks sheet sent 06/17 reads 06/16); the hand-entered harvest-date fields were used as the authoritative visit dates.</t>
+        </is>
+      </c>
+      <c r="C105" s="20"/>
+      <c r="D105" s="20"/>
+      <c r="E105" s="20"/>
+      <c r="F105" s="20"/>
+      <c r="G105" s="20"/>
+      <c r="H105" s="20"/>
+      <c r="I105" s="20"/>
+      <c r="J105" s="20"/>
+      <c r="K105" s="20"/>
+      <c r="L105" s="20"/>
+    </row>
+    <row r="106" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14. Lot-number carry-over recurs (Visits 9 &amp; 12)</t>
+        </is>
+      </c>
+      <c r="B106" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Visit 9 (06/08) reuses Visit 7’s lots 5502428786/5502428782, and Visit 12 (06/24) reuses Visit 10’s intact lot 5502462845 — the same template carry-over pattern documented in note 9 for lot 5502421192. Each is recorded as its own visit with its own raw and rollup rows, but per the note-9 precedent only the FIRST occurrence of each lot is reconciled in the SH→ATM section, so the reused-lot inspections do not generate duplicate SH→ATM rows.</t>
+        </is>
+      </c>
+      <c r="C106" s="20"/>
+      <c r="D106" s="20"/>
+      <c r="E106" s="20"/>
+      <c r="F106" s="20"/>
+      <c r="G106" s="20"/>
+      <c r="H106" s="20"/>
+      <c r="I106" s="20"/>
+      <c r="J106" s="20"/>
+      <c r="K106" s="20"/>
+      <c r="L106" s="20"/>
+    </row>
+    <row r="107" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15. Visit 10 (06/15) — two intact tally lines combined; no non-intact</t>
+        </is>
+      </c>
+      <c r="B107" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The source recorded two intact 666541 lines on 06/15 (13/12/1 and 18/18/0); they share date, lot and condition, so they are combined into a single raw row (31/30/1). No non-intact units were collected (the SH had met its non-intact quota and run low on labels), so lot 5502462842 appears in the metadata but has no raw/rollup row.</t>
+        </is>
+      </c>
+      <c r="C107" s="20"/>
+      <c r="D107" s="20"/>
+      <c r="E107" s="20"/>
+      <c r="F107" s="20"/>
+      <c r="G107" s="20"/>
+      <c r="H107" s="20"/>
+      <c r="I107" s="20"/>
+      <c r="J107" s="20"/>
+      <c r="K107" s="20"/>
+      <c r="L107" s="20"/>
+    </row>
+    <row r="108" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16. Visit 11 (06/16 Parks) — heavy upstream miscut losses</t>
+        </is>
+      </c>
+      <c r="B108" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The inspector noted ~100 pigs slaughtered, with the majority of blocks failing BEFORE reaching IQC due to miscuts during block removal. Of the 16 that reached inspection, 14 passed (1 bladder hole, 1 ureter damage). That upstream loss is a Parks harvest-technique signal not captured in the pass/fail counts here. PN normalized 668518 → 666518 per note 10. Separately, the “PARKS0603” sheet (internal date 06/02, 7/7 intact, no batch) is the SAME inspection already recorded as Visit 8 and was not re-added.</t>
+        </is>
+      </c>
+      <c r="C108" s="20"/>
+      <c r="D108" s="20"/>
+      <c r="E108" s="20"/>
+      <c r="F108" s="20"/>
+      <c r="G108" s="20"/>
+      <c r="H108" s="20"/>
+      <c r="I108" s="20"/>
+      <c r="J108" s="20"/>
+      <c r="K108" s="20"/>
+      <c r="L108" s="20"/>
+    </row>
+    <row r="109" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17. New Parks visits 13 (06/22) &amp; 14 (06/25)</t>
+        </is>
+      </c>
+      <c r="B109" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Two more intact-only Parks inspections (no batch data; PN normalized 668518 → 666518). Visit 13 (06/22) = 36 inspected / 31 pass / 5 fail (1 bladder hole, 2 critical-area lacerations, 2 short blocks); Visit 14 (06/25) = 19 inspected / 16 pass / 3 fail (1 bladder hole, 1 ureter laceration, 1 short block). Both were received after Visit 12, so Visit 13’s harvest date (06/22) precedes Visit 12’s (06/24 Martins) — visit numbers reflect processing order, as with the existing Visit 7/8 overlap. No batch on either, so neither has an SH→ATM link (consistent with Visits 6, 8 and 11). Short blocks and critical-zone mesentery damage continue to dominate Parks scrap.</t>
+        </is>
+      </c>
+      <c r="C109" s="20"/>
+      <c r="D109" s="20"/>
+      <c r="E109" s="20"/>
+      <c r="F109" s="20"/>
+      <c r="G109" s="20"/>
+      <c r="H109" s="20"/>
+      <c r="I109" s="20"/>
+      <c r="J109" s="20"/>
+      <c r="K109" s="20"/>
+      <c r="L109" s="20"/>
+      <c r="C109" s="20"/>
+      <c r="D109" s="20"/>
+      <c r="E109" s="20"/>
+      <c r="F109" s="20"/>
+      <c r="G109" s="20"/>
+      <c r="H109" s="20"/>
+      <c r="I109" s="20"/>
+      <c r="J109" s="20"/>
+      <c r="K109" s="20"/>
+      <c r="L109" s="20"/>
+    </row>
   </sheetData>
-  <mergeCells count="23">
+  <mergeCells count="24">
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A2:L2"/>
     <mergeCell ref="A4:L4"/>
-    <mergeCell ref="A19:L19"/>
-    <mergeCell ref="A50:L50"/>
-    <mergeCell ref="A72:L72"/>
-    <mergeCell ref="A86:L86"/>
-    <mergeCell ref="B87:L87"/>
-    <mergeCell ref="B88:L88"/>
-    <mergeCell ref="B89:L89"/>
-    <mergeCell ref="B90:L90"/>
-    <mergeCell ref="B91:L91"/>
-    <mergeCell ref="B92:L92"/>
+    <mergeCell ref="A21:L21"/>
+    <mergeCell ref="A54:L54"/>
+    <mergeCell ref="A78:L78"/>
+    <mergeCell ref="A92:L92"/>
     <mergeCell ref="B93:L93"/>
     <mergeCell ref="B94:L94"/>
     <mergeCell ref="B95:L95"/>
@@ -9151,6 +9457,13 @@
     <mergeCell ref="B100:L100"/>
     <mergeCell ref="B101:L101"/>
     <mergeCell ref="B102:L102"/>
+    <mergeCell ref="B103:L103"/>
+    <mergeCell ref="B104:L104"/>
+    <mergeCell ref="B105:L105"/>
+    <mergeCell ref="B106:L106"/>
+    <mergeCell ref="B107:L107"/>
+    <mergeCell ref="B108:L108"/>
+    <mergeCell ref="B109:L109"/>
   </mergeCells>
   <conditionalFormatting sqref="J17:J39">
     <cfRule type="colorScale" priority="2">

--- a/QC inspections suppliers/Pelvic_Blocks_Quality_062626.xlsx
+++ b/QC inspections suppliers/Pelvic_Blocks_Quality_062626.xlsx
@@ -10,6 +10,7 @@
   <sheets>
     <sheet name="Defect Trends- ATM" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="Slaughterhouse IQC" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="SmartAssessment" sheetId="12" state="visible" r:id="rId15"/>
     <sheet name="Receipt Summary" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="Master Data" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="Defect Pivot 666541-F" sheetId="5" state="visible" r:id="rId7"/>
@@ -6054,6 +6055,263 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A37"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="98" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SmartAssessment — Pelvic Block Quality (Claude analysis)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Author: Claude · Compiled 2026-06-26 · Scope: Slaughterhouse IQC visits 1–14 + ATM receipt data. These are working analyst notes and interpretation — verify with Quality before any external/supplier use.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. OBJECTIVE (as understood)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Root-cause pelvic-block defects to their point of origin UPSTREAM — before the harvesting tech consolidates the pelvic block, and ideally back to slaughter/evisceration (handling of the main tissue block and GI). Goal: raise HARVESTING FIRST-PASS YIELD = successful pelvic blocks consolidated ÷ main tissue blocks the harvesting tech receives. Active at BOTH suppliers: Parks (already engaged) and Martins (sampling defective pelvics and bringing them to ATM for evaluation/root-cause). This is a yield-improvement / root-cause program, not a supplier down-select.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2. THE QUALITY PIPELINE — WHERE YIELD IS LOST</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stage model</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stage 0  Upstream: slaughter + evisceration; handling of the main tissue block / GI.
+Stage 1  Harvesting: SH tech consolidates the pelvic block  ← first major yield loss, today largely UNMEASURED.
+Stage 2  SH-floor IQC: our ATM inspector, PRE-freeze — this is the current '# Inspected / Pass / Fail'.
+Stage 3  Freeze.
+Stage 4  ATM receipt: POST-freeze — the gate tied to performance goals.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Key gap</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The tally sheets only count blocks that REACH our SH inspector. Blocks lost during harvesting (miscuts before presentation) are NOT in the pass/fail counts. See Parks Visit 11 (06/16): '~100 pigs slaughtered, the majority of blocks failed BEFORE reaching IQC due to miscuts during block removal.' That upstream loss IS the harvesting first-pass yield this program targets — and it is currently invisible. RECOMMEND adding two fields to the tally template: (a) main blocks received by harvesting tech, (b) blocks rejected at harvesting before IQC. Then harvesting FPY can be computed instead of inferred from a note.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="0"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3. PARKS 05/11 CRITICAL-MESENTERY EVENT — ROOT-CAUSE SUCCESS STORY</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ATM receipt 05/11 (PN 666518): 220 received, 195 scrapped (88.6% rejection), of which 187 were critical mesentery holes/lacerations. This ONE event is 187 of Parks's 218 total critical-mesentery defects across the entire record — it dominates the Parks picture.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Confirmed REAL (per Quality). Root cause: a harvesting cut that was dividing the mesentery from the block, plus bowel-area handling issues the slaughterhouse was unaware of. Corrected via training + monitoring; monthly verification calls ongoing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Post-intervention SH-floor visits (05/28 → 06/25) show NO recurrence of catastrophic rejection — yields 69–100%, steady ~84–88% recently. Residual scrap is now dominated by 'short blocks' and 'critical-area lacerations.' Read: the program fixed the catastrophic failure mode; a residual mesentery-length / critical-zone signal remains and is the next root-cause target at Parks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="0"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4. WHERE DEFECTS ORIGINATE (origin tagging for root-cause)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">• Upstream / harvesting (the target of this program): critical mesentery hole/laceration; the mesentery-dividing cut; mesentery length too short (≤7" / 'short block'); bowel, bladder and urethra lacerations from miscuts; blood clots.
+• Freeze/thaw-attributable (per Quality — appear POST-thaw at ATM, not at the SH floor): small lacerations. These should NOT be charged to the harvesting tech's FPY; they explain part of the SH→ATM gap.
+• Spec / measurement drift (already in the IQC notes): bladder-length lower spec changed &lt;3"→&lt;2"; 'mesentery ≤7"' first measured 03/30.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Recommendation</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">When ATM root-cause data arrives, tag each scrapped unit as harvesting-origin vs freeze/thaw-origin vs spec-drift, so the harvesting-FPY metric is not polluted by freeze/thaw damage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="0"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5. SH-FLOOR vs ATM YIELD (the stage gap)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SH-floor pass (pre-freeze): Martins 94.4% (640/678), Parks 84.0% (79/94).
+ATM receipt (post-freeze, rolling): Martins ~85.4% accepted (2119/2481), Parks ~39.8% (167/420) — Parks dominated by the 05/11 event.
+The SH→ATM gap is partly REAL freeze/thaw damage (small lacerations) and partly that ATM is a stricter/later gate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Caveat</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Only 3 lots currently have BOTH SH and ATM data (5502378434, 5502391862, 5502404928). The cleanest freeze/thaw proxy is the SH-pass → ATM-accept delta on MATCHED lots; we need more matched lots — especially post-intervention Parks — before trusting the gap quantitatively.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="0"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6. 666541 vs 666506 — SPEC CORRECTION</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Per Quality (06/26): 666506 = pelvic block with the MORE stringent spec; 666541 = the same part, LESS strict, and tied to ATM performance goals — so protecting 666541's ATM yield is the priority metric.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">⚠ Supersedes earlier assumption</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">This REVERSES the workbook's earlier framing (Slaughterhouse IQC note 1 / README) that treated 666506 as a 'downgrade/recovery' grade. Naming tension to reconcile: the tally sheets label 666541 'intact' and 666506 'non intact,' and some scrap notes say defective units were 'moved to non-intact' — wording that reads like a downgrade, which is hard to square with 666506 being the TIGHTER spec. Worth a one-line confirmation so labels and spec hierarchy agree. (I have NOT edited the old notes — flagging only.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="0"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7. DATA-QUALITY CAVEATS AFFECTING THIS ASSESSMENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">• Parks SH sample is small (94 units, 5 visits) — supplier comparisons are directional, not statistical.
+• ATM Parks data currently ends 05/11, which PRE-DATES the SH-floor inspections (start 05/28) — so there is no clean post-intervention stage-to-stage comparison for Parks yet.
+• Lot-number carry-overs (Visits 5, 9, 12) mean some 'lots' repeat across weeks — see IQC notes 9 &amp; 14.
+• Several incoming tally dates are volatile =NOW() captures; hand-entered harvest dates were used as authoritative.
+• ATM data will soon lose batch numbers (Tableau) — a separate batch-less sheet is planned.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="0"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8. RECOMMENDED NEXT STEPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Add harvesting-FPY capture to the tally template (main blocks received; blocks rejected pre-IQC) so upstream loss is measured, not inferred.
+2. Tag ATM scrap by stage-of-origin (harvesting vs freeze/thaw vs spec-drift); keep freeze/thaw small-lacerations out of the harvesting-FPY denominator.
+3. Build a matched-lot SH→ATM tracker as more lots gain both stages — prioritize post-intervention Parks lots to verify the 05/11 fix holds through freeze/thaw.
+4. Reconcile the 666506 / 'non-intact' naming vs the tighter-spec definition; once confirmed, update IQC note 1 and the README.
+5. Continue monthly supplier calls; trend the residual Parks 'short block' / critical-zone signal and the Martins sampled-defect root-causes.
+6. When Tableau ATM data lands, link defect categories to stage-of-origin in the new batch-less sheet.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="false">

--- a/QC inspections suppliers/Pelvic_Blocks_Quality_062626.xlsx
+++ b/QC inspections suppliers/Pelvic_Blocks_Quality_062626.xlsx
@@ -6642,7 +6642,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="14" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="13.5" customHeight="true">
       <c r="A14" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Visit 9</t>
@@ -6689,7 +6689,7 @@
         </is>
       </c>
     </row>
-    <row r="15" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="13.5" customHeight="true">
       <c r="A15" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Visit 10</t>
@@ -6736,7 +6736,7 @@
         </is>
       </c>
     </row>
-    <row r="16" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="13.5" customHeight="true">
       <c r="A16" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Visit 11</t>
@@ -6783,7 +6783,7 @@
         </is>
       </c>
     </row>
-    <row r="17" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="13.5" customHeight="true">
       <c r="A17" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Visit 12</t>
@@ -6830,7 +6830,7 @@
         </is>
       </c>
     </row>
-    <row r="18" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="13.5" customHeight="true">
       <c r="A18" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Visit 13</t>
@@ -6877,7 +6877,7 @@
         </is>
       </c>
     </row>
-    <row r="19" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="13.5" customHeight="true">
       <c r="A19" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Visit 14</t>
@@ -7842,7 +7842,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="46" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="13.5" customHeight="true">
       <c r="A46" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-06-08</t>
@@ -7896,7 +7896,7 @@
         </is>
       </c>
     </row>
-    <row r="47" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="13.5" customHeight="true">
       <c r="A47" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-06-08</t>
@@ -7950,7 +7950,7 @@
         </is>
       </c>
     </row>
-    <row r="48" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="27.0" customHeight="true">
       <c r="A48" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-06-15</t>
@@ -8004,7 +8004,7 @@
         </is>
       </c>
     </row>
-    <row r="49" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="40.5" customHeight="true">
       <c r="A49" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-06-16</t>
@@ -8058,7 +8058,7 @@
         </is>
       </c>
     </row>
-    <row r="50" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="13.5" customHeight="true">
       <c r="A50" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-06-24</t>
@@ -8112,7 +8112,7 @@
         </is>
       </c>
     </row>
-    <row r="51" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="27.0" customHeight="true">
       <c r="A51" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-06-22</t>
@@ -8166,7 +8166,7 @@
         </is>
       </c>
     </row>
-    <row r="52" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="27.0" customHeight="true">
       <c r="A52" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-06-25</t>
@@ -8642,7 +8642,7 @@
         <f aca="false">IFERROR(G68/F68,0)</f>
       </c>
     </row>
-    <row r="69" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="13.5" customHeight="true">
       <c r="A69" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">5502428786</t>
@@ -8681,7 +8681,7 @@
         <f aca="false">IFERROR(G69/F69,0)</f>
       </c>
     </row>
-    <row r="70" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="13.5" customHeight="true">
       <c r="A70" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">5502428782</t>
@@ -8720,7 +8720,7 @@
         <f aca="false">IFERROR(G70/F70,0)</f>
       </c>
     </row>
-    <row r="71" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="13.5" customHeight="true">
       <c r="A71" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">5502462845</t>
@@ -8759,7 +8759,7 @@
         <f aca="false">IFERROR(G71/F71,0)</f>
       </c>
     </row>
-    <row r="72" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="13.5" customHeight="true">
       <c r="A72" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">5502462845</t>
@@ -8798,7 +8798,7 @@
         <f aca="false">IFERROR(G72/F72,0)</f>
       </c>
     </row>
-    <row r="73" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="13.5" customHeight="true">
       <c r="A73" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">(no batch data)</t>
@@ -8837,7 +8837,7 @@
         <f aca="false">IFERROR(G73/F73,0)</f>
       </c>
     </row>
-    <row r="74" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="13.5" customHeight="true">
       <c r="A74" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">(no batch data)</t>
@@ -8876,7 +8876,7 @@
         <f aca="false">IFERROR(G74/F74,0)</f>
       </c>
     </row>
-    <row r="75" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="13.5" customHeight="true">
       <c r="A75" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">(no batch data)</t>
@@ -9304,7 +9304,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="90" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+    <row r="90" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="72.0" customHeight="true">
       <c r="A90" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">5502462845</t>
@@ -9576,7 +9576,7 @@
       <c r="K104" s="20"/>
       <c r="L104" s="20"/>
     </row>
-    <row r="105" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+    <row r="105" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="48.0" customHeight="true">
       <c r="A105" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">13. New visits 9–12 (06/08–06/24)</t>
@@ -9598,7 +9598,7 @@
       <c r="K105" s="20"/>
       <c r="L105" s="20"/>
     </row>
-    <row r="106" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+    <row r="106" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="48.0" customHeight="true">
       <c r="A106" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">14. Lot-number carry-over recurs (Visits 9 &amp; 12)</t>
@@ -9620,7 +9620,7 @@
       <c r="K106" s="20"/>
       <c r="L106" s="20"/>
     </row>
-    <row r="107" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+    <row r="107" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="48.0" customHeight="true">
       <c r="A107" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">15. Visit 10 (06/15) — two intact tally lines combined; no non-intact</t>
@@ -9642,7 +9642,7 @@
       <c r="K107" s="20"/>
       <c r="L107" s="20"/>
     </row>
-    <row r="108" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+    <row r="108" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="48.0" customHeight="true">
       <c r="A108" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">16. Visit 11 (06/16 Parks) — heavy upstream miscut losses</t>
@@ -9664,7 +9664,7 @@
       <c r="K108" s="20"/>
       <c r="L108" s="20"/>
     </row>
-    <row r="109" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+    <row r="109" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="48.0" customHeight="true">
       <c r="A109" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">17. New Parks visits 13 (06/22) &amp; 14 (06/25)</t>
@@ -9723,7 +9723,7 @@
     <mergeCell ref="B108:L108"/>
     <mergeCell ref="B109:L109"/>
   </mergeCells>
-  <conditionalFormatting sqref="J17:J39">
+  <conditionalFormatting sqref="J23:J52">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="num" val="0.7"/>
@@ -9735,7 +9735,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I43:I55">
+  <conditionalFormatting sqref="I56:I75">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="num" val="0.7"/>
@@ -9747,7 +9747,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E60:E69">
+  <conditionalFormatting sqref="E80:E90">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="num" val="0.7"/>
@@ -9759,7 +9759,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H60:H69">
+  <conditionalFormatting sqref="H80:H90">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="num" val="0.7"/>

--- a/QC inspections suppliers/Pelvic_Blocks_Quality_062626.xlsx
+++ b/QC inspections suppliers/Pelvic_Blocks_Quality_062626.xlsx
@@ -6317,7 +6317,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L109"/>
+  <dimension ref="A1:L134"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16.78"/>
@@ -6924,257 +6924,304 @@
         </is>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="3" t="s">
+    <row r="20" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="13.5" customHeight="true">
+      <c r="A20" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Visit 15</t>
+        </is>
+      </c>
+      <c r="B20" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-29</t>
+        </is>
+      </c>
+      <c r="C20" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Martins</t>
+        </is>
+      </c>
+      <c r="D20" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Toni Cruz</t>
+        </is>
+      </c>
+      <c r="E20" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jesus</t>
+        </is>
+      </c>
+      <c r="F20" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5502471460</t>
+        </is>
+      </c>
+      <c r="G20" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5502471457</t>
+        </is>
+      </c>
+      <c r="H20" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">666541</t>
+        </is>
+      </c>
+      <c r="I20" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">666506</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="13.5" customHeight="true">
+      <c r="A21" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Visit 16</t>
+        </is>
+      </c>
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-29</t>
+        </is>
+      </c>
+      <c r="C21" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Parks Family Meats</t>
+        </is>
+      </c>
+      <c r="D21" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rasmin Mujanovic</t>
+        </is>
+      </c>
+      <c r="E21" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Natalie</t>
+        </is>
+      </c>
+      <c r="F21" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(no batch data)</t>
+        </is>
+      </c>
+      <c r="G21" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="H21" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">666518</t>
+        </is>
+      </c>
+      <c r="I21" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="13.5" customHeight="true">
+      <c r="A22" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Visit 17</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-07-06</t>
+        </is>
+      </c>
+      <c r="C22" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Martins</t>
+        </is>
+      </c>
+      <c r="D22" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Toni Cruz</t>
+        </is>
+      </c>
+      <c r="E22" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jesus</t>
+        </is>
+      </c>
+      <c r="F22" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5502471460</t>
+        </is>
+      </c>
+      <c r="G22" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5502471457</t>
+        </is>
+      </c>
+      <c r="H22" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">666541</t>
+        </is>
+      </c>
+      <c r="I22" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">666506</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="13.5" customHeight="true">
+      <c r="A23" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Visit 18</t>
+        </is>
+      </c>
+      <c r="B23" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-07-13</t>
+        </is>
+      </c>
+      <c r="C23" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Martins</t>
+        </is>
+      </c>
+      <c r="D23" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Toni Cruz</t>
+        </is>
+      </c>
+      <c r="E23" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jesus</t>
+        </is>
+      </c>
+      <c r="F23" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5502495107</t>
+        </is>
+      </c>
+      <c r="G23" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5502495104</t>
+        </is>
+      </c>
+      <c r="H23" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">666541</t>
+        </is>
+      </c>
+      <c r="I23" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">666506</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="13.5" customHeight="true">
+      <c r="A24" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Visit 19</t>
+        </is>
+      </c>
+      <c r="B24" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-07-13</t>
+        </is>
+      </c>
+      <c r="C24" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Parks Family Meats</t>
+        </is>
+      </c>
+      <c r="D24" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rasmin Mujanovic</t>
+        </is>
+      </c>
+      <c r="E24" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Natalie</t>
+        </is>
+      </c>
+      <c r="F24" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(no batch data)</t>
+        </is>
+      </c>
+      <c r="G24" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="H24" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">666518</t>
+        </is>
+      </c>
+      <c r="I24" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
-      <c r="H21" s="3"/>
-      <c r="I21" s="3"/>
-      <c r="J21" s="3"/>
-      <c r="K21" s="3"/>
-      <c r="L21" s="3"/>
-    </row>
-    <row r="22" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="11" t="s">
+      <c r="B26" s="3"/>
+      <c r="C26" s="3"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
+      <c r="H26" s="3"/>
+      <c r="I26" s="3"/>
+      <c r="J26" s="3"/>
+      <c r="K26" s="3"/>
+      <c r="L26" s="3"/>
+    </row>
+    <row r="27" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="B22" s="11" t="s">
+      <c r="B27" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="C22" s="11" t="s">
+      <c r="C27" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="D22" s="11" t="s">
+      <c r="D27" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="E22" s="11" t="s">
+      <c r="E27" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="F22" s="11" t="s">
+      <c r="F27" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="G22" s="11" t="s">
+      <c r="G27" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="H22" s="11" t="s">
+      <c r="H27" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="I22" s="11" t="s">
+      <c r="I27" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="J22" s="11" t="s">
+      <c r="J27" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="K22" s="11" t="s">
+      <c r="K27" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="L22" s="11" t="s">
+      <c r="L27" s="11" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="5" t="s">
+    <row r="28" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="5" t="s">
         <v>12</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="F23" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="G23" s="6" t="n">
-        <v>48</v>
-      </c>
-      <c r="H23" s="6" t="n">
-        <v>47</v>
-      </c>
-      <c r="I23" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J23" s="15" t="n">
-        <f aca="false">IFERROR(H23/G23,0)</f>
-      </c>
-      <c r="K23" s="16" t="s">
-        <v>102</v>
-      </c>
-      <c r="L23" s="5" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="F24" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="G24" s="6" t="n">
-        <v>17</v>
-      </c>
-      <c r="H24" s="6" t="n">
-        <v>13</v>
-      </c>
-      <c r="I24" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="J24" s="15" t="n">
-        <f aca="false">IFERROR(H24/G24,0)</f>
-      </c>
-      <c r="K24" s="16" t="s">
-        <v>105</v>
-      </c>
-      <c r="L24" s="5" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="F25" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="G25" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="H25" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="I25" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" s="15" t="n">
-        <f aca="false">IFERROR(H25/G25,0)</f>
-      </c>
-      <c r="K25" s="16" t="s">
-        <v>108</v>
-      </c>
-      <c r="L25" s="5" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="F26" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="G26" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="H26" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="I26" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" s="15" t="n">
-        <f aca="false">IFERROR(H26/G26,0)</f>
-      </c>
-      <c r="K26" s="16"/>
-      <c r="L26" s="5" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="E27" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="F27" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="G27" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" s="15" t="n">
-        <f aca="false">IFERROR(H27/G27,0)</f>
-      </c>
-      <c r="K27" s="16" t="s">
-        <v>109</v>
-      </c>
-      <c r="L27" s="5" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="5" t="s">
-        <v>110</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>53</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D28" s="5" t="s">
         <v>58</v>
@@ -7186,10 +7233,10 @@
         <v>101</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="I28" s="6" t="n">
         <v>1</v>
@@ -7198,59 +7245,59 @@
         <f aca="false">IFERROR(H28/G28,0)</f>
       </c>
       <c r="K28" s="16" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="L28" s="5" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
-        <v>13</v>
+        <v>104</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>53</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J29" s="15" t="n">
         <f aca="false">IFERROR(H29/G29,0)</f>
       </c>
       <c r="K29" s="16" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="L29" s="5" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="s">
-        <v>110</v>
+        <v>12</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>53</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="D30" s="5" t="s">
         <v>59</v>
@@ -7262,19 +7309,19 @@
         <v>107</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J30" s="15" t="n">
         <f aca="false">IFERROR(H30/G30,0)</f>
       </c>
       <c r="K30" s="16" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="L30" s="5" t="s">
         <v>103</v>
@@ -7282,51 +7329,49 @@
     </row>
     <row r="31" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="s">
-        <v>14</v>
+        <v>104</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>53</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J31" s="15" t="n">
         <f aca="false">IFERROR(H31/G31,0)</f>
       </c>
-      <c r="K31" s="16" t="s">
-        <v>114</v>
-      </c>
+      <c r="K31" s="16"/>
       <c r="L31" s="5" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="s">
-        <v>115</v>
+        <v>13</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>53</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D32" s="5" t="s">
         <v>58</v>
@@ -7338,19 +7383,19 @@
         <v>101</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J32" s="15" t="n">
         <f aca="false">IFERROR(H32/G32,0)</f>
       </c>
       <c r="K32" s="16" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="L32" s="5" t="s">
         <v>103</v>
@@ -7358,37 +7403,37 @@
     </row>
     <row r="33" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="5" t="s">
-        <v>14</v>
+        <v>110</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>53</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>16</v>
+        <v>57</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>13</v>
+        <v>56</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J33" s="15" t="n">
         <f aca="false">IFERROR(H33/G33,0)</f>
       </c>
       <c r="K33" s="16" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="L33" s="5" t="s">
         <v>103</v>
@@ -7396,13 +7441,13 @@
     </row>
     <row r="34" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="5" t="s">
-        <v>115</v>
+        <v>13</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>53</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D34" s="5" t="s">
         <v>59</v>
@@ -7414,19 +7459,19 @@
         <v>107</v>
       </c>
       <c r="G34" s="6" t="n">
+        <v>31</v>
+      </c>
+      <c r="H34" s="6" t="n">
         <v>29</v>
       </c>
-      <c r="H34" s="6" t="n">
-        <v>28</v>
-      </c>
       <c r="I34" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J34" s="15" t="n">
         <f aca="false">IFERROR(H34/G34,0)</f>
       </c>
       <c r="K34" s="16" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="L34" s="5" t="s">
         <v>103</v>
@@ -7434,37 +7479,37 @@
     </row>
     <row r="35" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="5" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>53</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>58</v>
+        <v>19</v>
       </c>
       <c r="I35" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J35" s="15" t="n">
         <f aca="false">IFERROR(H35/G35,0)</f>
       </c>
       <c r="K35" s="16" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="L35" s="5" t="s">
         <v>103</v>
@@ -7472,13 +7517,13 @@
     </row>
     <row r="36" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="5" t="s">
-        <v>120</v>
+        <v>14</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>53</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D36" s="5" t="s">
         <v>58</v>
@@ -7490,57 +7535,57 @@
         <v>101</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="I36" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J36" s="15" t="n">
         <f aca="false">IFERROR(H36/G36,0)</f>
       </c>
       <c r="K36" s="16" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="L36" s="5" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="5" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>53</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J37" s="15" t="n">
         <f aca="false">IFERROR(H37/G37,0)</f>
       </c>
       <c r="K37" s="16" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="L37" s="5" t="s">
         <v>103</v>
@@ -7548,13 +7593,13 @@
     </row>
     <row r="38" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="5" t="s">
-        <v>120</v>
+        <v>14</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>53</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D38" s="5" t="s">
         <v>59</v>
@@ -7566,109 +7611,109 @@
         <v>107</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J38" s="15" t="n">
         <f aca="false">IFERROR(H38/G38,0)</f>
       </c>
       <c r="K38" s="16" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="L38" s="5" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="5" t="s">
-        <v>73</v>
+        <v>115</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>53</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J39" s="15" t="n">
         <f aca="false">IFERROR(H39/G39,0)</f>
       </c>
       <c r="K39" s="16" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="L39" s="5" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="5" t="s">
-        <v>16</v>
+        <v>118</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>81</v>
+        <v>58</v>
       </c>
       <c r="E40" s="5" t="s">
         <v>100</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>125</v>
+        <v>101</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>16</v>
+        <v>62</v>
       </c>
       <c r="H40" s="6" t="n">
-        <v>11</v>
+        <v>58</v>
       </c>
       <c r="I40" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J40" s="15" t="n">
         <f aca="false">IFERROR(H40/G40,0)</f>
       </c>
       <c r="K40" s="16" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="L40" s="5" t="s">
-        <v>127</v>
+        <v>103</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="5" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>53</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="D41" s="5" t="s">
         <v>58</v>
@@ -7680,55 +7725,57 @@
         <v>101</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="H41" s="6" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="I41" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J41" s="15" t="n">
         <f aca="false">IFERROR(H41/G41,0)</f>
       </c>
-      <c r="K41" s="16"/>
+      <c r="K41" s="16" t="s">
+        <v>121</v>
+      </c>
       <c r="L41" s="5" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="5" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>53</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="G42" s="6" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="H42" s="6" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I42" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J42" s="15" t="n">
         <f aca="false">IFERROR(H42/G42,0)</f>
       </c>
       <c r="K42" s="16" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="L42" s="5" t="s">
         <v>103</v>
@@ -7736,13 +7783,13 @@
     </row>
     <row r="43" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="5" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>53</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="D43" s="5" t="s">
         <v>59</v>
@@ -7754,61 +7801,65 @@
         <v>107</v>
       </c>
       <c r="G43" s="6" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="H43" s="6" t="n">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J43" s="15" t="n">
         <f aca="false">IFERROR(H43/G43,0)</f>
       </c>
-      <c r="K43" s="16"/>
+      <c r="K43" s="16" t="s">
+        <v>123</v>
+      </c>
       <c r="L43" s="5" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="5" t="s">
-        <v>129</v>
+        <v>73</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>53</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="G44" s="6" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="H44" s="6" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="I44" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J44" s="15" t="n">
         <f aca="false">IFERROR(H44/G44,0)</f>
       </c>
-      <c r="K44" s="16"/>
+      <c r="K44" s="16" t="s">
+        <v>124</v>
+      </c>
       <c r="L44" s="5" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="5" t="s">
-        <v>87</v>
+        <v>16</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>77</v>
@@ -7826,311 +7877,225 @@
         <v>125</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J45" s="15" t="n">
         <f aca="false">IFERROR(H45/G45,0)</f>
       </c>
-      <c r="K45" s="16"/>
+      <c r="K45" s="16" t="s">
+        <v>126</v>
+      </c>
       <c r="L45" s="5" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="46" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="13.5" customHeight="true">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-08</t>
-        </is>
-      </c>
-      <c r="B46" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Martins</t>
-        </is>
-      </c>
-      <c r="C46" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5502428786</t>
-        </is>
-      </c>
-      <c r="D46" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">666541</t>
-        </is>
-      </c>
-      <c r="E46" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Intact</t>
-        </is>
-      </c>
-      <c r="F46" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tiss, porcine, fem, Pelvic block, intact</t>
-        </is>
+    <row r="46" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="E46" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="F46" s="5" t="s">
+        <v>101</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="H46" s="6" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="I46" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J46" s="15" t="n">
         <f aca="false">IFERROR(H46/G46,0)</f>
       </c>
-      <c r="K46" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 cut urethra</t>
-        </is>
-      </c>
-      <c r="L46" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Toni Cruz / Jesus</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="13.5" customHeight="true">
-      <c r="A47" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-08</t>
-        </is>
-      </c>
-      <c r="B47" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Martins</t>
-        </is>
-      </c>
-      <c r="C47" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5502428782</t>
-        </is>
-      </c>
-      <c r="D47" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">666506</t>
-        </is>
-      </c>
-      <c r="E47" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Non-intact</t>
-        </is>
-      </c>
-      <c r="F47" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tiss, porcine, fem, Pelvic block, non-intact</t>
-        </is>
+      <c r="K46" s="16"/>
+      <c r="L46" s="5" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="D47" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="E47" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="F47" s="5" t="s">
+        <v>101</v>
       </c>
       <c r="G47" s="6" t="n">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="H47" s="6" t="n">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="I47" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J47" s="15" t="n">
         <f aca="false">IFERROR(H47/G47,0)</f>
       </c>
-      <c r="K47" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 short block</t>
-        </is>
-      </c>
-      <c r="L47" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Toni Cruz / Jesus</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="27.0" customHeight="true">
-      <c r="A48" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-15</t>
-        </is>
-      </c>
-      <c r="B48" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Martins</t>
-        </is>
-      </c>
-      <c r="C48" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5502462845</t>
-        </is>
-      </c>
-      <c r="D48" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">666541</t>
-        </is>
-      </c>
-      <c r="E48" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Intact</t>
-        </is>
-      </c>
-      <c r="F48" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tiss, porcine, fem, Pelvic block, intact</t>
-        </is>
+      <c r="K47" s="16" t="s">
+        <v>130</v>
+      </c>
+      <c r="L47" s="5" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D48" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="E48" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="F48" s="5" t="s">
+        <v>107</v>
       </c>
       <c r="G48" s="6" t="n">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="H48" s="6" t="n">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="I48" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J48" s="15" t="n">
         <f aca="false">IFERROR(H48/G48,0)</f>
       </c>
-      <c r="K48" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 damaged bowel (source had two intact tally lines: 13/12/1 + 18/18/0, combined here)</t>
-        </is>
-      </c>
-      <c r="L48" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Toni Cruz / Jesus</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="40.5" customHeight="true">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-16</t>
-        </is>
-      </c>
-      <c r="B49" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Parks Family Meats</t>
-        </is>
-      </c>
-      <c r="C49" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(no batch data)</t>
-        </is>
-      </c>
-      <c r="D49" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">666518</t>
-        </is>
-      </c>
-      <c r="E49" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Intact</t>
-        </is>
-      </c>
-      <c r="F49" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tiss, porcine, fem, Pelvic block, intact, SM</t>
-        </is>
+      <c r="K48" s="16"/>
+      <c r="L48" s="5" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="E49" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="F49" s="5" t="s">
+        <v>107</v>
       </c>
       <c r="G49" s="6" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="H49" s="6" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="I49" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J49" s="15" t="n">
         <f aca="false">IFERROR(H49/G49,0)</f>
       </c>
-      <c r="K49" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 bladder hole; 1 ureter damage (many blocks failed upstream from miscuts during removal — see notes)</t>
-        </is>
-      </c>
-      <c r="L49" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Rasmin Mujanovic / Natalie</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="13.5" customHeight="true">
-      <c r="A50" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-24</t>
-        </is>
-      </c>
-      <c r="B50" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Martins</t>
-        </is>
-      </c>
-      <c r="C50" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5502462845</t>
-        </is>
-      </c>
-      <c r="D50" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">666541</t>
-        </is>
-      </c>
-      <c r="E50" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Intact</t>
-        </is>
-      </c>
-      <c r="F50" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tiss, porcine, fem, Pelvic block, intact</t>
-        </is>
+      <c r="K49" s="16"/>
+      <c r="L49" s="5" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="D50" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="E50" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="F50" s="5" t="s">
+        <v>125</v>
       </c>
       <c r="G50" s="6" t="n">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="H50" s="6" t="n">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="I50" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J50" s="15" t="n">
         <f aca="false">IFERROR(H50/G50,0)</f>
       </c>
-      <c r="K50" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 damaged bladder; 3 damaged membrane</t>
-        </is>
-      </c>
-      <c r="L50" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Toni Cruz / Jesus</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="27.0" customHeight="true">
+      <c r="K50" s="16"/>
+      <c r="L50" s="5" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="13.5" customHeight="true">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-22</t>
+          <t xml:space="preserve">2026-06-08</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parks Family Meats</t>
+          <t xml:space="preserve">Martins</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">(no batch data)</t>
+          <t xml:space="preserve">5502428786</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">666518</t>
+          <t xml:space="preserve">666541</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -8140,1590 +8105,2728 @@
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tiss, porcine, fem, Pelvic block, intact, SM</t>
+          <t xml:space="preserve">Tiss, porcine, fem, Pelvic block, intact</t>
         </is>
       </c>
       <c r="G51" s="6" t="n">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="H51" s="6" t="n">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="I51" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J51" s="15" t="n">
         <f aca="false">IFERROR(H51/G51,0)</f>
       </c>
       <c r="K51" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 bladder hole; 2 critical-area lacerations; 2 short blocks</t>
+          <t xml:space="preserve">1 cut urethra</t>
         </is>
       </c>
       <c r="L51" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rasmin Mujanovic / Natalie</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="27.0" customHeight="true">
+          <t xml:space="preserve">Toni Cruz / Jesus</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="13.5" customHeight="true">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-25</t>
+          <t xml:space="preserve">2026-06-08</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parks Family Meats</t>
+          <t xml:space="preserve">Martins</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">(no batch data)</t>
+          <t xml:space="preserve">5502428782</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">666518</t>
+          <t xml:space="preserve">666506</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Intact</t>
+          <t xml:space="preserve">Non-intact</t>
         </is>
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tiss, porcine, fem, Pelvic block, intact, SM</t>
+          <t xml:space="preserve">Tiss, porcine, fem, Pelvic block, non-intact</t>
         </is>
       </c>
       <c r="G52" s="6" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="H52" s="6" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I52" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J52" s="15" t="n">
         <f aca="false">IFERROR(H52/G52,0)</f>
       </c>
       <c r="K52" s="16" t="inlineStr">
         <is>
+          <t xml:space="preserve">1 short block</t>
+        </is>
+      </c>
+      <c r="L52" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Toni Cruz / Jesus</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="27.0" customHeight="true">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-15</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Martins</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5502462845</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">666541</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Intact</t>
+        </is>
+      </c>
+      <c r="F53" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tiss, porcine, fem, Pelvic block, intact</t>
+        </is>
+      </c>
+      <c r="G53" s="6" t="n">
+        <v>31</v>
+      </c>
+      <c r="H53" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="I53" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J53" s="15" t="n">
+        <f aca="false">IFERROR(H53/G53,0)</f>
+      </c>
+      <c r="K53" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 damaged bowel (source had two intact tally lines: 13/12/1 + 18/18/0, combined here)</t>
+        </is>
+      </c>
+      <c r="L53" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Toni Cruz / Jesus</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="40.5" customHeight="true">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-16</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Parks Family Meats</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(no batch data)</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">666518</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Intact</t>
+        </is>
+      </c>
+      <c r="F54" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tiss, porcine, fem, Pelvic block, intact, SM</t>
+        </is>
+      </c>
+      <c r="G54" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="H54" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="I54" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J54" s="15" t="n">
+        <f aca="false">IFERROR(H54/G54,0)</f>
+      </c>
+      <c r="K54" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 bladder hole; 1 ureter damage (many blocks failed upstream from miscuts during removal — see notes)</t>
+        </is>
+      </c>
+      <c r="L54" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rasmin Mujanovic / Natalie</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="13.5" customHeight="true">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-24</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Martins</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5502462845</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">666541</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Intact</t>
+        </is>
+      </c>
+      <c r="F55" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tiss, porcine, fem, Pelvic block, intact</t>
+        </is>
+      </c>
+      <c r="G55" s="6" t="n">
+        <v>34</v>
+      </c>
+      <c r="H55" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="I55" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="J55" s="15" t="n">
+        <f aca="false">IFERROR(H55/G55,0)</f>
+      </c>
+      <c r="K55" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 damaged bladder; 3 damaged membrane</t>
+        </is>
+      </c>
+      <c r="L55" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Toni Cruz / Jesus</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="27.0" customHeight="true">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-22</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Parks Family Meats</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(no batch data)</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">666518</t>
+        </is>
+      </c>
+      <c r="E56" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Intact</t>
+        </is>
+      </c>
+      <c r="F56" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tiss, porcine, fem, Pelvic block, intact, SM</t>
+        </is>
+      </c>
+      <c r="G56" s="6" t="n">
+        <v>36</v>
+      </c>
+      <c r="H56" s="6" t="n">
+        <v>31</v>
+      </c>
+      <c r="I56" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="J56" s="15" t="n">
+        <f aca="false">IFERROR(H56/G56,0)</f>
+      </c>
+      <c r="K56" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 bladder hole; 2 critical-area lacerations; 2 short blocks</t>
+        </is>
+      </c>
+      <c r="L56" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rasmin Mujanovic / Natalie</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="27.0" customHeight="true">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-25</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Parks Family Meats</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(no batch data)</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">666518</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Intact</t>
+        </is>
+      </c>
+      <c r="F57" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tiss, porcine, fem, Pelvic block, intact, SM</t>
+        </is>
+      </c>
+      <c r="G57" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="H57" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="I57" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J57" s="15" t="n">
+        <f aca="false">IFERROR(H57/G57,0)</f>
+      </c>
+      <c r="K57" s="16" t="inlineStr">
+        <is>
           <t xml:space="preserve">1 bladder hole; 1 ureter laceration; 1 short block</t>
         </is>
       </c>
-      <c r="L52" s="5" t="inlineStr">
+      <c r="L57" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Rasmin Mujanovic / Natalie</t>
         </is>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="3" t="s">
+    <row r="58" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="13.5" customHeight="true">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-29</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Martins</t>
+        </is>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5502471460</t>
+        </is>
+      </c>
+      <c r="D58" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">666541</t>
+        </is>
+      </c>
+      <c r="E58" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Intact</t>
+        </is>
+      </c>
+      <c r="F58" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tiss, porcine, fem, Pelvic block, intact</t>
+        </is>
+      </c>
+      <c r="G58" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="H58" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="I58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" s="15" t="n">
+        <f aca="false">IFERROR(H58/G58,0)</f>
+      </c>
+      <c r="K58" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L58" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Toni Cruz / Jesus</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="13.5" customHeight="true">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-29</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Martins</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5502471457</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">666506</t>
+        </is>
+      </c>
+      <c r="E59" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non-intact</t>
+        </is>
+      </c>
+      <c r="F59" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tiss, porcine, fem, Pelvic block, non-intact</t>
+        </is>
+      </c>
+      <c r="G59" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="H59" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="I59" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" s="15" t="n">
+        <f aca="false">IFERROR(H59/G59,0)</f>
+      </c>
+      <c r="K59" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L59" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Toni Cruz / Jesus</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="54.0" customHeight="true">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-29</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Parks Family Meats</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(no batch data)</t>
+        </is>
+      </c>
+      <c r="D60" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">666518</t>
+        </is>
+      </c>
+      <c r="E60" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Intact</t>
+        </is>
+      </c>
+      <c r="F60" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tiss, porcine, fem, Pelvic block, intact, SM</t>
+        </is>
+      </c>
+      <c r="G60" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="H60" s="6" t="n">
+        <v>38</v>
+      </c>
+      <c r="I60" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="J60" s="15" t="n">
+        <f aca="false">IFERROR(H60/G60,0)</f>
+      </c>
+      <c r="K60" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 damaged during bowel cleaning (bowel blockage burst); 2 short blocks; 1 critical-area laceration; 7 urethra/bladder lacerations (cuts near template edge)</t>
+        </is>
+      </c>
+      <c r="L60" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rasmin Mujanovic / Natalie</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="13.5" customHeight="true">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-07-06</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Martins</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5502471460</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">666541</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Intact</t>
+        </is>
+      </c>
+      <c r="F61" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tiss, porcine, fem, Pelvic block, intact</t>
+        </is>
+      </c>
+      <c r="G61" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="H61" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="I61" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J61" s="15" t="n">
+        <f aca="false">IFERROR(H61/G61,0)</f>
+      </c>
+      <c r="K61" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 damaged urethra</t>
+        </is>
+      </c>
+      <c r="L61" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Toni Cruz / Jesus</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="13.5" customHeight="true">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-07-06</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Martins</t>
+        </is>
+      </c>
+      <c r="C62" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5502471457</t>
+        </is>
+      </c>
+      <c r="D62" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">666506</t>
+        </is>
+      </c>
+      <c r="E62" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non-intact</t>
+        </is>
+      </c>
+      <c r="F62" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tiss, porcine, fem, Pelvic block, non-intact</t>
+        </is>
+      </c>
+      <c r="G62" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="H62" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="I62" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J62" s="15" t="n">
+        <f aca="false">IFERROR(H62/G62,0)</f>
+      </c>
+      <c r="K62" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 membrane damage larger than 1.5"</t>
+        </is>
+      </c>
+      <c r="L62" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Toni Cruz / Jesus</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="13.5" customHeight="true">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-07-13</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Martins</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5502495107</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">666541</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Intact</t>
+        </is>
+      </c>
+      <c r="F63" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tiss, porcine, fem, Pelvic block, intact</t>
+        </is>
+      </c>
+      <c r="G63" s="6" t="n">
+        <v>38</v>
+      </c>
+      <c r="H63" s="6" t="n">
+        <v>36</v>
+      </c>
+      <c r="I63" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J63" s="15" t="n">
+        <f aca="false">IFERROR(H63/G63,0)</f>
+      </c>
+      <c r="K63" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 damaged membrane; 1 damaged bladder</t>
+        </is>
+      </c>
+      <c r="L63" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Toni Cruz / Jesus</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="13.5" customHeight="true">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-07-13</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Martins</t>
+        </is>
+      </c>
+      <c r="C64" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5502495104</t>
+        </is>
+      </c>
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">666506</t>
+        </is>
+      </c>
+      <c r="E64" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non-intact</t>
+        </is>
+      </c>
+      <c r="F64" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tiss, porcine, fem, Pelvic block, non-intact</t>
+        </is>
+      </c>
+      <c r="G64" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="H64" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="I64" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" s="15" t="n">
+        <f aca="false">IFERROR(H64/G64,0)</f>
+      </c>
+      <c r="K64" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L64" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Toni Cruz / Jesus</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="27.0" customHeight="true">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-07-13</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Parks Family Meats</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(no batch data)</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">666518</t>
+        </is>
+      </c>
+      <c r="E65" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Intact</t>
+        </is>
+      </c>
+      <c r="F65" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tiss, porcine, fem, Pelvic block, intact, SM</t>
+        </is>
+      </c>
+      <c r="G65" s="6" t="n">
+        <v>34</v>
+      </c>
+      <c r="H65" s="6" t="n">
+        <v>29</v>
+      </c>
+      <c r="I65" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="J65" s="15" t="n">
+        <f aca="false">IFERROR(H65/G65,0)</f>
+      </c>
+      <c r="K65" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 damaged during bowel cleaning (bowel blockage burst); 3 short blocks (smaller pigs)</t>
+        </is>
+      </c>
+      <c r="L65" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rasmin Mujanovic / Natalie</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A67" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="B54" s="3"/>
-      <c r="C54" s="3"/>
-      <c r="D54" s="3"/>
-      <c r="E54" s="3"/>
-      <c r="F54" s="3"/>
-      <c r="G54" s="3"/>
-      <c r="H54" s="3"/>
-      <c r="I54" s="3"/>
-      <c r="J54" s="3"/>
-      <c r="K54" s="3"/>
-      <c r="L54" s="3"/>
-    </row>
-    <row r="55" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="11" t="s">
+      <c r="B67" s="3"/>
+      <c r="C67" s="3"/>
+      <c r="D67" s="3"/>
+      <c r="E67" s="3"/>
+      <c r="F67" s="3"/>
+      <c r="G67" s="3"/>
+      <c r="H67" s="3"/>
+      <c r="I67" s="3"/>
+      <c r="J67" s="3"/>
+      <c r="K67" s="3"/>
+      <c r="L67" s="3"/>
+    </row>
+    <row r="68" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A68" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="B55" s="11" t="s">
+      <c r="B68" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="C55" s="11" t="s">
+      <c r="C68" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="D55" s="11" t="s">
+      <c r="D68" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="E55" s="11" t="s">
+      <c r="E68" s="11" t="s">
         <v>132</v>
       </c>
-      <c r="F55" s="11" t="s">
+      <c r="F68" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="G55" s="11" t="s">
+      <c r="G68" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="H55" s="11" t="s">
+      <c r="H68" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="I55" s="11" t="s">
+      <c r="I68" s="11" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="12" t="s">
+    <row r="69" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A69" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="B56" s="12" t="s">
+      <c r="B69" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="C56" s="12" t="s">
+      <c r="C69" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="D56" s="12" t="s">
+      <c r="D69" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="E56" s="12" t="s">
+      <c r="E69" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="F56" s="6" t="n">
+      <c r="F69" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="G56" s="6" t="n">
+      <c r="G69" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="H56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I56" s="15" t="n">
-        <f aca="false">IFERROR(G56/F56,0)</f>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="B57" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="C57" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="D57" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="E57" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="F57" s="6" t="n">
-        <v>65</v>
-      </c>
-      <c r="G57" s="6" t="n">
-        <v>60</v>
-      </c>
-      <c r="H57" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="I57" s="15" t="n">
-        <f aca="false">IFERROR(G57/F57,0)</f>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="B58" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="C58" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="D58" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="E58" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="F58" s="6" t="n">
-        <v>52</v>
-      </c>
-      <c r="G58" s="6" t="n">
-        <v>48</v>
-      </c>
-      <c r="H58" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="I58" s="15" t="n">
-        <f aca="false">IFERROR(G58/F58,0)</f>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="B59" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="C59" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="D59" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="E59" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="F59" s="6" t="n">
-        <v>57</v>
-      </c>
-      <c r="G59" s="6" t="n">
-        <v>56</v>
-      </c>
-      <c r="H59" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I59" s="15" t="n">
-        <f aca="false">IFERROR(G59/F59,0)</f>
-      </c>
-    </row>
-    <row r="60" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="B60" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="C60" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="D60" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="E60" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="F60" s="6" t="n">
-        <v>45</v>
-      </c>
-      <c r="G60" s="6" t="n">
-        <v>41</v>
-      </c>
-      <c r="H60" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="I60" s="15" t="n">
-        <f aca="false">IFERROR(G60/F60,0)</f>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="B61" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="C61" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="D61" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="E61" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="F61" s="6" t="n">
-        <v>62</v>
-      </c>
-      <c r="G61" s="6" t="n">
-        <v>58</v>
-      </c>
-      <c r="H61" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="I61" s="15" t="n">
-        <f aca="false">IFERROR(G61/F61,0)</f>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="B62" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="C62" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="D62" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="E62" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="F62" s="6" t="n">
-        <v>73</v>
-      </c>
-      <c r="G62" s="6" t="n">
-        <v>71</v>
-      </c>
-      <c r="H62" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="I62" s="15" t="n">
-        <f aca="false">IFERROR(G62/F62,0)</f>
-      </c>
-    </row>
-    <row r="63" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="B63" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="C63" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="D63" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="E63" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="F63" s="6" t="n">
-        <v>93</v>
-      </c>
-      <c r="G63" s="6" t="n">
-        <v>87</v>
-      </c>
-      <c r="H63" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="I63" s="15" t="n">
-        <f aca="false">IFERROR(G63/F63,0)</f>
-      </c>
-    </row>
-    <row r="64" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="B64" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="C64" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="D64" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="E64" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="F64" s="6" t="n">
-        <v>39</v>
-      </c>
-      <c r="G64" s="6" t="n">
-        <v>36</v>
-      </c>
-      <c r="H64" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="I64" s="15" t="n">
-        <f aca="false">IFERROR(G64/F64,0)</f>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A65" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="B65" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="C65" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="D65" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="E65" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="F65" s="6" t="n">
-        <v>16</v>
-      </c>
-      <c r="G65" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="H65" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="I65" s="15" t="n">
-        <f aca="false">IFERROR(G65/F65,0)</f>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="B66" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="C66" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="D66" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="E66" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="F66" s="6" t="n">
-        <v>54</v>
-      </c>
-      <c r="G66" s="6" t="n">
-        <v>52</v>
-      </c>
-      <c r="H66" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="I66" s="15" t="n">
-        <f aca="false">IFERROR(G66/F66,0)</f>
-      </c>
-    </row>
-    <row r="67" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A67" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="B67" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="C67" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="D67" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="E67" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="F67" s="6" t="n">
-        <v>36</v>
-      </c>
-      <c r="G67" s="6" t="n">
-        <v>36</v>
-      </c>
-      <c r="H67" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I67" s="15" t="n">
-        <f aca="false">IFERROR(G67/F67,0)</f>
-      </c>
-    </row>
-    <row r="68" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A68" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="B68" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="C68" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="D68" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="E68" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="F68" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="G68" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="H68" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I68" s="15" t="n">
-        <f aca="false">IFERROR(G68/F68,0)</f>
-      </c>
-    </row>
-    <row r="69" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="13.5" customHeight="true">
-      <c r="A69" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5502428786</t>
-        </is>
-      </c>
-      <c r="B69" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">666541</t>
-        </is>
-      </c>
-      <c r="C69" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Intact</t>
-        </is>
-      </c>
-      <c r="D69" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Martins</t>
-        </is>
-      </c>
-      <c r="E69" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-08</t>
-        </is>
-      </c>
-      <c r="F69" s="6" t="n">
-        <v>17</v>
-      </c>
-      <c r="G69" s="6" t="n">
-        <v>16</v>
-      </c>
       <c r="H69" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I69" s="15" t="n">
         <f aca="false">IFERROR(G69/F69,0)</f>
       </c>
     </row>
-    <row r="70" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="13.5" customHeight="true">
-      <c r="A70" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5502428782</t>
-        </is>
-      </c>
-      <c r="B70" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">666506</t>
-        </is>
-      </c>
-      <c r="C70" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Non-intact</t>
-        </is>
-      </c>
-      <c r="D70" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Martins</t>
-        </is>
-      </c>
-      <c r="E70" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-08</t>
-        </is>
+    <row r="70" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A70" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="B70" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="C70" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="D70" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="E70" s="12" t="s">
+        <v>52</v>
       </c>
       <c r="F70" s="6" t="n">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="G70" s="6" t="n">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="H70" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I70" s="15" t="n">
         <f aca="false">IFERROR(G70/F70,0)</f>
       </c>
     </row>
-    <row r="71" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="13.5" customHeight="true">
-      <c r="A71" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5502462845</t>
-        </is>
-      </c>
-      <c r="B71" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">666541</t>
-        </is>
-      </c>
-      <c r="C71" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Intact</t>
-        </is>
-      </c>
-      <c r="D71" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Martins</t>
-        </is>
-      </c>
-      <c r="E71" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-15</t>
-        </is>
+    <row r="71" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A71" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="B71" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="C71" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="D71" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="E71" s="12" t="s">
+        <v>61</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="G71" s="6" t="n">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="H71" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I71" s="15" t="n">
         <f aca="false">IFERROR(G71/F71,0)</f>
       </c>
     </row>
-    <row r="72" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="13.5" customHeight="true">
-      <c r="A72" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5502462845</t>
-        </is>
-      </c>
-      <c r="B72" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">666541</t>
-        </is>
-      </c>
-      <c r="C72" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Intact</t>
-        </is>
-      </c>
-      <c r="D72" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Martins</t>
-        </is>
-      </c>
-      <c r="E72" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-24</t>
-        </is>
+    <row r="72" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A72" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="B72" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="C72" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="D72" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="E72" s="12" t="s">
+        <v>61</v>
       </c>
       <c r="F72" s="6" t="n">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="G72" s="6" t="n">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="H72" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I72" s="15" t="n">
         <f aca="false">IFERROR(G72/F72,0)</f>
       </c>
     </row>
-    <row r="73" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="13.5" customHeight="true">
-      <c r="A73" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(no batch data)</t>
-        </is>
-      </c>
-      <c r="B73" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">666518</t>
-        </is>
-      </c>
-      <c r="C73" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Intact</t>
-        </is>
-      </c>
-      <c r="D73" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Parks Family Meats</t>
-        </is>
-      </c>
-      <c r="E73" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-16</t>
-        </is>
+    <row r="73" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A73" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="B73" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="C73" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="D73" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="E73" s="12" t="s">
+        <v>65</v>
       </c>
       <c r="F73" s="6" t="n">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="G73" s="6" t="n">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="H73" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I73" s="15" t="n">
         <f aca="false">IFERROR(G73/F73,0)</f>
       </c>
     </row>
-    <row r="74" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="13.5" customHeight="true">
-      <c r="A74" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(no batch data)</t>
-        </is>
-      </c>
-      <c r="B74" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">666518</t>
-        </is>
-      </c>
-      <c r="C74" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Intact</t>
-        </is>
-      </c>
-      <c r="D74" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Parks Family Meats</t>
-        </is>
-      </c>
-      <c r="E74" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-22</t>
-        </is>
+    <row r="74" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A74" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="B74" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="C74" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="D74" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="E74" s="12" t="s">
+        <v>65</v>
       </c>
       <c r="F74" s="6" t="n">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="G74" s="6" t="n">
-        <v>31</v>
+        <v>58</v>
       </c>
       <c r="H74" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I74" s="15" t="n">
         <f aca="false">IFERROR(G74/F74,0)</f>
       </c>
     </row>
-    <row r="75" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="13.5" customHeight="true">
-      <c r="A75" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(no batch data)</t>
-        </is>
-      </c>
-      <c r="B75" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">666518</t>
-        </is>
-      </c>
-      <c r="C75" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Intact</t>
-        </is>
-      </c>
-      <c r="D75" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Parks Family Meats</t>
-        </is>
-      </c>
-      <c r="E75" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-25</t>
-        </is>
+    <row r="75" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A75" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="B75" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="C75" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="D75" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="E75" s="12" t="s">
+        <v>69</v>
       </c>
       <c r="F75" s="6" t="n">
-        <v>19</v>
+        <v>73</v>
       </c>
       <c r="G75" s="6" t="n">
-        <v>16</v>
+        <v>71</v>
       </c>
       <c r="H75" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I75" s="15" t="n">
         <f aca="false">IFERROR(G75/F75,0)</f>
       </c>
     </row>
     <row r="76" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A76" s="17" t="s">
+      <c r="A76" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="B76" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="C76" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="D76" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="E76" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="F76" s="6" t="n">
+        <v>93</v>
+      </c>
+      <c r="G76" s="6" t="n">
+        <v>87</v>
+      </c>
+      <c r="H76" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="I76" s="15" t="n">
+        <f aca="false">IFERROR(G76/F76,0)</f>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A77" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="B77" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="C77" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="D77" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="E77" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="F77" s="6" t="n">
+        <v>39</v>
+      </c>
+      <c r="G77" s="6" t="n">
+        <v>36</v>
+      </c>
+      <c r="H77" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I77" s="15" t="n">
+        <f aca="false">IFERROR(G77/F77,0)</f>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A78" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="B78" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="C78" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="D78" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="E78" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="F78" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="G78" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="H78" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="I78" s="15" t="n">
+        <f aca="false">IFERROR(G78/F78,0)</f>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A79" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="B79" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="C79" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="D79" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="E79" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="F79" s="6" t="n">
+        <v>54</v>
+      </c>
+      <c r="G79" s="6" t="n">
+        <v>52</v>
+      </c>
+      <c r="H79" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I79" s="15" t="n">
+        <f aca="false">IFERROR(G79/F79,0)</f>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A80" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="B80" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="C80" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="D80" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="E80" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="F80" s="6" t="n">
+        <v>36</v>
+      </c>
+      <c r="G80" s="6" t="n">
+        <v>36</v>
+      </c>
+      <c r="H80" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I80" s="15" t="n">
+        <f aca="false">IFERROR(G80/F80,0)</f>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A81" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="B81" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="C81" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="D81" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="E81" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="F81" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="G81" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="H81" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I81" s="15" t="n">
+        <f aca="false">IFERROR(G81/F81,0)</f>
+      </c>
+    </row>
+    <row r="82" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="13.5" customHeight="true">
+      <c r="A82" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5502428786</t>
+        </is>
+      </c>
+      <c r="B82" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">666541</t>
+        </is>
+      </c>
+      <c r="C82" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Intact</t>
+        </is>
+      </c>
+      <c r="D82" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Martins</t>
+        </is>
+      </c>
+      <c r="E82" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-08</t>
+        </is>
+      </c>
+      <c r="F82" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="G82" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="H82" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I82" s="15" t="n">
+        <f aca="false">IFERROR(G82/F82,0)</f>
+      </c>
+    </row>
+    <row r="83" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="13.5" customHeight="true">
+      <c r="A83" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5502428782</t>
+        </is>
+      </c>
+      <c r="B83" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">666506</t>
+        </is>
+      </c>
+      <c r="C83" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non-intact</t>
+        </is>
+      </c>
+      <c r="D83" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Martins</t>
+        </is>
+      </c>
+      <c r="E83" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-08</t>
+        </is>
+      </c>
+      <c r="F83" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="G83" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="H83" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I83" s="15" t="n">
+        <f aca="false">IFERROR(G83/F83,0)</f>
+      </c>
+    </row>
+    <row r="84" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="13.5" customHeight="true">
+      <c r="A84" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5502462845</t>
+        </is>
+      </c>
+      <c r="B84" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">666541</t>
+        </is>
+      </c>
+      <c r="C84" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Intact</t>
+        </is>
+      </c>
+      <c r="D84" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Martins</t>
+        </is>
+      </c>
+      <c r="E84" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-15</t>
+        </is>
+      </c>
+      <c r="F84" s="6" t="n">
+        <v>31</v>
+      </c>
+      <c r="G84" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="H84" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I84" s="15" t="n">
+        <f aca="false">IFERROR(G84/F84,0)</f>
+      </c>
+    </row>
+    <row r="85" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="13.5" customHeight="true">
+      <c r="A85" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5502462845</t>
+        </is>
+      </c>
+      <c r="B85" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">666541</t>
+        </is>
+      </c>
+      <c r="C85" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Intact</t>
+        </is>
+      </c>
+      <c r="D85" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Martins</t>
+        </is>
+      </c>
+      <c r="E85" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-24</t>
+        </is>
+      </c>
+      <c r="F85" s="6" t="n">
+        <v>34</v>
+      </c>
+      <c r="G85" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="H85" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="I85" s="15" t="n">
+        <f aca="false">IFERROR(G85/F85,0)</f>
+      </c>
+    </row>
+    <row r="86" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="13.5" customHeight="true">
+      <c r="A86" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(no batch data)</t>
+        </is>
+      </c>
+      <c r="B86" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">666518</t>
+        </is>
+      </c>
+      <c r="C86" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Intact</t>
+        </is>
+      </c>
+      <c r="D86" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Parks Family Meats</t>
+        </is>
+      </c>
+      <c r="E86" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-16</t>
+        </is>
+      </c>
+      <c r="F86" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="G86" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="H86" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I86" s="15" t="n">
+        <f aca="false">IFERROR(G86/F86,0)</f>
+      </c>
+    </row>
+    <row r="87" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="13.5" customHeight="true">
+      <c r="A87" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(no batch data)</t>
+        </is>
+      </c>
+      <c r="B87" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">666518</t>
+        </is>
+      </c>
+      <c r="C87" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Intact</t>
+        </is>
+      </c>
+      <c r="D87" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Parks Family Meats</t>
+        </is>
+      </c>
+      <c r="E87" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-22</t>
+        </is>
+      </c>
+      <c r="F87" s="6" t="n">
+        <v>36</v>
+      </c>
+      <c r="G87" s="6" t="n">
+        <v>31</v>
+      </c>
+      <c r="H87" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="I87" s="15" t="n">
+        <f aca="false">IFERROR(G87/F87,0)</f>
+      </c>
+    </row>
+    <row r="88" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="13.5" customHeight="true">
+      <c r="A88" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(no batch data)</t>
+        </is>
+      </c>
+      <c r="B88" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">666518</t>
+        </is>
+      </c>
+      <c r="C88" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Intact</t>
+        </is>
+      </c>
+      <c r="D88" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Parks Family Meats</t>
+        </is>
+      </c>
+      <c r="E88" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-25</t>
+        </is>
+      </c>
+      <c r="F88" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="G88" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="H88" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I88" s="15" t="n">
+        <f aca="false">IFERROR(G88/F88,0)</f>
+      </c>
+    </row>
+    <row r="89" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="13.5" customHeight="true">
+      <c r="A89" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5502471460</t>
+        </is>
+      </c>
+      <c r="B89" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">666541</t>
+        </is>
+      </c>
+      <c r="C89" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Intact</t>
+        </is>
+      </c>
+      <c r="D89" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Martins</t>
+        </is>
+      </c>
+      <c r="E89" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-29</t>
+        </is>
+      </c>
+      <c r="F89" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="G89" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="H89" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" s="15" t="n">
+        <f aca="false">IFERROR(G89/F89,0)</f>
+      </c>
+    </row>
+    <row r="90" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="13.5" customHeight="true">
+      <c r="A90" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5502471457</t>
+        </is>
+      </c>
+      <c r="B90" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">666506</t>
+        </is>
+      </c>
+      <c r="C90" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non-intact</t>
+        </is>
+      </c>
+      <c r="D90" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Martins</t>
+        </is>
+      </c>
+      <c r="E90" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-29</t>
+        </is>
+      </c>
+      <c r="F90" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="G90" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="H90" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" s="15" t="n">
+        <f aca="false">IFERROR(G90/F90,0)</f>
+      </c>
+    </row>
+    <row r="91" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="13.5" customHeight="true">
+      <c r="A91" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(no batch data)</t>
+        </is>
+      </c>
+      <c r="B91" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">666518</t>
+        </is>
+      </c>
+      <c r="C91" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Intact</t>
+        </is>
+      </c>
+      <c r="D91" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Parks Family Meats</t>
+        </is>
+      </c>
+      <c r="E91" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-29</t>
+        </is>
+      </c>
+      <c r="F91" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="G91" s="6" t="n">
+        <v>38</v>
+      </c>
+      <c r="H91" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I91" s="15" t="n">
+        <f aca="false">IFERROR(G91/F91,0)</f>
+      </c>
+    </row>
+    <row r="92" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="13.5" customHeight="true">
+      <c r="A92" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5502471460</t>
+        </is>
+      </c>
+      <c r="B92" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">666541</t>
+        </is>
+      </c>
+      <c r="C92" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Intact</t>
+        </is>
+      </c>
+      <c r="D92" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Martins</t>
+        </is>
+      </c>
+      <c r="E92" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-07-06</t>
+        </is>
+      </c>
+      <c r="F92" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="G92" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="H92" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I92" s="15" t="n">
+        <f aca="false">IFERROR(G92/F92,0)</f>
+      </c>
+    </row>
+    <row r="93" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="13.5" customHeight="true">
+      <c r="A93" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5502471457</t>
+        </is>
+      </c>
+      <c r="B93" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">666506</t>
+        </is>
+      </c>
+      <c r="C93" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non-intact</t>
+        </is>
+      </c>
+      <c r="D93" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Martins</t>
+        </is>
+      </c>
+      <c r="E93" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-07-06</t>
+        </is>
+      </c>
+      <c r="F93" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G93" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H93" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I93" s="15" t="n">
+        <f aca="false">IFERROR(G93/F93,0)</f>
+      </c>
+    </row>
+    <row r="94" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="13.5" customHeight="true">
+      <c r="A94" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5502495107</t>
+        </is>
+      </c>
+      <c r="B94" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">666541</t>
+        </is>
+      </c>
+      <c r="C94" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Intact</t>
+        </is>
+      </c>
+      <c r="D94" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Martins</t>
+        </is>
+      </c>
+      <c r="E94" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-07-13</t>
+        </is>
+      </c>
+      <c r="F94" s="6" t="n">
+        <v>38</v>
+      </c>
+      <c r="G94" s="6" t="n">
+        <v>36</v>
+      </c>
+      <c r="H94" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I94" s="15" t="n">
+        <f aca="false">IFERROR(G94/F94,0)</f>
+      </c>
+    </row>
+    <row r="95" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="13.5" customHeight="true">
+      <c r="A95" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5502495104</t>
+        </is>
+      </c>
+      <c r="B95" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">666506</t>
+        </is>
+      </c>
+      <c r="C95" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non-intact</t>
+        </is>
+      </c>
+      <c r="D95" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Martins</t>
+        </is>
+      </c>
+      <c r="E95" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-07-13</t>
+        </is>
+      </c>
+      <c r="F95" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="G95" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="H95" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" s="15" t="n">
+        <f aca="false">IFERROR(G95/F95,0)</f>
+      </c>
+    </row>
+    <row r="96" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="13.5" customHeight="true">
+      <c r="A96" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(no batch data)</t>
+        </is>
+      </c>
+      <c r="B96" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">666518</t>
+        </is>
+      </c>
+      <c r="C96" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Intact</t>
+        </is>
+      </c>
+      <c r="D96" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Parks Family Meats</t>
+        </is>
+      </c>
+      <c r="E96" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-07-13</t>
+        </is>
+      </c>
+      <c r="F96" s="6" t="n">
+        <v>34</v>
+      </c>
+      <c r="G96" s="6" t="n">
+        <v>29</v>
+      </c>
+      <c r="H96" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="I96" s="15" t="n">
+        <f aca="false">IFERROR(G96/F96,0)</f>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A97" s="17" t="s">
         <v>133</v>
       </c>
-      <c r="B76" s="17"/>
-      <c r="C76" s="17"/>
-      <c r="D76" s="17"/>
-      <c r="E76" s="17"/>
-      <c r="F76" s="8" t="n">
-        <f aca="false">SUM(F56:F75)</f>
-      </c>
-      <c r="G76" s="8" t="n">
-        <f aca="false">SUM(G56:G75)</f>
-      </c>
-      <c r="H76" s="8" t="n">
-        <f aca="false">SUM(H56:H75)</f>
-      </c>
-      <c r="I76" s="9" t="n">
-        <f aca="false">IFERROR(G76/F76,0)</f>
-      </c>
-    </row>
-    <row r="78" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A78" s="10" t="s">
+      <c r="B97" s="17"/>
+      <c r="C97" s="17"/>
+      <c r="D97" s="17"/>
+      <c r="E97" s="17"/>
+      <c r="F97" s="8" t="n">
+        <f aca="false">SUM(F69:F96)</f>
+      </c>
+      <c r="G97" s="8" t="n">
+        <f aca="false">SUM(G69:G96)</f>
+      </c>
+      <c r="H97" s="8" t="n">
+        <f aca="false">SUM(H69:H96)</f>
+      </c>
+      <c r="I97" s="9" t="n">
+        <f aca="false">IFERROR(G97/F97,0)</f>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A99" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="B78" s="10"/>
-      <c r="C78" s="10"/>
-      <c r="D78" s="10"/>
-      <c r="E78" s="10"/>
-      <c r="F78" s="10"/>
-      <c r="G78" s="10"/>
-      <c r="H78" s="10"/>
-      <c r="I78" s="10"/>
-      <c r="J78" s="10"/>
-      <c r="K78" s="10"/>
-      <c r="L78" s="10"/>
-    </row>
-    <row r="79" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A79" s="11" t="s">
+      <c r="B99" s="10"/>
+      <c r="C99" s="10"/>
+      <c r="D99" s="10"/>
+      <c r="E99" s="10"/>
+      <c r="F99" s="10"/>
+      <c r="G99" s="10"/>
+      <c r="H99" s="10"/>
+      <c r="I99" s="10"/>
+      <c r="J99" s="10"/>
+      <c r="K99" s="10"/>
+      <c r="L99" s="10"/>
+    </row>
+    <row r="100" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A100" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="B79" s="11" t="s">
+      <c r="B100" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="C79" s="11" t="s">
+      <c r="C100" s="11" t="s">
         <v>135</v>
       </c>
-      <c r="D79" s="11" t="s">
+      <c r="D100" s="11" t="s">
         <v>136</v>
       </c>
-      <c r="E79" s="11" t="s">
+      <c r="E100" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="F79" s="11" t="s">
+      <c r="F100" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="G79" s="11" t="s">
+      <c r="G100" s="11" t="s">
         <v>139</v>
       </c>
-      <c r="H79" s="11" t="s">
+      <c r="H100" s="11" t="s">
         <v>140</v>
       </c>
-      <c r="I79" s="11" t="s">
+      <c r="I100" s="11" t="s">
         <v>141</v>
       </c>
-      <c r="J79" s="11" t="s">
+      <c r="J100" s="11" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A80" s="18" t="s">
+    <row r="101" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A101" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="B80" s="18" t="s">
+      <c r="B101" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="C80" s="6" t="n">
+      <c r="C101" s="6" t="n">
         <v>65</v>
       </c>
-      <c r="D80" s="6" t="n">
+      <c r="D101" s="6" t="n">
         <v>60</v>
       </c>
-      <c r="E80" s="15" t="n">
-        <f aca="false">IFERROR(D80/C80,0)</f>
-      </c>
-      <c r="F80" s="6" t="n">
-        <f aca="false">SUMIFS('Receipt Summary'!F:F,'Receipt Summary'!E:E,A80)</f>
-      </c>
-      <c r="G80" s="6" t="n">
-        <f aca="false">SUMIFS('Receipt Summary'!G:G,'Receipt Summary'!E:E,A80)</f>
-      </c>
-      <c r="H80" s="15" t="n">
-        <f aca="false">IFERROR(G80/F80,0)</f>
-      </c>
-      <c r="I80" s="6" t="n">
-        <f aca="false">D80-F80</f>
-      </c>
-      <c r="J80" s="16" t="s">
+      <c r="E101" s="15" t="n">
+        <f aca="false">IFERROR(D101/C101,0)</f>
+      </c>
+      <c r="F101" s="6" t="n">
+        <f aca="false">SUMIFS('Receipt Summary'!F:F,'Receipt Summary'!E:E,A101)</f>
+      </c>
+      <c r="G101" s="6" t="n">
+        <f aca="false">SUMIFS('Receipt Summary'!G:G,'Receipt Summary'!E:E,A101)</f>
+      </c>
+      <c r="H101" s="15" t="n">
+        <f aca="false">IFERROR(G101/F101,0)</f>
+      </c>
+      <c r="I101" s="6" t="n">
+        <f aca="false">D101-F101</f>
+      </c>
+      <c r="J101" s="16" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A81" s="18" t="s">
+    <row r="102" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A102" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="B81" s="18" t="s">
+      <c r="B102" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="C81" s="6" t="n">
+      <c r="C102" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="D81" s="6" t="n">
+      <c r="D102" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="E81" s="15" t="n">
-        <f aca="false">IFERROR(D81/C81,0)</f>
-      </c>
-      <c r="F81" s="6" t="n">
-        <f aca="false">SUMIFS('Receipt Summary'!F:F,'Receipt Summary'!E:E,A81)</f>
-      </c>
-      <c r="G81" s="6" t="n">
-        <f aca="false">SUMIFS('Receipt Summary'!G:G,'Receipt Summary'!E:E,A81)</f>
-      </c>
-      <c r="H81" s="15" t="n">
-        <f aca="false">IFERROR(G81/F81,0)</f>
-      </c>
-      <c r="I81" s="6" t="n">
-        <f aca="false">D81-F81</f>
-      </c>
-      <c r="J81" s="16" t="s">
+      <c r="E102" s="15" t="n">
+        <f aca="false">IFERROR(D102/C102,0)</f>
+      </c>
+      <c r="F102" s="6" t="n">
+        <f aca="false">SUMIFS('Receipt Summary'!F:F,'Receipt Summary'!E:E,A102)</f>
+      </c>
+      <c r="G102" s="6" t="n">
+        <f aca="false">SUMIFS('Receipt Summary'!G:G,'Receipt Summary'!E:E,A102)</f>
+      </c>
+      <c r="H102" s="15" t="n">
+        <f aca="false">IFERROR(G102/F102,0)</f>
+      </c>
+      <c r="I102" s="6" t="n">
+        <f aca="false">D102-F102</f>
+      </c>
+      <c r="J102" s="16" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="82" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A82" s="18" t="s">
+    <row r="103" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A103" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="B82" s="18" t="s">
+      <c r="B103" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="C82" s="6" t="n">
+      <c r="C103" s="6" t="n">
         <v>57</v>
       </c>
-      <c r="D82" s="6" t="n">
+      <c r="D103" s="6" t="n">
         <v>56</v>
       </c>
-      <c r="E82" s="15" t="n">
-        <f aca="false">IFERROR(D82/C82,0)</f>
-      </c>
-      <c r="F82" s="6" t="n">
-        <f aca="false">SUMIFS('Receipt Summary'!F:F,'Receipt Summary'!E:E,A82)</f>
-      </c>
-      <c r="G82" s="6" t="n">
-        <f aca="false">SUMIFS('Receipt Summary'!G:G,'Receipt Summary'!E:E,A82)</f>
-      </c>
-      <c r="H82" s="15" t="n">
-        <f aca="false">IFERROR(G82/F82,0)</f>
-      </c>
-      <c r="I82" s="6" t="n">
-        <f aca="false">D82-F82</f>
-      </c>
-      <c r="J82" s="16" t="s">
+      <c r="E103" s="15" t="n">
+        <f aca="false">IFERROR(D103/C103,0)</f>
+      </c>
+      <c r="F103" s="6" t="n">
+        <f aca="false">SUMIFS('Receipt Summary'!F:F,'Receipt Summary'!E:E,A103)</f>
+      </c>
+      <c r="G103" s="6" t="n">
+        <f aca="false">SUMIFS('Receipt Summary'!G:G,'Receipt Summary'!E:E,A103)</f>
+      </c>
+      <c r="H103" s="15" t="n">
+        <f aca="false">IFERROR(G103/F103,0)</f>
+      </c>
+      <c r="I103" s="6" t="n">
+        <f aca="false">D103-F103</f>
+      </c>
+      <c r="J103" s="16" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A83" s="18" t="s">
+    <row r="104" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A104" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="B83" s="18" t="s">
+      <c r="B104" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="C83" s="6" t="n">
+      <c r="C104" s="6" t="n">
         <v>52</v>
       </c>
-      <c r="D83" s="6" t="n">
+      <c r="D104" s="6" t="n">
         <v>48</v>
       </c>
-      <c r="E83" s="15" t="n">
-        <f aca="false">IFERROR(D83/C83,0)</f>
-      </c>
-      <c r="F83" s="6" t="n">
-        <f aca="false">SUMIFS('Receipt Summary'!F:F,'Receipt Summary'!E:E,A83)</f>
-      </c>
-      <c r="G83" s="6" t="n">
-        <f aca="false">SUMIFS('Receipt Summary'!G:G,'Receipt Summary'!E:E,A83)</f>
-      </c>
-      <c r="H83" s="15" t="n">
-        <f aca="false">IFERROR(G83/F83,0)</f>
-      </c>
-      <c r="I83" s="6" t="n">
-        <f aca="false">D83-F83</f>
-      </c>
-      <c r="J83" s="16" t="s">
+      <c r="E104" s="15" t="n">
+        <f aca="false">IFERROR(D104/C104,0)</f>
+      </c>
+      <c r="F104" s="6" t="n">
+        <f aca="false">SUMIFS('Receipt Summary'!F:F,'Receipt Summary'!E:E,A104)</f>
+      </c>
+      <c r="G104" s="6" t="n">
+        <f aca="false">SUMIFS('Receipt Summary'!G:G,'Receipt Summary'!E:E,A104)</f>
+      </c>
+      <c r="H104" s="15" t="n">
+        <f aca="false">IFERROR(G104/F104,0)</f>
+      </c>
+      <c r="I104" s="6" t="n">
+        <f aca="false">D104-F104</f>
+      </c>
+      <c r="J104" s="16" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="84" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A84" s="18" t="s">
+    <row r="105" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A105" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="B84" s="18" t="s">
+      <c r="B105" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="C84" s="6" t="n">
+      <c r="C105" s="6" t="n">
         <v>62</v>
       </c>
-      <c r="D84" s="6" t="n">
+      <c r="D105" s="6" t="n">
         <v>58</v>
       </c>
-      <c r="E84" s="15" t="n">
-        <f aca="false">IFERROR(D84/C84,0)</f>
-      </c>
-      <c r="F84" s="6" t="n">
-        <f aca="false">SUMIFS('Receipt Summary'!F:F,'Receipt Summary'!E:E,A84)</f>
-      </c>
-      <c r="G84" s="6" t="n">
-        <f aca="false">SUMIFS('Receipt Summary'!G:G,'Receipt Summary'!E:E,A84)</f>
-      </c>
-      <c r="H84" s="15" t="n">
-        <f aca="false">IFERROR(G84/F84,0)</f>
-      </c>
-      <c r="I84" s="6" t="n">
-        <f aca="false">D84-F84</f>
-      </c>
-      <c r="J84" s="16" t="s">
+      <c r="E105" s="15" t="n">
+        <f aca="false">IFERROR(D105/C105,0)</f>
+      </c>
+      <c r="F105" s="6" t="n">
+        <f aca="false">SUMIFS('Receipt Summary'!F:F,'Receipt Summary'!E:E,A105)</f>
+      </c>
+      <c r="G105" s="6" t="n">
+        <f aca="false">SUMIFS('Receipt Summary'!G:G,'Receipt Summary'!E:E,A105)</f>
+      </c>
+      <c r="H105" s="15" t="n">
+        <f aca="false">IFERROR(G105/F105,0)</f>
+      </c>
+      <c r="I105" s="6" t="n">
+        <f aca="false">D105-F105</f>
+      </c>
+      <c r="J105" s="16" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="85" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A85" s="18" t="s">
+    <row r="106" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A106" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="B85" s="18" t="s">
+      <c r="B106" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="C85" s="6" t="n">
+      <c r="C106" s="6" t="n">
         <v>45</v>
       </c>
-      <c r="D85" s="6" t="n">
+      <c r="D106" s="6" t="n">
         <v>41</v>
       </c>
-      <c r="E85" s="15" t="n">
-        <f aca="false">IFERROR(D85/C85,0)</f>
-      </c>
-      <c r="F85" s="6" t="n">
-        <f aca="false">SUMIFS('Receipt Summary'!F:F,'Receipt Summary'!E:E,A85)</f>
-      </c>
-      <c r="G85" s="6" t="n">
-        <f aca="false">SUMIFS('Receipt Summary'!G:G,'Receipt Summary'!E:E,A85)</f>
-      </c>
-      <c r="H85" s="15" t="n">
-        <f aca="false">IFERROR(G85/F85,0)</f>
-      </c>
-      <c r="I85" s="6" t="n">
-        <f aca="false">D85-F85</f>
-      </c>
-      <c r="J85" s="16" t="s">
+      <c r="E106" s="15" t="n">
+        <f aca="false">IFERROR(D106/C106,0)</f>
+      </c>
+      <c r="F106" s="6" t="n">
+        <f aca="false">SUMIFS('Receipt Summary'!F:F,'Receipt Summary'!E:E,A106)</f>
+      </c>
+      <c r="G106" s="6" t="n">
+        <f aca="false">SUMIFS('Receipt Summary'!G:G,'Receipt Summary'!E:E,A106)</f>
+      </c>
+      <c r="H106" s="15" t="n">
+        <f aca="false">IFERROR(G106/F106,0)</f>
+      </c>
+      <c r="I106" s="6" t="n">
+        <f aca="false">D106-F106</f>
+      </c>
+      <c r="J106" s="16" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="86" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A86" s="18" t="s">
+    <row r="107" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A107" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="B86" s="18" t="s">
+      <c r="B107" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="C86" s="6" t="n">
+      <c r="C107" s="6" t="n">
         <v>93</v>
       </c>
-      <c r="D86" s="6" t="n">
+      <c r="D107" s="6" t="n">
         <v>87</v>
       </c>
-      <c r="E86" s="15" t="n">
-        <f aca="false">IFERROR(D86/C86,0)</f>
-      </c>
-      <c r="F86" s="6" t="n">
-        <f aca="false">SUMIFS('Receipt Summary'!F:F,'Receipt Summary'!E:E,A86)</f>
-      </c>
-      <c r="G86" s="6" t="n">
-        <f aca="false">SUMIFS('Receipt Summary'!G:G,'Receipt Summary'!E:E,A86)</f>
-      </c>
-      <c r="H86" s="15" t="n">
-        <f aca="false">IFERROR(G86/F86,0)</f>
-      </c>
-      <c r="I86" s="6" t="n">
-        <f aca="false">D86-F86</f>
-      </c>
-      <c r="J86" s="16" t="s">
+      <c r="E107" s="15" t="n">
+        <f aca="false">IFERROR(D107/C107,0)</f>
+      </c>
+      <c r="F107" s="6" t="n">
+        <f aca="false">SUMIFS('Receipt Summary'!F:F,'Receipt Summary'!E:E,A107)</f>
+      </c>
+      <c r="G107" s="6" t="n">
+        <f aca="false">SUMIFS('Receipt Summary'!G:G,'Receipt Summary'!E:E,A107)</f>
+      </c>
+      <c r="H107" s="15" t="n">
+        <f aca="false">IFERROR(G107/F107,0)</f>
+      </c>
+      <c r="I107" s="6" t="n">
+        <f aca="false">D107-F107</f>
+      </c>
+      <c r="J107" s="16" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="87" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A87" s="18" t="s">
+    <row r="108" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A108" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="B87" s="18" t="s">
+      <c r="B108" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="C87" s="6" t="n">
+      <c r="C108" s="6" t="n">
         <v>73</v>
       </c>
-      <c r="D87" s="6" t="n">
+      <c r="D108" s="6" t="n">
         <v>71</v>
       </c>
-      <c r="E87" s="15" t="n">
-        <f aca="false">IFERROR(D87/C87,0)</f>
-      </c>
-      <c r="F87" s="6" t="n">
-        <f aca="false">SUMIFS('Receipt Summary'!F:F,'Receipt Summary'!E:E,A87)</f>
-      </c>
-      <c r="G87" s="6" t="n">
-        <f aca="false">SUMIFS('Receipt Summary'!G:G,'Receipt Summary'!E:E,A87)</f>
-      </c>
-      <c r="H87" s="15" t="n">
-        <f aca="false">IFERROR(G87/F87,0)</f>
-      </c>
-      <c r="I87" s="6" t="n">
-        <f aca="false">D87-F87</f>
-      </c>
-      <c r="J87" s="16" t="s">
+      <c r="E108" s="15" t="n">
+        <f aca="false">IFERROR(D108/C108,0)</f>
+      </c>
+      <c r="F108" s="6" t="n">
+        <f aca="false">SUMIFS('Receipt Summary'!F:F,'Receipt Summary'!E:E,A108)</f>
+      </c>
+      <c r="G108" s="6" t="n">
+        <f aca="false">SUMIFS('Receipt Summary'!G:G,'Receipt Summary'!E:E,A108)</f>
+      </c>
+      <c r="H108" s="15" t="n">
+        <f aca="false">IFERROR(G108/F108,0)</f>
+      </c>
+      <c r="I108" s="6" t="n">
+        <f aca="false">D108-F108</f>
+      </c>
+      <c r="J108" s="16" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="88" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A88" s="18" t="s">
+    <row r="109" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A109" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="B88" s="18" t="s">
+      <c r="B109" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="C88" s="6" t="n">
+      <c r="C109" s="6" t="n">
         <v>54</v>
       </c>
-      <c r="D88" s="6" t="n">
+      <c r="D109" s="6" t="n">
         <v>52</v>
       </c>
-      <c r="E88" s="15" t="n">
-        <f aca="false">IFERROR(D88/C88,0)</f>
-      </c>
-      <c r="F88" s="6" t="n">
-        <f aca="false">SUMIFS('Receipt Summary'!F:F,'Receipt Summary'!E:E,A88)</f>
-      </c>
-      <c r="G88" s="6" t="n">
-        <f aca="false">SUMIFS('Receipt Summary'!G:G,'Receipt Summary'!E:E,A88)</f>
-      </c>
-      <c r="H88" s="15" t="n">
-        <f aca="false">IFERROR(G88/F88,0)</f>
-      </c>
-      <c r="I88" s="6" t="n">
-        <f aca="false">D88-F88</f>
-      </c>
-      <c r="J88" s="16" t="s">
+      <c r="E109" s="15" t="n">
+        <f aca="false">IFERROR(D109/C109,0)</f>
+      </c>
+      <c r="F109" s="6" t="n">
+        <f aca="false">SUMIFS('Receipt Summary'!F:F,'Receipt Summary'!E:E,A109)</f>
+      </c>
+      <c r="G109" s="6" t="n">
+        <f aca="false">SUMIFS('Receipt Summary'!G:G,'Receipt Summary'!E:E,A109)</f>
+      </c>
+      <c r="H109" s="15" t="n">
+        <f aca="false">IFERROR(G109/F109,0)</f>
+      </c>
+      <c r="I109" s="6" t="n">
+        <f aca="false">D109-F109</f>
+      </c>
+      <c r="J109" s="16" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="89" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A89" s="18" t="s">
+    <row r="110" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A110" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="B89" s="18" t="s">
+      <c r="B110" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="C89" s="6" t="n">
+      <c r="C110" s="6" t="n">
         <v>36</v>
       </c>
-      <c r="D89" s="6" t="n">
+      <c r="D110" s="6" t="n">
         <v>36</v>
       </c>
-      <c r="E89" s="15" t="n">
-        <f aca="false">IFERROR(D89/C89,0)</f>
-      </c>
-      <c r="F89" s="6" t="n">
-        <f aca="false">SUMIFS('Receipt Summary'!F:F,'Receipt Summary'!E:E,A89)</f>
-      </c>
-      <c r="G89" s="6" t="n">
-        <f aca="false">SUMIFS('Receipt Summary'!G:G,'Receipt Summary'!E:E,A89)</f>
-      </c>
-      <c r="H89" s="15" t="n">
-        <f aca="false">IFERROR(G89/F89,0)</f>
-      </c>
-      <c r="I89" s="6" t="n">
-        <f aca="false">D89-F89</f>
-      </c>
-      <c r="J89" s="16" t="s">
+      <c r="E110" s="15" t="n">
+        <f aca="false">IFERROR(D110/C110,0)</f>
+      </c>
+      <c r="F110" s="6" t="n">
+        <f aca="false">SUMIFS('Receipt Summary'!F:F,'Receipt Summary'!E:E,A110)</f>
+      </c>
+      <c r="G110" s="6" t="n">
+        <f aca="false">SUMIFS('Receipt Summary'!G:G,'Receipt Summary'!E:E,A110)</f>
+      </c>
+      <c r="H110" s="15" t="n">
+        <f aca="false">IFERROR(G110/F110,0)</f>
+      </c>
+      <c r="I110" s="6" t="n">
+        <f aca="false">D110-F110</f>
+      </c>
+      <c r="J110" s="16" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="90" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="72.0" customHeight="true">
-      <c r="A90" s="18" t="inlineStr">
+    <row r="111" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="72.0" customHeight="true">
+      <c r="A111" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">5502462845</t>
         </is>
       </c>
-      <c r="B90" s="18" t="inlineStr">
+      <c r="B111" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">666541</t>
         </is>
       </c>
-      <c r="C90" s="6" t="n">
+      <c r="C111" s="6" t="n">
         <v>31</v>
       </c>
-      <c r="D90" s="6" t="n">
+      <c r="D111" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="E90" s="15" t="n">
-        <f aca="false">IFERROR(D90/C90,0)</f>
-      </c>
-      <c r="F90" s="6" t="n">
-        <f aca="false">SUMIFS('Receipt Summary'!F:F,'Receipt Summary'!E:E,A90)</f>
-      </c>
-      <c r="G90" s="6" t="n">
-        <f aca="false">SUMIFS('Receipt Summary'!G:G,'Receipt Summary'!E:E,A90)</f>
-      </c>
-      <c r="H90" s="15" t="n">
-        <f aca="false">IFERROR(G90/F90,0)</f>
-      </c>
-      <c r="I90" s="6" t="n">
-        <f aca="false">D90-F90</f>
-      </c>
-      <c r="J90" s="16" t="inlineStr">
+      <c r="E111" s="15" t="n">
+        <f aca="false">IFERROR(D111/C111,0)</f>
+      </c>
+      <c r="F111" s="6" t="n">
+        <f aca="false">SUMIFS('Receipt Summary'!F:F,'Receipt Summary'!E:E,A111)</f>
+      </c>
+      <c r="G111" s="6" t="n">
+        <f aca="false">SUMIFS('Receipt Summary'!G:G,'Receipt Summary'!E:E,A111)</f>
+      </c>
+      <c r="H111" s="15" t="n">
+        <f aca="false">IFERROR(G111/F111,0)</f>
+      </c>
+      <c r="I111" s="6" t="n">
+        <f aca="false">D111-F111</f>
+      </c>
+      <c r="J111" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">Newly harvested 06/15. SH sampled 31 intact, passed 30 (96.8%). Lot # reappears on the 06/24 tally (34 inspected / 30 passed) — recorded as a separate Visit 12, likely a tally-sheet lot carry-over (see notes). Not yet at ATM; expected in coming weeks.</t>
         </is>
       </c>
     </row>
-    <row r="92" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A92" s="3" t="s">
+    <row r="112" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="72.0" customHeight="true">
+      <c r="A112" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5502471460</t>
+        </is>
+      </c>
+      <c r="B112" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">666541</t>
+        </is>
+      </c>
+      <c r="C112" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="D112" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="E112" s="15" t="n">
+        <f aca="false">IFERROR(D112/C112,0)</f>
+      </c>
+      <c r="F112" s="6" t="n">
+        <f aca="false">SUMIFS('Receipt Summary'!F:F,'Receipt Summary'!E:E,A112)</f>
+      </c>
+      <c r="G112" s="6" t="n">
+        <f aca="false">SUMIFS('Receipt Summary'!G:G,'Receipt Summary'!E:E,A112)</f>
+      </c>
+      <c r="H112" s="15" t="n">
+        <f aca="false">IFERROR(G112/F112,0)</f>
+      </c>
+      <c r="I112" s="6" t="n">
+        <f aca="false">D112-F112</f>
+      </c>
+      <c r="J112" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Newly harvested 06/29. SH sampled 16 intact, all passed (100%). Lot # reused on the 07/06 tally (12 inspected / 11 passed) — recorded as a separate Visit 17, likely a tally-sheet lot carry-over. Not yet at ATM; expected in coming weeks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="72.0" customHeight="true">
+      <c r="A113" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5502495107</t>
+        </is>
+      </c>
+      <c r="B113" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">666541</t>
+        </is>
+      </c>
+      <c r="C113" s="6" t="n">
+        <v>38</v>
+      </c>
+      <c r="D113" s="6" t="n">
+        <v>36</v>
+      </c>
+      <c r="E113" s="15" t="n">
+        <f aca="false">IFERROR(D113/C113,0)</f>
+      </c>
+      <c r="F113" s="6" t="n">
+        <f aca="false">SUMIFS('Receipt Summary'!F:F,'Receipt Summary'!E:E,A113)</f>
+      </c>
+      <c r="G113" s="6" t="n">
+        <f aca="false">SUMIFS('Receipt Summary'!G:G,'Receipt Summary'!E:E,A113)</f>
+      </c>
+      <c r="H113" s="15" t="n">
+        <f aca="false">IFERROR(G113/F113,0)</f>
+      </c>
+      <c r="I113" s="6" t="n">
+        <f aca="false">D113-F113</f>
+      </c>
+      <c r="J113" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Newly harvested 07/13. SH sampled 38 intact, passed 36 (94.7%). Not yet at ATM; expected in coming weeks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A115" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="B92" s="3"/>
-      <c r="C92" s="3"/>
-      <c r="D92" s="3"/>
-      <c r="E92" s="3"/>
-      <c r="F92" s="3"/>
-      <c r="G92" s="3"/>
-      <c r="H92" s="3"/>
-      <c r="I92" s="3"/>
-      <c r="J92" s="3"/>
-      <c r="K92" s="3"/>
-      <c r="L92" s="3"/>
-    </row>
-    <row r="93" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A93" s="19" t="s">
+      <c r="B115" s="3"/>
+      <c r="C115" s="3"/>
+      <c r="D115" s="3"/>
+      <c r="E115" s="3"/>
+      <c r="F115" s="3"/>
+      <c r="G115" s="3"/>
+      <c r="H115" s="3"/>
+      <c r="I115" s="3"/>
+      <c r="J115" s="3"/>
+      <c r="K115" s="3"/>
+      <c r="L115" s="3"/>
+    </row>
+    <row r="116" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A116" s="19" t="s">
         <v>152</v>
       </c>
-      <c r="B93" s="20" t="s">
+      <c r="B116" s="20" t="s">
         <v>153</v>
       </c>
-      <c r="C93" s="20"/>
-      <c r="D93" s="20"/>
-      <c r="E93" s="20"/>
-      <c r="F93" s="20"/>
-      <c r="G93" s="20"/>
-      <c r="H93" s="20"/>
-      <c r="I93" s="20"/>
-      <c r="J93" s="20"/>
-      <c r="K93" s="20"/>
-      <c r="L93" s="20"/>
-    </row>
-    <row r="94" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A94" s="19" t="s">
+      <c r="C116" s="20"/>
+      <c r="D116" s="20"/>
+      <c r="E116" s="20"/>
+      <c r="F116" s="20"/>
+      <c r="G116" s="20"/>
+      <c r="H116" s="20"/>
+      <c r="I116" s="20"/>
+      <c r="J116" s="20"/>
+      <c r="K116" s="20"/>
+      <c r="L116" s="20"/>
+    </row>
+    <row r="117" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A117" s="19" t="s">
         <v>154</v>
       </c>
-      <c r="B94" s="20" t="s">
+      <c r="B117" s="20" t="s">
         <v>155</v>
       </c>
-      <c r="C94" s="20"/>
-      <c r="D94" s="20"/>
-      <c r="E94" s="20"/>
-      <c r="F94" s="20"/>
-      <c r="G94" s="20"/>
-      <c r="H94" s="20"/>
-      <c r="I94" s="20"/>
-      <c r="J94" s="20"/>
-      <c r="K94" s="20"/>
-      <c r="L94" s="20"/>
-    </row>
-    <row r="95" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A95" s="19" t="s">
+      <c r="C117" s="20"/>
+      <c r="D117" s="20"/>
+      <c r="E117" s="20"/>
+      <c r="F117" s="20"/>
+      <c r="G117" s="20"/>
+      <c r="H117" s="20"/>
+      <c r="I117" s="20"/>
+      <c r="J117" s="20"/>
+      <c r="K117" s="20"/>
+      <c r="L117" s="20"/>
+    </row>
+    <row r="118" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A118" s="19" t="s">
         <v>156</v>
       </c>
-      <c r="B95" s="20" t="s">
+      <c r="B118" s="20" t="s">
         <v>157</v>
       </c>
-      <c r="C95" s="20"/>
-      <c r="D95" s="20"/>
-      <c r="E95" s="20"/>
-      <c r="F95" s="20"/>
-      <c r="G95" s="20"/>
-      <c r="H95" s="20"/>
-      <c r="I95" s="20"/>
-      <c r="J95" s="20"/>
-      <c r="K95" s="20"/>
-      <c r="L95" s="20"/>
-    </row>
-    <row r="96" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A96" s="19" t="s">
+      <c r="C118" s="20"/>
+      <c r="D118" s="20"/>
+      <c r="E118" s="20"/>
+      <c r="F118" s="20"/>
+      <c r="G118" s="20"/>
+      <c r="H118" s="20"/>
+      <c r="I118" s="20"/>
+      <c r="J118" s="20"/>
+      <c r="K118" s="20"/>
+      <c r="L118" s="20"/>
+    </row>
+    <row r="119" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A119" s="19" t="s">
         <v>158</v>
       </c>
-      <c r="B96" s="20" t="s">
+      <c r="B119" s="20" t="s">
         <v>159</v>
       </c>
-      <c r="C96" s="20"/>
-      <c r="D96" s="20"/>
-      <c r="E96" s="20"/>
-      <c r="F96" s="20"/>
-      <c r="G96" s="20"/>
-      <c r="H96" s="20"/>
-      <c r="I96" s="20"/>
-      <c r="J96" s="20"/>
-      <c r="K96" s="20"/>
-      <c r="L96" s="20"/>
-    </row>
-    <row r="97" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A97" s="19" t="s">
+      <c r="C119" s="20"/>
+      <c r="D119" s="20"/>
+      <c r="E119" s="20"/>
+      <c r="F119" s="20"/>
+      <c r="G119" s="20"/>
+      <c r="H119" s="20"/>
+      <c r="I119" s="20"/>
+      <c r="J119" s="20"/>
+      <c r="K119" s="20"/>
+      <c r="L119" s="20"/>
+    </row>
+    <row r="120" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A120" s="19" t="s">
         <v>160</v>
       </c>
-      <c r="B97" s="20" t="s">
+      <c r="B120" s="20" t="s">
         <v>161</v>
       </c>
-      <c r="C97" s="20"/>
-      <c r="D97" s="20"/>
-      <c r="E97" s="20"/>
-      <c r="F97" s="20"/>
-      <c r="G97" s="20"/>
-      <c r="H97" s="20"/>
-      <c r="I97" s="20"/>
-      <c r="J97" s="20"/>
-      <c r="K97" s="20"/>
-      <c r="L97" s="20"/>
-    </row>
-    <row r="98" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A98" s="19" t="s">
+      <c r="C120" s="20"/>
+      <c r="D120" s="20"/>
+      <c r="E120" s="20"/>
+      <c r="F120" s="20"/>
+      <c r="G120" s="20"/>
+      <c r="H120" s="20"/>
+      <c r="I120" s="20"/>
+      <c r="J120" s="20"/>
+      <c r="K120" s="20"/>
+      <c r="L120" s="20"/>
+    </row>
+    <row r="121" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A121" s="19" t="s">
         <v>162</v>
       </c>
-      <c r="B98" s="20" t="s">
+      <c r="B121" s="20" t="s">
         <v>163</v>
       </c>
-      <c r="C98" s="20"/>
-      <c r="D98" s="20"/>
-      <c r="E98" s="20"/>
-      <c r="F98" s="20"/>
-      <c r="G98" s="20"/>
-      <c r="H98" s="20"/>
-      <c r="I98" s="20"/>
-      <c r="J98" s="20"/>
-      <c r="K98" s="20"/>
-      <c r="L98" s="20"/>
-    </row>
-    <row r="99" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A99" s="19" t="s">
+      <c r="C121" s="20"/>
+      <c r="D121" s="20"/>
+      <c r="E121" s="20"/>
+      <c r="F121" s="20"/>
+      <c r="G121" s="20"/>
+      <c r="H121" s="20"/>
+      <c r="I121" s="20"/>
+      <c r="J121" s="20"/>
+      <c r="K121" s="20"/>
+      <c r="L121" s="20"/>
+    </row>
+    <row r="122" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A122" s="19" t="s">
         <v>164</v>
       </c>
-      <c r="B99" s="20" t="s">
+      <c r="B122" s="20" t="s">
         <v>165</v>
       </c>
-      <c r="C99" s="20"/>
-      <c r="D99" s="20"/>
-      <c r="E99" s="20"/>
-      <c r="F99" s="20"/>
-      <c r="G99" s="20"/>
-      <c r="H99" s="20"/>
-      <c r="I99" s="20"/>
-      <c r="J99" s="20"/>
-      <c r="K99" s="20"/>
-      <c r="L99" s="20"/>
-    </row>
-    <row r="100" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A100" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="B100" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fourteen inspection visits so far. Nine at Martins (Visits 1–5, 7, 9, 10, 12) and five at Parks (Visits 6, 8, 11, 13, 14). To extend, append new visit metadata, raw-data rows, and rollup rows; the TOTAL and SH→ATM sections then need refreshing.</t>
-        </is>
-      </c>
-      <c r="C100" s="20"/>
-      <c r="D100" s="20"/>
-      <c r="E100" s="20"/>
-      <c r="F100" s="20"/>
-      <c r="G100" s="20"/>
-      <c r="H100" s="20"/>
-      <c r="I100" s="20"/>
-      <c r="J100" s="20"/>
-      <c r="K100" s="20"/>
-      <c r="L100" s="20"/>
-    </row>
-    <row r="101" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A101" s="19" t="s">
+      <c r="C122" s="20"/>
+      <c r="D122" s="20"/>
+      <c r="E122" s="20"/>
+      <c r="F122" s="20"/>
+      <c r="G122" s="20"/>
+      <c r="H122" s="20"/>
+      <c r="I122" s="20"/>
+      <c r="J122" s="20"/>
+      <c r="K122" s="20"/>
+      <c r="L122" s="20"/>
+    </row>
+    <row r="123" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A123" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8. Nineteen inspection visits so far</t>
+        </is>
+      </c>
+      <c r="B123" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nineteen inspection visits so far. Twelve at Martins (Visits 1–5, 7, 9, 10, 12, 15, 17, 18) and seven at Parks (Visits 6, 8, 11, 13, 14, 16, 19). To extend, append new visit metadata, raw-data rows, and rollup rows; the TOTAL and SH→ATM sections then need refreshing.</t>
+        </is>
+      </c>
+      <c r="C123" s="20"/>
+      <c r="D123" s="20"/>
+      <c r="E123" s="20"/>
+      <c r="F123" s="20"/>
+      <c r="G123" s="20"/>
+      <c r="H123" s="20"/>
+      <c r="I123" s="20"/>
+      <c r="J123" s="20"/>
+      <c r="K123" s="20"/>
+      <c r="L123" s="20"/>
+    </row>
+    <row r="124" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A124" s="19" t="s">
         <v>168</v>
       </c>
-      <c r="B101" s="20" t="s">
+      <c r="B124" s="20" t="s">
         <v>169</v>
       </c>
-      <c r="C101" s="20"/>
-      <c r="D101" s="20"/>
-      <c r="E101" s="20"/>
-      <c r="F101" s="20"/>
-      <c r="G101" s="20"/>
-      <c r="H101" s="20"/>
-      <c r="I101" s="20"/>
-      <c r="J101" s="20"/>
-      <c r="K101" s="20"/>
-      <c r="L101" s="20"/>
-    </row>
-    <row r="102" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A102" s="19" t="s">
+      <c r="C124" s="20"/>
+      <c r="D124" s="20"/>
+      <c r="E124" s="20"/>
+      <c r="F124" s="20"/>
+      <c r="G124" s="20"/>
+      <c r="H124" s="20"/>
+      <c r="I124" s="20"/>
+      <c r="J124" s="20"/>
+      <c r="K124" s="20"/>
+      <c r="L124" s="20"/>
+    </row>
+    <row r="125" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A125" s="19" t="s">
         <v>170</v>
       </c>
-      <c r="B102" s="20" t="s">
+      <c r="B125" s="20" t="s">
         <v>171</v>
       </c>
-      <c r="C102" s="20"/>
-      <c r="D102" s="20"/>
-      <c r="E102" s="20"/>
-      <c r="F102" s="20"/>
-      <c r="G102" s="20"/>
-      <c r="H102" s="20"/>
-      <c r="I102" s="20"/>
-      <c r="J102" s="20"/>
-      <c r="K102" s="20"/>
-      <c r="L102" s="20"/>
-    </row>
-    <row r="103" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A103" s="19" t="s">
+      <c r="C125" s="20"/>
+      <c r="D125" s="20"/>
+      <c r="E125" s="20"/>
+      <c r="F125" s="20"/>
+      <c r="G125" s="20"/>
+      <c r="H125" s="20"/>
+      <c r="I125" s="20"/>
+      <c r="J125" s="20"/>
+      <c r="K125" s="20"/>
+      <c r="L125" s="20"/>
+    </row>
+    <row r="126" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A126" s="19" t="s">
         <v>172</v>
       </c>
-      <c r="B103" s="20" t="s">
+      <c r="B126" s="20" t="s">
         <v>173</v>
       </c>
-      <c r="C103" s="20"/>
-      <c r="D103" s="20"/>
-      <c r="E103" s="20"/>
-      <c r="F103" s="20"/>
-      <c r="G103" s="20"/>
-      <c r="H103" s="20"/>
-      <c r="I103" s="20"/>
-      <c r="J103" s="20"/>
-      <c r="K103" s="20"/>
-      <c r="L103" s="20"/>
-    </row>
-    <row r="104" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A104" s="19" t="s">
+      <c r="C126" s="20"/>
+      <c r="D126" s="20"/>
+      <c r="E126" s="20"/>
+      <c r="F126" s="20"/>
+      <c r="G126" s="20"/>
+      <c r="H126" s="20"/>
+      <c r="I126" s="20"/>
+      <c r="J126" s="20"/>
+      <c r="K126" s="20"/>
+      <c r="L126" s="20"/>
+    </row>
+    <row r="127" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A127" s="19" t="s">
         <v>174</v>
       </c>
-      <c r="B104" s="20" t="s">
+      <c r="B127" s="20" t="s">
         <v>175</v>
       </c>
-      <c r="C104" s="20"/>
-      <c r="D104" s="20"/>
-      <c r="E104" s="20"/>
-      <c r="F104" s="20"/>
-      <c r="G104" s="20"/>
-      <c r="H104" s="20"/>
-      <c r="I104" s="20"/>
-      <c r="J104" s="20"/>
-      <c r="K104" s="20"/>
-      <c r="L104" s="20"/>
-    </row>
-    <row r="105" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="48.0" customHeight="true">
-      <c r="A105" s="19" t="inlineStr">
+      <c r="C127" s="20"/>
+      <c r="D127" s="20"/>
+      <c r="E127" s="20"/>
+      <c r="F127" s="20"/>
+      <c r="G127" s="20"/>
+      <c r="H127" s="20"/>
+      <c r="I127" s="20"/>
+      <c r="J127" s="20"/>
+      <c r="K127" s="20"/>
+      <c r="L127" s="20"/>
+    </row>
+    <row r="128" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="48.0" customHeight="true">
+      <c r="A128" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">13. New visits 9–12 (06/08–06/24)</t>
         </is>
       </c>
-      <c r="B105" s="20" t="inlineStr">
+      <c r="B128" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">Visit 9 = 06/08 Martins; Visit 10 = 06/15 Martins; Visit 11 = 06/16 Parks (intact-only); Visit 12 = 06/24 Martins (intact-only). Source date/kill fields on several incoming sheets are volatile =NOW() captures (e.g. the Parks sheet sent 06/17 reads 06/16); the hand-entered harvest-date fields were used as the authoritative visit dates.</t>
         </is>
       </c>
-      <c r="C105" s="20"/>
-      <c r="D105" s="20"/>
-      <c r="E105" s="20"/>
-      <c r="F105" s="20"/>
-      <c r="G105" s="20"/>
-      <c r="H105" s="20"/>
-      <c r="I105" s="20"/>
-      <c r="J105" s="20"/>
-      <c r="K105" s="20"/>
-      <c r="L105" s="20"/>
-    </row>
-    <row r="106" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="48.0" customHeight="true">
-      <c r="A106" s="19" t="inlineStr">
+      <c r="C128" s="20"/>
+      <c r="D128" s="20"/>
+      <c r="E128" s="20"/>
+      <c r="F128" s="20"/>
+      <c r="G128" s="20"/>
+      <c r="H128" s="20"/>
+      <c r="I128" s="20"/>
+      <c r="J128" s="20"/>
+      <c r="K128" s="20"/>
+      <c r="L128" s="20"/>
+    </row>
+    <row r="129" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="48.0" customHeight="true">
+      <c r="A129" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">14. Lot-number carry-over recurs (Visits 9 &amp; 12)</t>
         </is>
       </c>
-      <c r="B106" s="20" t="inlineStr">
+      <c r="B129" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">Visit 9 (06/08) reuses Visit 7’s lots 5502428786/5502428782, and Visit 12 (06/24) reuses Visit 10’s intact lot 5502462845 — the same template carry-over pattern documented in note 9 for lot 5502421192. Each is recorded as its own visit with its own raw and rollup rows, but per the note-9 precedent only the FIRST occurrence of each lot is reconciled in the SH→ATM section, so the reused-lot inspections do not generate duplicate SH→ATM rows.</t>
         </is>
       </c>
-      <c r="C106" s="20"/>
-      <c r="D106" s="20"/>
-      <c r="E106" s="20"/>
-      <c r="F106" s="20"/>
-      <c r="G106" s="20"/>
-      <c r="H106" s="20"/>
-      <c r="I106" s="20"/>
-      <c r="J106" s="20"/>
-      <c r="K106" s="20"/>
-      <c r="L106" s="20"/>
-    </row>
-    <row r="107" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="48.0" customHeight="true">
-      <c r="A107" s="19" t="inlineStr">
+      <c r="C129" s="20"/>
+      <c r="D129" s="20"/>
+      <c r="E129" s="20"/>
+      <c r="F129" s="20"/>
+      <c r="G129" s="20"/>
+      <c r="H129" s="20"/>
+      <c r="I129" s="20"/>
+      <c r="J129" s="20"/>
+      <c r="K129" s="20"/>
+      <c r="L129" s="20"/>
+    </row>
+    <row r="130" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="48.0" customHeight="true">
+      <c r="A130" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">15. Visit 10 (06/15) — two intact tally lines combined; no non-intact</t>
         </is>
       </c>
-      <c r="B107" s="20" t="inlineStr">
+      <c r="B130" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">The source recorded two intact 666541 lines on 06/15 (13/12/1 and 18/18/0); they share date, lot and condition, so they are combined into a single raw row (31/30/1). No non-intact units were collected (the SH had met its non-intact quota and run low on labels), so lot 5502462842 appears in the metadata but has no raw/rollup row.</t>
         </is>
       </c>
-      <c r="C107" s="20"/>
-      <c r="D107" s="20"/>
-      <c r="E107" s="20"/>
-      <c r="F107" s="20"/>
-      <c r="G107" s="20"/>
-      <c r="H107" s="20"/>
-      <c r="I107" s="20"/>
-      <c r="J107" s="20"/>
-      <c r="K107" s="20"/>
-      <c r="L107" s="20"/>
-    </row>
-    <row r="108" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="48.0" customHeight="true">
-      <c r="A108" s="19" t="inlineStr">
+      <c r="C130" s="20"/>
+      <c r="D130" s="20"/>
+      <c r="E130" s="20"/>
+      <c r="F130" s="20"/>
+      <c r="G130" s="20"/>
+      <c r="H130" s="20"/>
+      <c r="I130" s="20"/>
+      <c r="J130" s="20"/>
+      <c r="K130" s="20"/>
+      <c r="L130" s="20"/>
+    </row>
+    <row r="131" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="48.0" customHeight="true">
+      <c r="A131" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">16. Visit 11 (06/16 Parks) — heavy upstream miscut losses</t>
         </is>
       </c>
-      <c r="B108" s="20" t="inlineStr">
+      <c r="B131" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">The inspector noted ~100 pigs slaughtered, with the majority of blocks failing BEFORE reaching IQC due to miscuts during block removal. Of the 16 that reached inspection, 14 passed (1 bladder hole, 1 ureter damage). That upstream loss is a Parks harvest-technique signal not captured in the pass/fail counts here. PN normalized 668518 → 666518 per note 10. Separately, the “PARKS0603” sheet (internal date 06/02, 7/7 intact, no batch) is the SAME inspection already recorded as Visit 8 and was not re-added.</t>
         </is>
       </c>
-      <c r="C108" s="20"/>
-      <c r="D108" s="20"/>
-      <c r="E108" s="20"/>
-      <c r="F108" s="20"/>
-      <c r="G108" s="20"/>
-      <c r="H108" s="20"/>
-      <c r="I108" s="20"/>
-      <c r="J108" s="20"/>
-      <c r="K108" s="20"/>
-      <c r="L108" s="20"/>
-    </row>
-    <row r="109" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="48.0" customHeight="true">
-      <c r="A109" s="19" t="inlineStr">
+      <c r="C131" s="20"/>
+      <c r="D131" s="20"/>
+      <c r="E131" s="20"/>
+      <c r="F131" s="20"/>
+      <c r="G131" s="20"/>
+      <c r="H131" s="20"/>
+      <c r="I131" s="20"/>
+      <c r="J131" s="20"/>
+      <c r="K131" s="20"/>
+      <c r="L131" s="20"/>
+    </row>
+    <row r="132" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="48.0" customHeight="true">
+      <c r="A132" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">17. New Parks visits 13 (06/22) &amp; 14 (06/25)</t>
         </is>
       </c>
-      <c r="B109" s="20" t="inlineStr">
+      <c r="B132" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">Two more intact-only Parks inspections (no batch data; PN normalized 668518 → 666518). Visit 13 (06/22) = 36 inspected / 31 pass / 5 fail (1 bladder hole, 2 critical-area lacerations, 2 short blocks); Visit 14 (06/25) = 19 inspected / 16 pass / 3 fail (1 bladder hole, 1 ureter laceration, 1 short block). Both were received after Visit 12, so Visit 13’s harvest date (06/22) precedes Visit 12’s (06/24 Martins) — visit numbers reflect processing order, as with the existing Visit 7/8 overlap. No batch on either, so neither has an SH→ATM link (consistent with Visits 6, 8 and 11). Short blocks and critical-zone mesentery damage continue to dominate Parks scrap.</t>
         </is>
       </c>
-      <c r="C109" s="20"/>
-      <c r="D109" s="20"/>
-      <c r="E109" s="20"/>
-      <c r="F109" s="20"/>
-      <c r="G109" s="20"/>
-      <c r="H109" s="20"/>
-      <c r="I109" s="20"/>
-      <c r="J109" s="20"/>
-      <c r="K109" s="20"/>
-      <c r="L109" s="20"/>
-      <c r="C109" s="20"/>
-      <c r="D109" s="20"/>
-      <c r="E109" s="20"/>
-      <c r="F109" s="20"/>
-      <c r="G109" s="20"/>
-      <c r="H109" s="20"/>
-      <c r="I109" s="20"/>
-      <c r="J109" s="20"/>
-      <c r="K109" s="20"/>
-      <c r="L109" s="20"/>
+      <c r="C132" s="20"/>
+      <c r="D132" s="20"/>
+      <c r="E132" s="20"/>
+      <c r="F132" s="20"/>
+      <c r="G132" s="20"/>
+      <c r="H132" s="20"/>
+      <c r="I132" s="20"/>
+      <c r="J132" s="20"/>
+      <c r="K132" s="20"/>
+      <c r="L132" s="20"/>
+      <c r="C132" s="20"/>
+      <c r="D132" s="20"/>
+      <c r="E132" s="20"/>
+      <c r="F132" s="20"/>
+      <c r="G132" s="20"/>
+      <c r="H132" s="20"/>
+      <c r="I132" s="20"/>
+      <c r="J132" s="20"/>
+      <c r="K132" s="20"/>
+      <c r="L132" s="20"/>
+    </row>
+    <row r="133" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="48.0" customHeight="true">
+      <c r="A133" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18. New visits 15–19 (06/29–07/13); two Parks fail-count corrections</t>
+        </is>
+      </c>
+      <c r="B133" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Visit 15 = 06/29 Martins; Visit 16 = 06/29 Parks; Visit 17 = 07/06 Martins; Visit 18 = 07/13 Martins; Visit 19 = 07/13 Parks. DATA-ACCURACY FIX: on both Parks sheets the source “# Fail” cell undercounted because blocks damaged during bowel-cleaning were written in the notes but not added to the fail tally. Corrected to inspected − pass, which matches the scrap breakdown — Visit 16 (06/29) = 50/38/12 (source cell read 10; 2 cleaning-damage + 2 short + 1 critical + 7 urethra/bladder = 12); Visit 19 (07/13) = 34/29/5 (source cell read 3; 2 cleaning-damage + 3 short = 5). Visit 17 (07/06) reuses Visit 15’s lots 5502471460/5502471457 — a tally-sheet carry-over recorded as a separate visit (see note 9). Visit 18’s inspector field was blank on the source; recorded as Toni Cruz, the standing Martins inspector.</t>
+        </is>
+      </c>
+      <c r="C133" s="20"/>
+      <c r="D133" s="20"/>
+      <c r="E133" s="20"/>
+      <c r="F133" s="20"/>
+      <c r="G133" s="20"/>
+      <c r="H133" s="20"/>
+      <c r="I133" s="20"/>
+      <c r="J133" s="20"/>
+      <c r="K133" s="20"/>
+      <c r="L133" s="20"/>
+    </row>
+    <row r="134" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="48.0" customHeight="true">
+      <c r="A134" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19. Visit 19 (Parks) harvest-date ambiguity</t>
+        </is>
+      </c>
+      <c r="B134" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The source file is named “PARKS_0713” (→ 07/13), was sent as a most-recent inspection, and a Martins 07/13 sheet arrived in the same batch — so Visit 19 is recorded as harvest 07/13/2026. However, all three internal date fields on that sheet (Date, Kill, Harvest) read 06/13/2026, likely a month typo. If 06/13 was intended, flip Visit 19’s date; the counts (34/29/5) are unaffected either way.</t>
+        </is>
+      </c>
+      <c r="C134" s="20"/>
+      <c r="D134" s="20"/>
+      <c r="E134" s="20"/>
+      <c r="F134" s="20"/>
+      <c r="G134" s="20"/>
+      <c r="H134" s="20"/>
+      <c r="I134" s="20"/>
+      <c r="J134" s="20"/>
+      <c r="K134" s="20"/>
+      <c r="L134" s="20"/>
     </row>
   </sheetData>
-  <mergeCells count="24">
+  <mergeCells count="26">
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A2:L2"/>
     <mergeCell ref="A4:L4"/>
-    <mergeCell ref="A21:L21"/>
-    <mergeCell ref="A54:L54"/>
-    <mergeCell ref="A78:L78"/>
-    <mergeCell ref="A92:L92"/>
-    <mergeCell ref="B93:L93"/>
-    <mergeCell ref="B94:L94"/>
-    <mergeCell ref="B95:L95"/>
-    <mergeCell ref="B96:L96"/>
-    <mergeCell ref="B97:L97"/>
-    <mergeCell ref="B98:L98"/>
-    <mergeCell ref="B99:L99"/>
-    <mergeCell ref="B100:L100"/>
-    <mergeCell ref="B101:L101"/>
-    <mergeCell ref="B102:L102"/>
-    <mergeCell ref="B103:L103"/>
-    <mergeCell ref="B104:L104"/>
-    <mergeCell ref="B105:L105"/>
-    <mergeCell ref="B106:L106"/>
-    <mergeCell ref="B107:L107"/>
-    <mergeCell ref="B108:L108"/>
-    <mergeCell ref="B109:L109"/>
+    <mergeCell ref="A26:L26"/>
+    <mergeCell ref="A67:L67"/>
+    <mergeCell ref="A99:L99"/>
+    <mergeCell ref="A115:L115"/>
+    <mergeCell ref="B116:L116"/>
+    <mergeCell ref="B117:L117"/>
+    <mergeCell ref="B118:L118"/>
+    <mergeCell ref="B119:L119"/>
+    <mergeCell ref="B120:L120"/>
+    <mergeCell ref="B121:L121"/>
+    <mergeCell ref="B122:L122"/>
+    <mergeCell ref="B123:L123"/>
+    <mergeCell ref="B124:L124"/>
+    <mergeCell ref="B125:L125"/>
+    <mergeCell ref="B126:L126"/>
+    <mergeCell ref="B127:L127"/>
+    <mergeCell ref="B128:L128"/>
+    <mergeCell ref="B129:L129"/>
+    <mergeCell ref="B130:L130"/>
+    <mergeCell ref="B131:L131"/>
+    <mergeCell ref="B132:L132"/>
+    <mergeCell ref="B133:L133"/>
+    <mergeCell ref="B134:L134"/>
   </mergeCells>
-  <conditionalFormatting sqref="J23:J52">
+  <conditionalFormatting sqref="J28:J65">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="num" val="0.7"/>
@@ -9735,7 +10838,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I56:I75">
+  <conditionalFormatting sqref="I69:I96">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="num" val="0.7"/>
@@ -9747,7 +10850,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E80:E90">
+  <conditionalFormatting sqref="E101:E113">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="num" val="0.7"/>
@@ -9759,7 +10862,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H80:H90">
+  <conditionalFormatting sqref="H101:H113">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="num" val="0.7"/>

--- a/QC inspections suppliers/Pelvic_Blocks_Quality_062626.xlsx
+++ b/QC inspections suppliers/Pelvic_Blocks_Quality_062626.xlsx
@@ -11,6 +11,7 @@
     <sheet name="Defect Trends- ATM" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="Slaughterhouse IQC" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="SmartAssessment" sheetId="12" state="visible" r:id="rId15"/>
+    <sheet name="ATM_Scrap_TableuData" sheetId="13" state="visible" r:id="rId16"/>
     <sheet name="Receipt Summary" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="Master Data" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="Defect Pivot 666541-F" sheetId="5" state="visible" r:id="rId7"/>
@@ -6312,6 +6313,473 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F36"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="4" max="4" width="34" customWidth="1"/>
+    <col min="5" max="6" width="12" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="true">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ATM Scrap — Tableau Data (post-freeze / thaw)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="60" customHeight="true">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Source: Tableau “Top 5 Part” scrap views, June 2026. ATM = receipt inspection AFTER freeze/thaw (product sits frozen ~1–1.5 months), so this month reflects SH harvest from roughly late-April to late-May. No batch/lot numbers in the ATM feed, so cross-stage links are by time-window + part only. Values read from the two charts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4" ht="18" customHeight="true">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WEEKLY SCRAP % TREND — JUNE 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Week (ATM receipt)</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">666541 Scrap %</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">666506 Scrap %</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Goal</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5/25</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D6" s="15" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6/1</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="n">
+        <v>0.063</v>
+      </c>
+      <c r="C7" s="15" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="D7" s="15" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6/8</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="C8" s="15" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="D8" s="15" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6/15</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="C9" s="15" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="D9" s="15" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6/22</t>
+        </is>
+      </c>
+      <c r="B10" s="15" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="C10" s="15" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="D10" s="15" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6/29</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="C11" s="15" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="D11" s="15" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="12"/>
+    <row r="13" ht="18" customHeight="true">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OVERALL SCRAP % BY PART — JUNE 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Part</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Description</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">June Scrap %</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vs 5% Goal</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">666541</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DV Tech Pelvic Block (F), intact — performance-goal part</t>
+        </is>
+      </c>
+      <c r="C15" s="15" t="n">
+        <v>0.046</v>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Under (0.4 pt below goal)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">666506</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pelvic Block, non-intact — tighter spec</t>
+        </is>
+      </c>
+      <c r="C16" s="15" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Under</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18" ht="18" customHeight="true">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STAGE-TO-STAGE LAG CORRELATION  (ATM week  ←  SH harvest ~4–6 weeks earlier)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="44" customHeight="true">
+      <c r="A19" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Directional only: ATM is weekly, SH visits are sporadic, and there is no lot linkage. SH 666541 scrap below is from the Martins intact rows on the Slaughterhouse IQC tab for the matching harvest window.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ATM week</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ATM 666541 scrap</t>
+        </is>
+      </c>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SH harvest window</t>
+        </is>
+      </c>
+      <c r="D20" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SH 666541 scrap (Martins)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5/25</t>
+        </is>
+      </c>
+      <c r="B21" s="15" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">~4/13–4/22</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.9% blended — 4/15 visit spiked to 23.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6/1</t>
+        </is>
+      </c>
+      <c r="B22" s="15" t="n">
+        <v>0.063</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">~4/20–4/29</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.8% (4/22)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6/8</t>
+        </is>
+      </c>
+      <c r="B23" s="15" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">~4/27–5/6</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6.5% (5/4 + 5/6; 5/6 = 12.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6/15</t>
+        </is>
+      </c>
+      <c r="B24" s="15" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">~5/4–5/13</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6.5% (5/6 = 12.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6/22</t>
+        </is>
+      </c>
+      <c r="B25" s="15" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">~5/11–5/20</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6.5% (5/18)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6/29</t>
+        </is>
+      </c>
+      <c r="B26" s="15" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">~5/18–5/27</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6.8% (5/18–5/27)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27"/>
+    <row r="28" ht="18" customHeight="true">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KEY TAKEAWAYS</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="44" customHeight="true">
+      <c r="A29" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">• 666541 (the performance-goal part) fell 25% → 0% across June and finished the month at 4.6% overall — just under the 5% goal. One early spike (25% on the 5/25 receipt) drove most of the month; it is the part to watch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="44" customHeight="true">
+      <c r="A30" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">• 666506 (tighter spec) held ~0% all month (0.4% overall) — well controlled through freeze/thaw.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="44" customHeight="true">
+      <c r="A31" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">• Lag alignment: the 25% ATM spike (5/25) lands ~5–6 weeks after the roughest SH visit (4/15, 23.5% scrap) — consistent with the ~1–1.5-month freeze dwell and with defects originating upstream at harvest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="44" customHeight="true">
+      <c r="A32" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">• Both parts trend down into summer, matching the harvesting-training improvements at the slaughterhouses.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33"/>
+    <row r="34" ht="18" customHeight="true">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NOTES &amp; ASSUMPTIONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="56" customHeight="true">
+      <c r="A35" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Line→part mapping (dark = 666541, light = 666506) inferred from the overall-by-part chart. Lag band = 4–6 weeks (≈1–1.5-month freeze dwell). These June charts are Martins parts; Parks 666518 is not in this top-5 view.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="56" customHeight="true">
+      <c r="A36" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Original Tableau screenshots are not embedded here — the image files were not available to paste. Drop the two screenshots beside these tables if you want the visuals inline. Refresh monthly as new Tableau months arrive.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="B6:C11 C15:C16 B21:B26">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0.05"/>
+        <cfvo type="num" val="0.1"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <mergeCells count="14">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="A28:F28"/>
+    <mergeCell ref="A29:F29"/>
+    <mergeCell ref="A30:F30"/>
+    <mergeCell ref="A31:F31"/>
+    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="A34:F34"/>
+    <mergeCell ref="A35:F35"/>
+    <mergeCell ref="A36:F36"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="false">

--- a/QC inspections suppliers/Pelvic_Blocks_Quality_062626.xlsx
+++ b/QC inspections suppliers/Pelvic_Blocks_Quality_062626.xlsx
@@ -3695,6 +3695,439 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <c:style val="2"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="en-US" sz="1400" b="1"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="1"/>
+              <a:t>ATM Scrap % Trend — June 2026 (666541 vs 666506)</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'ATM_Scrap_TableuData'!$B$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>666541 Scrap %</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28800">
+              <a:solidFill>
+                <a:srgbClr val="4FB8CC"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="6"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="4FB8CC"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:numFmt formatCode="0.0%" sourceLinked="0"/>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900"/>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="t"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'ATM_Scrap_TableuData'!$A$6:$A$11</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>5/25</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6/1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6/8</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6/15</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6/22</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6/29</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'ATM_Scrap_TableuData'!$B$6:$B$11</c:f>
+              <c:numCache>
+                <c:formatCode>0.0%</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.063</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.074</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.032</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.032</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'ATM_Scrap_TableuData'!$C$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>666506 Scrap %</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28800">
+              <a:solidFill>
+                <a:srgbClr val="9ECAE1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="6"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="9ECAE1"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:numFmt formatCode="0.0%" sourceLinked="0"/>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900"/>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="t"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'ATM_Scrap_TableuData'!$A$6:$A$11</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>5/25</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6/1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6/8</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6/15</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6/22</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6/29</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'ATM_Scrap_TableuData'!$C$6:$C$11</c:f>
+              <c:numCache>
+                <c:formatCode>0.0%</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="1">
+                  <c:v>0.0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.014</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'ATM_Scrap_TableuData'!$D$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Goal</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28800">
+              <a:solidFill>
+                <a:srgbClr val="9A9A9A"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'ATM_Scrap_TableuData'!$A$6:$A$11</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>5/25</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6/1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6/8</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6/15</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6/22</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6/29</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'ATM_Scrap_TableuData'!$D$6:$D$11</c:f>
+              <c:numCache>
+                <c:formatCode>0.0%</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.05</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:marker val="1"/>
+        <c:axId val="111111111"/>
+        <c:axId val="222222222"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="111111111"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr lang="en-US" sz="1000" b="1"/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1000" b="1"/>
+                  <a:t>Week (ATM receipt)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="222222222"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="222222222"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr lang="en-US" sz="1000" b="1"/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1000" b="1"/>
+                  <a:t>Scrap %</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="0%" sourceLinked="0"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="111111111"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="FFFFFF"/>
+    </a:solidFill>
+    <a:ln w="9360">
+      <a:solidFill>
+        <a:srgbClr val="D9D9D9"/>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+  </c:spPr>
+</c:chartSpace>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:twoCellAnchor editAs="oneCell">
@@ -3995,6 +4428,41 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="ATM Scrap Trend Chart"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="7200000" cy="4000000"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
   <a:themeElements>
@@ -6332,10 +6800,10 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="60" customHeight="true">
+    <row r="2" ht="72" customHeight="true">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Source: Tableau “Top 5 Part” scrap views, June 2026. ATM = receipt inspection AFTER freeze/thaw (product sits frozen ~1–1.5 months), so this month reflects SH harvest from roughly late-April to late-May. No batch/lot numbers in the ATM feed, so cross-stage links are by time-window + part only. Values read from the two charts.</t>
+          <t xml:space="preserve">Source: Tableau “Top 5 Part” scrap views, June 2026. ATM = receipt inspection AFTER freeze/thaw (product sits frozen ~1–1.5 months), so this month reflects SH harvest from roughly late-April to late-May. Batch/lot numbers are NOT tracked in the ATM feed, so scrap can only be split by part number (666541 / 666506) — not by slaughterhouse. Values read from the two charts.</t>
         </is>
       </c>
     </row>
@@ -6500,7 +6968,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">DV Tech Pelvic Block (F), intact — performance-goal part</t>
+          <t xml:space="preserve">Pelvic Block (F), intact — performance-goal part</t>
         </is>
       </c>
       <c r="C15" s="15" t="n">
@@ -6540,10 +7008,10 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="44" customHeight="true">
+    <row r="19" ht="56" customHeight="true">
       <c r="A19" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Directional only: ATM is weekly, SH visits are sporadic, and there is no lot linkage. SH 666541 scrap below is from the Martins intact rows on the Slaughterhouse IQC tab for the matching harvest window.</t>
+          <t xml:space="preserve">Directional only: ATM is weekly, SH visits are sporadic, there is no lot linkage, and ATM can no longer be traced to a slaughterhouse. The SH scrap below is the female-intact scrap for the harvest window; Parks SH inspections only began 5/28, so these pre-June windows are Martins-dominated at the SH floor.</t>
         </is>
       </c>
     </row>
@@ -6565,7 +7033,7 @@
       </c>
       <c r="D20" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">SH 666541 scrap (Martins)</t>
+          <t xml:space="preserve">SH female-intact scrap</t>
         </is>
       </c>
     </row>
@@ -6736,30 +7204,18 @@
     <row r="35" ht="56" customHeight="true">
       <c r="A35" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Line→part mapping (dark = 666541, light = 666506) inferred from the overall-by-part chart. Lag band = 4–6 weeks (≈1–1.5-month freeze dwell). These June charts are Martins parts; Parks 666518 is not in this top-5 view.</t>
+          <t xml:space="preserve">Line→part mapping: 666541 = the light-cyan line (the series with the most data points, 25% → 0%); 666506 = the flatter near-zero series. Lag band = 4–6 weeks (≈1–1.5-month freeze dwell).</t>
         </is>
       </c>
     </row>
     <row r="36" ht="56" customHeight="true">
       <c r="A36" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Original Tableau screenshots are not embedded here — the image files were not available to paste. Drop the two screenshots beside these tables if you want the visuals inline. Refresh monthly as new Tableau months arrive.</t>
+          <t xml:space="preserve">ATM scrap can no longer be attributed to a slaughterhouse — batch/lot numbers are not tracked in Tableau, so a given ATM receipt can't be traced to Parks vs Martins; the part number (666541 intact, 666506 non-intact) is the only available split. Refresh monthly as new Tableau months arrive.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B6:C11 C15:C16 B21:B26">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0.05"/>
-        <cfvo type="num" val="0.1"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <mergeCells count="14">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
@@ -6776,7 +7232,20 @@
     <mergeCell ref="A35:F35"/>
     <mergeCell ref="A36:F36"/>
   </mergeCells>
+  <conditionalFormatting sqref="B6:C11 C15:C16 B21:B26">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0.05"/>
+        <cfvo type="num" val="0.1"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/QC inspections suppliers/Pelvic_Blocks_Quality_062626.xlsx
+++ b/QC inspections suppliers/Pelvic_Blocks_Quality_062626.xlsx
@@ -10,6 +10,7 @@
   <sheets>
     <sheet name="Defect Trends- ATM" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="Slaughterhouse IQC" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Quality Summary by Part" sheetId="14" state="visible" r:id="rId17"/>
     <sheet name="SmartAssessment" sheetId="12" state="visible" r:id="rId15"/>
     <sheet name="ATM_Scrap_TableuData" sheetId="13" state="visible" r:id="rId16"/>
     <sheet name="Receipt Summary" sheetId="3" state="visible" r:id="rId5"/>
@@ -7249,12 +7250,382 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I23"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="25" customWidth="1"/>
+    <col min="3" max="3" width="15" customWidth="1"/>
+    <col min="4" max="6" width="11" customWidth="1"/>
+    <col min="7" max="7" width="15" customWidth="1"/>
+    <col min="8" max="8" width="11" customWidth="1"/>
+    <col min="9" max="9" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="true">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quality Summary by Part</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="58" customHeight="true">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SH-floor IQC (pre-freeze incoming inspection) · all visits through 07/30/2026 · source: Slaughterhouse IQC tab. Pelvic parts are Martins (666541 / 666506) and Parks (666518); 666521 (thoracic) is a new product family at Nahunta and is kept out of the pelvic-block totals.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4" ht="18" customHeight="true">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SUMMARY — FIRST-PASS YIELD BY PART</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Part</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Description</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Slaughterhouse</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># Inspected</t>
+        </is>
+      </c>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># Pass</t>
+        </is>
+      </c>
+      <c r="F5" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># Fail</t>
+        </is>
+      </c>
+      <c r="G5" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">First-Pass Yield</t>
+        </is>
+      </c>
+      <c r="H5" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Scrap %</t>
+        </is>
+      </c>
+      <c r="I5" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Date span</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">666541</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pelvic block, intact</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Martins</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>629</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>596</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>33</v>
+      </c>
+      <c r="G6" s="15" t="n">
+        <f aca="false">IFERROR(E6/D6,0)</f>
+      </c>
+      <c r="H6" s="15" t="n">
+        <f aca="false">IFERROR(F6/D6,0)</f>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4/13 – 7/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">666506</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pelvic block, non-intact</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Martins</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>309</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>296</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="G7" s="15" t="n">
+        <f aca="false">IFERROR(E7/D7,0)</f>
+      </c>
+      <c r="H7" s="15" t="n">
+        <f aca="false">IFERROR(F7/D7,0)</f>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4/13 – 7/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">666521</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Thoracic</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nahunta</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="G8" s="15" t="n">
+        <f aca="false">IFERROR(E8/D8,0)</f>
+      </c>
+      <c r="H8" s="15" t="n">
+        <f aca="false">IFERROR(F8/D8,0)</f>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">666518</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pelvic block, intact (SM)</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Parks</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>188</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>155</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>33</v>
+      </c>
+      <c r="G9" s="15" t="n">
+        <f aca="false">IFERROR(E9/D9,0)</f>
+      </c>
+      <c r="H9" s="15" t="n">
+        <f aca="false">IFERROR(F9/D9,0)</f>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5/28 – 7/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="10"/>
+    <row r="11" ht="18" customHeight="true">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PART-BY-PART READ</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="16" customHeight="true">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">666541 — Pelvic block, intact (Martins)  ·  94.8% FPY  ·  629 inspected</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="44" customHeight="true">
+      <c r="A13" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The performance-goal part. Steady ~95% across 13 visits (4/13–7/27). Main rejects: urethra / bladder damage, membrane damage &gt; 0.5", and a few short blocks. Latest lots (07/20, 07/27) holding 95–98%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="16" customHeight="true">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">666506 — Pelvic block, non-intact (Martins)  ·  95.8% FPY  ·  309 inspected</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="44" customHeight="true">
+      <c r="A15" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tighter spec, yet the best yield of the group. Main rejects: membrane / urethra damage and a couple of early blood clots. Consistently ≥ 90% visit-to-visit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="16" customHeight="true">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">666521 — Thoracic (Nahunta)  ·  31.6% FPY  ·  19 inspected  (NEW)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="44" customHeight="true">
+      <c r="A17" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">New product family; first inspection 07/29 (small sample). 11 right-lung lacerations, mostly along the perimeter, plus 2 heart-damage rejects; 1 unit accepted with two sub-4 cm non-connecting lacerations. Inspector noted the majority of damage came from the harvesting side — the key engagement point. Held out of the pelvic totals; monitor as volume builds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="16" customHeight="true">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">666518 — Pelvic block, intact SM (Parks)  ·  82.4% FPY  ·  188 inspected  (context)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="44" customHeight="true">
+      <c r="A19" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Parks intact pelvic (batch-less). Recovering after the spring event; June–July rejects driven by urethra / bladder lacerations and short blocks on small-pig days. See the Parks deep-dive deck for detail.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="true">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NOTES</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="true">
+      <c r="A21" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">• Figures are SH-floor first-pass yield (pre-freeze), all visits to date. FPY and Scrap % are live formulas (Pass/Inspected, Fail/Inspected).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="true">
+      <c r="A22" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">• Thoracic 666521 is logged in the Slaughterhouse IQC raw data but excluded from the pelvic-block TOTAL and SH→ATM sections (single product family).</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="true">
+      <c r="A23" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">• Visit 20's 666541 count is provisional — recorded 65/63/2 pending confirmation (see Slaughterhouse IQC note 21). 666518 (Parks) is shown for context; the request was 506 / 541 / 521.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="16">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="A11:I11"/>
+    <mergeCell ref="A12:I12"/>
+    <mergeCell ref="A13:I13"/>
+    <mergeCell ref="A14:I14"/>
+    <mergeCell ref="A15:I15"/>
+    <mergeCell ref="A16:I16"/>
+    <mergeCell ref="A17:I17"/>
+    <mergeCell ref="A18:I18"/>
+    <mergeCell ref="A19:I19"/>
+    <mergeCell ref="A20:I20"/>
+    <mergeCell ref="A21:I21"/>
+    <mergeCell ref="A22:I22"/>
+    <mergeCell ref="A23:I23"/>
+  </mergeCells>
+  <conditionalFormatting sqref="G6:G9">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="num" val="0.3"/>
+        <cfvo type="num" val="0.8"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H6:H9">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0.1"/>
+        <cfvo type="num" val="0.2"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L134"/>
+  <dimension ref="A1:L152"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16.78"/>
@@ -8096,219 +8467,257 @@
         </is>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="3" t="s">
+    <row r="25" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="13.5" customHeight="true">
+      <c r="A25" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Visit 20</t>
+        </is>
+      </c>
+      <c r="B25" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-07-20</t>
+        </is>
+      </c>
+      <c r="C25" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Martins</t>
+        </is>
+      </c>
+      <c r="D25" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Toni Cruz</t>
+        </is>
+      </c>
+      <c r="E25" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jesus</t>
+        </is>
+      </c>
+      <c r="F25" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5502495107</t>
+        </is>
+      </c>
+      <c r="G25" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5502495104</t>
+        </is>
+      </c>
+      <c r="H25" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">666541</t>
+        </is>
+      </c>
+      <c r="I25" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">666506</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="13.5" customHeight="true">
+      <c r="A26" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Visit 21</t>
+        </is>
+      </c>
+      <c r="B26" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-07-27</t>
+        </is>
+      </c>
+      <c r="C26" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Martins</t>
+        </is>
+      </c>
+      <c r="D26" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Toni Cruz</t>
+        </is>
+      </c>
+      <c r="E26" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jesus</t>
+        </is>
+      </c>
+      <c r="F26" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5502512228</t>
+        </is>
+      </c>
+      <c r="G26" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5502512225</t>
+        </is>
+      </c>
+      <c r="H26" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">666541</t>
+        </is>
+      </c>
+      <c r="I26" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">666506</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="13.5" customHeight="true">
+      <c r="A27" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Visit 22</t>
+        </is>
+      </c>
+      <c r="B27" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-07-29</t>
+        </is>
+      </c>
+      <c r="C27" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nahunta</t>
+        </is>
+      </c>
+      <c r="D27" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kris</t>
+        </is>
+      </c>
+      <c r="E27" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jordan Guthrie</t>
+        </is>
+      </c>
+      <c r="F27" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5502512218</t>
+        </is>
+      </c>
+      <c r="G27" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="H27" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">666521</t>
+        </is>
+      </c>
+      <c r="I27" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="13.5" customHeight="true">
+      <c r="A28" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Visit 23</t>
+        </is>
+      </c>
+      <c r="B28" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-07-30</t>
+        </is>
+      </c>
+      <c r="C28" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Parks Family Meats</t>
+        </is>
+      </c>
+      <c r="D28" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rasmin Mujanovic</t>
+        </is>
+      </c>
+      <c r="E28" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Natalie</t>
+        </is>
+      </c>
+      <c r="F28" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(no batch data)</t>
+        </is>
+      </c>
+      <c r="G28" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="H28" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">666518</t>
+        </is>
+      </c>
+      <c r="I28" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="B26" s="3"/>
-      <c r="C26" s="3"/>
-      <c r="D26" s="3"/>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="3"/>
-      <c r="H26" s="3"/>
-      <c r="I26" s="3"/>
-      <c r="J26" s="3"/>
-      <c r="K26" s="3"/>
-      <c r="L26" s="3"/>
-    </row>
-    <row r="27" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="11" t="s">
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="3"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="3"/>
+      <c r="H30" s="3"/>
+      <c r="I30" s="3"/>
+      <c r="J30" s="3"/>
+      <c r="K30" s="3"/>
+      <c r="L30" s="3"/>
+    </row>
+    <row r="31" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="B27" s="11" t="s">
+      <c r="B31" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="C27" s="11" t="s">
+      <c r="C31" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="D27" s="11" t="s">
+      <c r="D31" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="E27" s="11" t="s">
+      <c r="E31" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="F27" s="11" t="s">
+      <c r="F31" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="G27" s="11" t="s">
+      <c r="G31" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="H27" s="11" t="s">
+      <c r="H31" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="I27" s="11" t="s">
+      <c r="I31" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="J27" s="11" t="s">
+      <c r="J31" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="K27" s="11" t="s">
+      <c r="K31" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="L27" s="11" t="s">
+      <c r="L31" s="11" t="s">
         <v>99</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="E28" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="F28" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="G28" s="6" t="n">
-        <v>48</v>
-      </c>
-      <c r="H28" s="6" t="n">
-        <v>47</v>
-      </c>
-      <c r="I28" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J28" s="15" t="n">
-        <f aca="false">IFERROR(H28/G28,0)</f>
-      </c>
-      <c r="K28" s="16" t="s">
-        <v>102</v>
-      </c>
-      <c r="L28" s="5" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="E29" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="F29" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="G29" s="6" t="n">
-        <v>17</v>
-      </c>
-      <c r="H29" s="6" t="n">
-        <v>13</v>
-      </c>
-      <c r="I29" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="J29" s="15" t="n">
-        <f aca="false">IFERROR(H29/G29,0)</f>
-      </c>
-      <c r="K29" s="16" t="s">
-        <v>105</v>
-      </c>
-      <c r="L29" s="5" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="E30" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="F30" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="G30" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="H30" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="I30" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" s="15" t="n">
-        <f aca="false">IFERROR(H30/G30,0)</f>
-      </c>
-      <c r="K30" s="16" t="s">
-        <v>108</v>
-      </c>
-      <c r="L30" s="5" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="E31" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="F31" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="G31" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="H31" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="I31" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" s="15" t="n">
-        <f aca="false">IFERROR(H31/G31,0)</f>
-      </c>
-      <c r="K31" s="16"/>
-      <c r="L31" s="5" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>53</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D32" s="5" t="s">
         <v>58</v>
@@ -8320,33 +8729,33 @@
         <v>101</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J32" s="15" t="n">
         <f aca="false">IFERROR(H32/G32,0)</f>
       </c>
       <c r="K32" s="16" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="L32" s="5" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="5" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>53</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D33" s="5" t="s">
         <v>58</v>
@@ -8358,33 +8767,33 @@
         <v>101</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>57</v>
+        <v>17</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J33" s="15" t="n">
         <f aca="false">IFERROR(H33/G33,0)</f>
       </c>
       <c r="K33" s="16" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="L33" s="5" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>53</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="D34" s="5" t="s">
         <v>59</v>
@@ -8396,19 +8805,19 @@
         <v>107</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J34" s="15" t="n">
         <f aca="false">IFERROR(H34/G34,0)</f>
       </c>
       <c r="K34" s="16" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="L34" s="5" t="s">
         <v>103</v>
@@ -8416,13 +8825,13 @@
     </row>
     <row r="35" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="5" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>53</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="D35" s="5" t="s">
         <v>59</v>
@@ -8434,33 +8843,31 @@
         <v>107</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="I35" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J35" s="15" t="n">
         <f aca="false">IFERROR(H35/G35,0)</f>
       </c>
-      <c r="K35" s="16" t="s">
-        <v>113</v>
-      </c>
+      <c r="K35" s="16"/>
       <c r="L35" s="5" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>53</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D36" s="5" t="s">
         <v>58</v>
@@ -8472,19 +8879,19 @@
         <v>101</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="I36" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J36" s="15" t="n">
         <f aca="false">IFERROR(H36/G36,0)</f>
       </c>
       <c r="K36" s="16" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="L36" s="5" t="s">
         <v>103</v>
@@ -8492,13 +8899,13 @@
     </row>
     <row r="37" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="5" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>53</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D37" s="5" t="s">
         <v>58</v>
@@ -8510,19 +8917,19 @@
         <v>101</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>25</v>
+        <v>57</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J37" s="15" t="n">
         <f aca="false">IFERROR(H37/G37,0)</f>
       </c>
       <c r="K37" s="16" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="L37" s="5" t="s">
         <v>103</v>
@@ -8530,13 +8937,13 @@
     </row>
     <row r="38" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>53</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D38" s="5" t="s">
         <v>59</v>
@@ -8548,19 +8955,19 @@
         <v>107</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J38" s="15" t="n">
         <f aca="false">IFERROR(H38/G38,0)</f>
       </c>
       <c r="K38" s="16" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="L38" s="5" t="s">
         <v>103</v>
@@ -8568,13 +8975,13 @@
     </row>
     <row r="39" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="5" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>53</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D39" s="5" t="s">
         <v>59</v>
@@ -8586,19 +8993,19 @@
         <v>107</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J39" s="15" t="n">
         <f aca="false">IFERROR(H39/G39,0)</f>
       </c>
       <c r="K39" s="16" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="L39" s="5" t="s">
         <v>103</v>
@@ -8606,13 +9013,13 @@
     </row>
     <row r="40" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="5" t="s">
-        <v>118</v>
+        <v>14</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>53</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D40" s="5" t="s">
         <v>58</v>
@@ -8624,19 +9031,19 @@
         <v>101</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="H40" s="6" t="n">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="I40" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J40" s="15" t="n">
         <f aca="false">IFERROR(H40/G40,0)</f>
       </c>
       <c r="K40" s="16" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="L40" s="5" t="s">
         <v>103</v>
@@ -8644,13 +9051,13 @@
     </row>
     <row r="41" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="5" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>53</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D41" s="5" t="s">
         <v>58</v>
@@ -8662,33 +9069,33 @@
         <v>101</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="H41" s="6" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="I41" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J41" s="15" t="n">
         <f aca="false">IFERROR(H41/G41,0)</f>
       </c>
       <c r="K41" s="16" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="L41" s="5" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="5" t="s">
-        <v>118</v>
+        <v>14</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>53</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D42" s="5" t="s">
         <v>59</v>
@@ -8700,19 +9107,19 @@
         <v>107</v>
       </c>
       <c r="G42" s="6" t="n">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="H42" s="6" t="n">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="I42" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J42" s="15" t="n">
         <f aca="false">IFERROR(H42/G42,0)</f>
       </c>
       <c r="K42" s="16" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="L42" s="5" t="s">
         <v>103</v>
@@ -8720,13 +9127,13 @@
     </row>
     <row r="43" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="5" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>53</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D43" s="5" t="s">
         <v>59</v>
@@ -8738,10 +9145,10 @@
         <v>107</v>
       </c>
       <c r="G43" s="6" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H43" s="6" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I43" s="6" t="n">
         <v>1</v>
@@ -8750,15 +9157,15 @@
         <f aca="false">IFERROR(H43/G43,0)</f>
       </c>
       <c r="K43" s="16" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="L43" s="5" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="5" t="s">
-        <v>73</v>
+        <v>118</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>53</v>
@@ -8776,232 +9183,238 @@
         <v>101</v>
       </c>
       <c r="G44" s="6" t="n">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="H44" s="6" t="n">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="I44" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J44" s="15" t="n">
         <f aca="false">IFERROR(H44/G44,0)</f>
       </c>
       <c r="K44" s="16" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="L44" s="5" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="5" t="s">
-        <v>16</v>
+        <v>120</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>81</v>
+        <v>58</v>
       </c>
       <c r="E45" s="5" t="s">
         <v>100</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>125</v>
+        <v>101</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J45" s="15" t="n">
         <f aca="false">IFERROR(H45/G45,0)</f>
       </c>
       <c r="K45" s="16" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="L45" s="5" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="5" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>53</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="H46" s="6" t="n">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="I46" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J46" s="15" t="n">
         <f aca="false">IFERROR(H46/G46,0)</f>
       </c>
-      <c r="K46" s="16"/>
+      <c r="K46" s="16" t="s">
+        <v>122</v>
+      </c>
       <c r="L46" s="5" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="5" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>53</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="G47" s="6" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="H47" s="6" t="n">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="I47" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J47" s="15" t="n">
         <f aca="false">IFERROR(H47/G47,0)</f>
       </c>
       <c r="K47" s="16" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="L47" s="5" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="5" t="s">
-        <v>128</v>
+        <v>73</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>53</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="G48" s="6" t="n">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="H48" s="6" t="n">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="I48" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J48" s="15" t="n">
         <f aca="false">IFERROR(H48/G48,0)</f>
       </c>
-      <c r="K48" s="16"/>
+      <c r="K48" s="16" t="s">
+        <v>124</v>
+      </c>
       <c r="L48" s="5" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="5" t="s">
-        <v>129</v>
+        <v>16</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="F49" s="5" t="s">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="G49" s="6" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="H49" s="6" t="n">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="I49" s="6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J49" s="15" t="n">
         <f aca="false">IFERROR(H49/G49,0)</f>
       </c>
-      <c r="K49" s="16"/>
+      <c r="K49" s="16" t="s">
+        <v>126</v>
+      </c>
       <c r="L49" s="5" t="s">
-        <v>103</v>
+        <v>127</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="5" t="s">
-        <v>87</v>
+        <v>128</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>81</v>
+        <v>58</v>
       </c>
       <c r="E50" s="5" t="s">
         <v>100</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>125</v>
+        <v>101</v>
       </c>
       <c r="G50" s="6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H50" s="6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I50" s="6" t="n">
         <v>0</v>
@@ -9011,229 +9424,159 @@
       </c>
       <c r="K50" s="16"/>
       <c r="L50" s="5" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="13.5" customHeight="true">
-      <c r="A51" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-08</t>
-        </is>
-      </c>
-      <c r="B51" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Martins</t>
-        </is>
-      </c>
-      <c r="C51" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5502428786</t>
-        </is>
-      </c>
-      <c r="D51" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">666541</t>
-        </is>
-      </c>
-      <c r="E51" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Intact</t>
-        </is>
-      </c>
-      <c r="F51" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tiss, porcine, fem, Pelvic block, intact</t>
-        </is>
+        <v>103</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="D51" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="E51" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="F51" s="5" t="s">
+        <v>101</v>
       </c>
       <c r="G51" s="6" t="n">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="H51" s="6" t="n">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="I51" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J51" s="15" t="n">
         <f aca="false">IFERROR(H51/G51,0)</f>
       </c>
-      <c r="K51" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 cut urethra</t>
-        </is>
-      </c>
-      <c r="L51" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Toni Cruz / Jesus</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="13.5" customHeight="true">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-08</t>
-        </is>
-      </c>
-      <c r="B52" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Martins</t>
-        </is>
-      </c>
-      <c r="C52" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5502428782</t>
-        </is>
-      </c>
-      <c r="D52" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">666506</t>
-        </is>
-      </c>
-      <c r="E52" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Non-intact</t>
-        </is>
-      </c>
-      <c r="F52" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tiss, porcine, fem, Pelvic block, non-intact</t>
-        </is>
+      <c r="K51" s="16" t="s">
+        <v>130</v>
+      </c>
+      <c r="L51" s="5" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D52" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="E52" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="F52" s="5" t="s">
+        <v>107</v>
       </c>
       <c r="G52" s="6" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="H52" s="6" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="I52" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J52" s="15" t="n">
         <f aca="false">IFERROR(H52/G52,0)</f>
       </c>
-      <c r="K52" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 short block</t>
-        </is>
-      </c>
-      <c r="L52" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Toni Cruz / Jesus</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="27.0" customHeight="true">
-      <c r="A53" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-15</t>
-        </is>
-      </c>
-      <c r="B53" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Martins</t>
-        </is>
-      </c>
-      <c r="C53" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5502462845</t>
-        </is>
-      </c>
-      <c r="D53" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">666541</t>
-        </is>
-      </c>
-      <c r="E53" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Intact</t>
-        </is>
-      </c>
-      <c r="F53" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tiss, porcine, fem, Pelvic block, intact</t>
-        </is>
+      <c r="K52" s="16"/>
+      <c r="L52" s="5" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D53" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="E53" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="F53" s="5" t="s">
+        <v>107</v>
       </c>
       <c r="G53" s="6" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H53" s="6" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I53" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J53" s="15" t="n">
         <f aca="false">IFERROR(H53/G53,0)</f>
       </c>
-      <c r="K53" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 damaged bowel (source had two intact tally lines: 13/12/1 + 18/18/0, combined here)</t>
-        </is>
-      </c>
-      <c r="L53" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Toni Cruz / Jesus</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="40.5" customHeight="true">
-      <c r="A54" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-16</t>
-        </is>
-      </c>
-      <c r="B54" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Parks Family Meats</t>
-        </is>
-      </c>
-      <c r="C54" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(no batch data)</t>
-        </is>
-      </c>
-      <c r="D54" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">666518</t>
-        </is>
-      </c>
-      <c r="E54" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Intact</t>
-        </is>
-      </c>
-      <c r="F54" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tiss, porcine, fem, Pelvic block, intact, SM</t>
-        </is>
+      <c r="K53" s="16"/>
+      <c r="L53" s="5" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="D54" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="E54" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="F54" s="5" t="s">
+        <v>125</v>
       </c>
       <c r="G54" s="6" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="H54" s="6" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="I54" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J54" s="15" t="n">
         <f aca="false">IFERROR(H54/G54,0)</f>
       </c>
-      <c r="K54" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 bladder hole; 1 ureter damage (many blocks failed upstream from miscuts during removal — see notes)</t>
-        </is>
-      </c>
-      <c r="L54" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Rasmin Mujanovic / Natalie</t>
-        </is>
+      <c r="K54" s="16"/>
+      <c r="L54" s="5" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="55" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="13.5" customHeight="true">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-24</t>
+          <t xml:space="preserve">2026-06-08</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
@@ -9243,7 +9586,7 @@
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">5502462845</t>
+          <t xml:space="preserve">5502428786</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
@@ -9262,20 +9605,20 @@
         </is>
       </c>
       <c r="G55" s="6" t="n">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="H55" s="6" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="I55" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J55" s="15" t="n">
         <f aca="false">IFERROR(H55/G55,0)</f>
       </c>
       <c r="K55" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 damaged bladder; 3 damaged membrane</t>
+          <t xml:space="preserve">1 cut urethra</t>
         </is>
       </c>
       <c r="L55" s="5" t="inlineStr">
@@ -9284,79 +9627,79 @@
         </is>
       </c>
     </row>
-    <row r="56" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="27.0" customHeight="true">
+    <row r="56" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="13.5" customHeight="true">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-22</t>
+          <t xml:space="preserve">2026-06-08</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parks Family Meats</t>
+          <t xml:space="preserve">Martins</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">(no batch data)</t>
+          <t xml:space="preserve">5502428782</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">666518</t>
+          <t xml:space="preserve">666506</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Intact</t>
+          <t xml:space="preserve">Non-intact</t>
         </is>
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tiss, porcine, fem, Pelvic block, intact, SM</t>
+          <t xml:space="preserve">Tiss, porcine, fem, Pelvic block, non-intact</t>
         </is>
       </c>
       <c r="G56" s="6" t="n">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="H56" s="6" t="n">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="I56" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J56" s="15" t="n">
         <f aca="false">IFERROR(H56/G56,0)</f>
       </c>
       <c r="K56" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 bladder hole; 2 critical-area lacerations; 2 short blocks</t>
+          <t xml:space="preserve">1 short block</t>
         </is>
       </c>
       <c r="L56" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rasmin Mujanovic / Natalie</t>
+          <t xml:space="preserve">Toni Cruz / Jesus</t>
         </is>
       </c>
     </row>
     <row r="57" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="27.0" customHeight="true">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-25</t>
+          <t xml:space="preserve">2026-06-15</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parks Family Meats</t>
+          <t xml:space="preserve">Martins</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">(no batch data)</t>
+          <t xml:space="preserve">5502462845</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">666518</t>
+          <t xml:space="preserve">666541</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -9366,51 +9709,51 @@
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tiss, porcine, fem, Pelvic block, intact, SM</t>
+          <t xml:space="preserve">Tiss, porcine, fem, Pelvic block, intact</t>
         </is>
       </c>
       <c r="G57" s="6" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="H57" s="6" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="I57" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J57" s="15" t="n">
         <f aca="false">IFERROR(H57/G57,0)</f>
       </c>
       <c r="K57" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 bladder hole; 1 ureter laceration; 1 short block</t>
+          <t xml:space="preserve">1 damaged bowel (source had two intact tally lines: 13/12/1 + 18/18/0, combined here)</t>
         </is>
       </c>
       <c r="L57" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rasmin Mujanovic / Natalie</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="13.5" customHeight="true">
+          <t xml:space="preserve">Toni Cruz / Jesus</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="40.5" customHeight="true">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-29</t>
+          <t xml:space="preserve">2026-06-16</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Martins</t>
+          <t xml:space="preserve">Parks Family Meats</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">5502471460</t>
+          <t xml:space="preserve">(no batch data)</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">666541</t>
+          <t xml:space="preserve">666518</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -9420,36 +9763,36 @@
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tiss, porcine, fem, Pelvic block, intact</t>
+          <t xml:space="preserve">Tiss, porcine, fem, Pelvic block, intact, SM</t>
         </is>
       </c>
       <c r="G58" s="6" t="n">
         <v>16</v>
       </c>
       <c r="H58" s="6" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I58" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J58" s="15" t="n">
         <f aca="false">IFERROR(H58/G58,0)</f>
       </c>
       <c r="K58" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">1 bladder hole; 1 ureter damage (many blocks failed upstream from miscuts during removal — see notes)</t>
         </is>
       </c>
       <c r="L58" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Toni Cruz / Jesus</t>
+          <t xml:space="preserve">Rasmin Mujanovic / Natalie</t>
         </is>
       </c>
     </row>
     <row r="59" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="13.5" customHeight="true">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-29</t>
+          <t xml:space="preserve">2026-06-24</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
@@ -9459,39 +9802,39 @@
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">5502471457</t>
+          <t xml:space="preserve">5502462845</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">666506</t>
+          <t xml:space="preserve">666541</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Non-intact</t>
+          <t xml:space="preserve">Intact</t>
         </is>
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tiss, porcine, fem, Pelvic block, non-intact</t>
+          <t xml:space="preserve">Tiss, porcine, fem, Pelvic block, intact</t>
         </is>
       </c>
       <c r="G59" s="6" t="n">
+        <v>34</v>
+      </c>
+      <c r="H59" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="I59" s="6" t="n">
         <v>4</v>
-      </c>
-      <c r="H59" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="I59" s="6" t="n">
-        <v>0</v>
       </c>
       <c r="J59" s="15" t="n">
         <f aca="false">IFERROR(H59/G59,0)</f>
       </c>
       <c r="K59" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">1 damaged bladder; 3 damaged membrane</t>
         </is>
       </c>
       <c r="L59" s="5" t="inlineStr">
@@ -9500,10 +9843,10 @@
         </is>
       </c>
     </row>
-    <row r="60" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="54.0" customHeight="true">
+    <row r="60" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="27.0" customHeight="true">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-29</t>
+          <t xml:space="preserve">2026-06-22</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
@@ -9532,20 +9875,20 @@
         </is>
       </c>
       <c r="G60" s="6" t="n">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="H60" s="6" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="I60" s="6" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="J60" s="15" t="n">
         <f aca="false">IFERROR(H60/G60,0)</f>
       </c>
       <c r="K60" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 damaged during bowel cleaning (bowel blockage burst); 2 short blocks; 1 critical-area laceration; 7 urethra/bladder lacerations (cuts near template edge)</t>
+          <t xml:space="preserve">1 bladder hole; 2 critical-area lacerations; 2 short blocks</t>
         </is>
       </c>
       <c r="L60" s="5" t="inlineStr">
@@ -9554,25 +9897,25 @@
         </is>
       </c>
     </row>
-    <row r="61" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="13.5" customHeight="true">
+    <row r="61" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="27.0" customHeight="true">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-07-06</t>
+          <t xml:space="preserve">2026-06-25</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Martins</t>
+          <t xml:space="preserve">Parks Family Meats</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">5502471460</t>
+          <t xml:space="preserve">(no batch data)</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">666541</t>
+          <t xml:space="preserve">666518</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -9582,36 +9925,36 @@
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tiss, porcine, fem, Pelvic block, intact</t>
+          <t xml:space="preserve">Tiss, porcine, fem, Pelvic block, intact, SM</t>
         </is>
       </c>
       <c r="G61" s="6" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="H61" s="6" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="I61" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J61" s="15" t="n">
         <f aca="false">IFERROR(H61/G61,0)</f>
       </c>
       <c r="K61" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 damaged urethra</t>
+          <t xml:space="preserve">1 bladder hole; 1 ureter laceration; 1 short block</t>
         </is>
       </c>
       <c r="L61" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Toni Cruz / Jesus</t>
+          <t xml:space="preserve">Rasmin Mujanovic / Natalie</t>
         </is>
       </c>
     </row>
     <row r="62" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="13.5" customHeight="true">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-07-06</t>
+          <t xml:space="preserve">2026-06-29</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
@@ -9621,39 +9964,39 @@
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">5502471457</t>
+          <t xml:space="preserve">5502471460</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">666506</t>
+          <t xml:space="preserve">666541</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Non-intact</t>
+          <t xml:space="preserve">Intact</t>
         </is>
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tiss, porcine, fem, Pelvic block, non-intact</t>
+          <t xml:space="preserve">Tiss, porcine, fem, Pelvic block, intact</t>
         </is>
       </c>
       <c r="G62" s="6" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="H62" s="6" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="I62" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J62" s="15" t="n">
         <f aca="false">IFERROR(H62/G62,0)</f>
       </c>
       <c r="K62" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 membrane damage larger than 1.5"</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="L62" s="5" t="inlineStr">
@@ -9665,7 +10008,7 @@
     <row r="63" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="13.5" customHeight="true">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-07-13</t>
+          <t xml:space="preserve">2026-06-29</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
@@ -9675,39 +10018,39 @@
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">5502495107</t>
+          <t xml:space="preserve">5502471457</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">666541</t>
+          <t xml:space="preserve">666506</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Intact</t>
+          <t xml:space="preserve">Non-intact</t>
         </is>
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tiss, porcine, fem, Pelvic block, intact</t>
+          <t xml:space="preserve">Tiss, porcine, fem, Pelvic block, non-intact</t>
         </is>
       </c>
       <c r="G63" s="6" t="n">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="H63" s="6" t="n">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="I63" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J63" s="15" t="n">
         <f aca="false">IFERROR(H63/G63,0)</f>
       </c>
       <c r="K63" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 damaged membrane; 1 damaged bladder</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="L63" s="5" t="inlineStr">
@@ -9716,79 +10059,79 @@
         </is>
       </c>
     </row>
-    <row r="64" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="13.5" customHeight="true">
+    <row r="64" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="54.0" customHeight="true">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-07-13</t>
+          <t xml:space="preserve">2026-06-29</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Martins</t>
+          <t xml:space="preserve">Parks Family Meats</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">5502495104</t>
+          <t xml:space="preserve">(no batch data)</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">666506</t>
+          <t xml:space="preserve">666518</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Non-intact</t>
+          <t xml:space="preserve">Intact</t>
         </is>
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tiss, porcine, fem, Pelvic block, non-intact</t>
+          <t xml:space="preserve">Tiss, porcine, fem, Pelvic block, intact, SM</t>
         </is>
       </c>
       <c r="G64" s="6" t="n">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="H64" s="6" t="n">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="I64" s="6" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J64" s="15" t="n">
         <f aca="false">IFERROR(H64/G64,0)</f>
       </c>
       <c r="K64" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2 damaged during bowel cleaning (bowel blockage burst); 2 short blocks; 1 critical-area laceration; 7 urethra/bladder lacerations (cuts near template edge)</t>
         </is>
       </c>
       <c r="L64" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Toni Cruz / Jesus</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="27.0" customHeight="true">
+          <t xml:space="preserve">Rasmin Mujanovic / Natalie</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="13.5" customHeight="true">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-07-13</t>
+          <t xml:space="preserve">2026-07-06</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parks Family Meats</t>
+          <t xml:space="preserve">Martins</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">(no batch data)</t>
+          <t xml:space="preserve">5502471460</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">666518</t>
+          <t xml:space="preserve">666541</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -9798,391 +10141,641 @@
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tiss, porcine, fem, Pelvic block, intact, SM</t>
+          <t xml:space="preserve">Tiss, porcine, fem, Pelvic block, intact</t>
         </is>
       </c>
       <c r="G65" s="6" t="n">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="H65" s="6" t="n">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="I65" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J65" s="15" t="n">
         <f aca="false">IFERROR(H65/G65,0)</f>
       </c>
       <c r="K65" s="16" t="inlineStr">
         <is>
+          <t xml:space="preserve">1 damaged urethra</t>
+        </is>
+      </c>
+      <c r="L65" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Toni Cruz / Jesus</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="13.5" customHeight="true">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-07-06</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Martins</t>
+        </is>
+      </c>
+      <c r="C66" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5502471457</t>
+        </is>
+      </c>
+      <c r="D66" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">666506</t>
+        </is>
+      </c>
+      <c r="E66" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non-intact</t>
+        </is>
+      </c>
+      <c r="F66" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tiss, porcine, fem, Pelvic block, non-intact</t>
+        </is>
+      </c>
+      <c r="G66" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="H66" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="I66" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J66" s="15" t="n">
+        <f aca="false">IFERROR(H66/G66,0)</f>
+      </c>
+      <c r="K66" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 membrane damage larger than 1.5"</t>
+        </is>
+      </c>
+      <c r="L66" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Toni Cruz / Jesus</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="13.5" customHeight="true">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-07-13</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Martins</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5502495107</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">666541</t>
+        </is>
+      </c>
+      <c r="E67" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Intact</t>
+        </is>
+      </c>
+      <c r="F67" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tiss, porcine, fem, Pelvic block, intact</t>
+        </is>
+      </c>
+      <c r="G67" s="6" t="n">
+        <v>38</v>
+      </c>
+      <c r="H67" s="6" t="n">
+        <v>36</v>
+      </c>
+      <c r="I67" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J67" s="15" t="n">
+        <f aca="false">IFERROR(H67/G67,0)</f>
+      </c>
+      <c r="K67" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 damaged membrane; 1 damaged bladder</t>
+        </is>
+      </c>
+      <c r="L67" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Toni Cruz / Jesus</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="13.5" customHeight="true">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-07-13</t>
+        </is>
+      </c>
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Martins</t>
+        </is>
+      </c>
+      <c r="C68" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5502495104</t>
+        </is>
+      </c>
+      <c r="D68" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">666506</t>
+        </is>
+      </c>
+      <c r="E68" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non-intact</t>
+        </is>
+      </c>
+      <c r="F68" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tiss, porcine, fem, Pelvic block, non-intact</t>
+        </is>
+      </c>
+      <c r="G68" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="H68" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="I68" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" s="15" t="n">
+        <f aca="false">IFERROR(H68/G68,0)</f>
+      </c>
+      <c r="K68" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L68" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Toni Cruz / Jesus</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="27.0" customHeight="true">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-07-13</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Parks Family Meats</t>
+        </is>
+      </c>
+      <c r="C69" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(no batch data)</t>
+        </is>
+      </c>
+      <c r="D69" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">666518</t>
+        </is>
+      </c>
+      <c r="E69" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Intact</t>
+        </is>
+      </c>
+      <c r="F69" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tiss, porcine, fem, Pelvic block, intact, SM</t>
+        </is>
+      </c>
+      <c r="G69" s="6" t="n">
+        <v>34</v>
+      </c>
+      <c r="H69" s="6" t="n">
+        <v>29</v>
+      </c>
+      <c r="I69" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="J69" s="15" t="n">
+        <f aca="false">IFERROR(H69/G69,0)</f>
+      </c>
+      <c r="K69" s="16" t="inlineStr">
+        <is>
           <t xml:space="preserve">2 damaged during bowel cleaning (bowel blockage burst); 3 short blocks (smaller pigs)</t>
         </is>
       </c>
-      <c r="L65" s="5" t="inlineStr">
+      <c r="L69" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Rasmin Mujanovic / Natalie</t>
         </is>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A67" s="3" t="s">
+    <row r="70" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="40.0" customHeight="true">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-07-20</t>
+        </is>
+      </c>
+      <c r="B70" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Martins</t>
+        </is>
+      </c>
+      <c r="C70" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5502495107</t>
+        </is>
+      </c>
+      <c r="D70" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">666541</t>
+        </is>
+      </c>
+      <c r="E70" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Intact</t>
+        </is>
+      </c>
+      <c r="F70" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tiss, porcine, fem, Pelvic block, intact</t>
+        </is>
+      </c>
+      <c r="G70" s="6" t="n">
+        <v>65</v>
+      </c>
+      <c r="H70" s="6" t="n">
+        <v>63</v>
+      </c>
+      <c r="I70" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J70" s="15" t="n">
+        <f aca="false">IFERROR(H70/G70,0)</f>
+      </c>
+      <c r="K70" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 deformed bladder documented; source #Fail cell read 1, but 65 inspected − 63 pass = 2 → 1 reject undocumented (confirm)</t>
+        </is>
+      </c>
+      <c r="L70" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Toni Cruz / Jesus</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="13.5" customHeight="true">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-07-20</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Martins</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5502495104</t>
+        </is>
+      </c>
+      <c r="D71" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">666506</t>
+        </is>
+      </c>
+      <c r="E71" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non-intact</t>
+        </is>
+      </c>
+      <c r="F71" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tiss, porcine, fem, Pelvic block, non-intact</t>
+        </is>
+      </c>
+      <c r="G71" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="H71" s="6" t="n">
+        <v>29</v>
+      </c>
+      <c r="I71" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J71" s="15" t="n">
+        <f aca="false">IFERROR(H71/G71,0)</f>
+      </c>
+      <c r="K71" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 large membrane damage</t>
+        </is>
+      </c>
+      <c r="L71" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Toni Cruz / Jesus</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="13.5" customHeight="true">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-07-27</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Martins</t>
+        </is>
+      </c>
+      <c r="C72" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5502512228</t>
+        </is>
+      </c>
+      <c r="D72" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">666541</t>
+        </is>
+      </c>
+      <c r="E72" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Intact</t>
+        </is>
+      </c>
+      <c r="F72" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tiss, porcine, fem, Pelvic block, intact</t>
+        </is>
+      </c>
+      <c r="G72" s="6" t="n">
+        <v>46</v>
+      </c>
+      <c r="H72" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="I72" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J72" s="15" t="n">
+        <f aca="false">IFERROR(H72/G72,0)</f>
+      </c>
+      <c r="K72" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 damaged membrane larger than 0.5"</t>
+        </is>
+      </c>
+      <c r="L72" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Toni Cruz / Jesus</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="13.5" customHeight="true">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-07-27</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Martins</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5502512225</t>
+        </is>
+      </c>
+      <c r="D73" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">666506</t>
+        </is>
+      </c>
+      <c r="E73" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non-intact</t>
+        </is>
+      </c>
+      <c r="F73" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tiss, porcine, fem, Pelvic block, non-intact</t>
+        </is>
+      </c>
+      <c r="G73" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="H73" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I73" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" s="15" t="n">
+        <f aca="false">IFERROR(H73/G73,0)</f>
+      </c>
+      <c r="K73" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L73" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Toni Cruz / Jesus</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="54.0" customHeight="true">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-07-29</t>
+        </is>
+      </c>
+      <c r="B74" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nahunta</t>
+        </is>
+      </c>
+      <c r="C74" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5502512218</t>
+        </is>
+      </c>
+      <c r="D74" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">666521</t>
+        </is>
+      </c>
+      <c r="E74" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="F74" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tiss, porcine, Thoracic</t>
+        </is>
+      </c>
+      <c r="G74" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="H74" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="I74" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="J74" s="15" t="n">
+        <f aca="false">IFERROR(H74/G74,0)</f>
+      </c>
+      <c r="K74" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11 right-lung lacerations (mostly along the perimeter); 2 heart damage; 1 accepted with two sub-4cm perimeter lacerations that did not connect. Majority of damage attributed to the harvesting side.</t>
+        </is>
+      </c>
+      <c r="L74" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kris / Jordan Guthrie</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="27.0" customHeight="true">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-07-30</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Parks Family Meats</t>
+        </is>
+      </c>
+      <c r="C75" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(no batch data)</t>
+        </is>
+      </c>
+      <c r="D75" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">666518</t>
+        </is>
+      </c>
+      <c r="E75" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Intact</t>
+        </is>
+      </c>
+      <c r="F75" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tiss, porcine, fem, Pelvic block, intact, SM</t>
+        </is>
+      </c>
+      <c r="G75" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="H75" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="I75" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J75" s="15" t="n">
+        <f aca="false">IFERROR(H75/G75,0)</f>
+      </c>
+      <c r="K75" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 pelvic block short (majority of pigs received were male → lower numbers)</t>
+        </is>
+      </c>
+      <c r="L75" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rasmin Mujanovic / Natalie</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A77" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="B67" s="3"/>
-      <c r="C67" s="3"/>
-      <c r="D67" s="3"/>
-      <c r="E67" s="3"/>
-      <c r="F67" s="3"/>
-      <c r="G67" s="3"/>
-      <c r="H67" s="3"/>
-      <c r="I67" s="3"/>
-      <c r="J67" s="3"/>
-      <c r="K67" s="3"/>
-      <c r="L67" s="3"/>
-    </row>
-    <row r="68" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A68" s="11" t="s">
+      <c r="B77" s="3"/>
+      <c r="C77" s="3"/>
+      <c r="D77" s="3"/>
+      <c r="E77" s="3"/>
+      <c r="F77" s="3"/>
+      <c r="G77" s="3"/>
+      <c r="H77" s="3"/>
+      <c r="I77" s="3"/>
+      <c r="J77" s="3"/>
+      <c r="K77" s="3"/>
+      <c r="L77" s="3"/>
+    </row>
+    <row r="78" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A78" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="B68" s="11" t="s">
+      <c r="B78" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="C68" s="11" t="s">
+      <c r="C78" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="D68" s="11" t="s">
+      <c r="D78" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="E68" s="11" t="s">
+      <c r="E78" s="11" t="s">
         <v>132</v>
       </c>
-      <c r="F68" s="11" t="s">
+      <c r="F78" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="G68" s="11" t="s">
+      <c r="G78" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="H68" s="11" t="s">
+      <c r="H78" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="I68" s="11" t="s">
+      <c r="I78" s="11" t="s">
         <v>97</v>
-      </c>
-    </row>
-    <row r="69" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A69" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="B69" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="C69" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="D69" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="E69" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="F69" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="G69" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="H69" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I69" s="15" t="n">
-        <f aca="false">IFERROR(G69/F69,0)</f>
-      </c>
-    </row>
-    <row r="70" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A70" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="B70" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="C70" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="D70" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="E70" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="F70" s="6" t="n">
-        <v>65</v>
-      </c>
-      <c r="G70" s="6" t="n">
-        <v>60</v>
-      </c>
-      <c r="H70" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="I70" s="15" t="n">
-        <f aca="false">IFERROR(G70/F70,0)</f>
-      </c>
-    </row>
-    <row r="71" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A71" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="B71" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="C71" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="D71" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="E71" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="F71" s="6" t="n">
-        <v>52</v>
-      </c>
-      <c r="G71" s="6" t="n">
-        <v>48</v>
-      </c>
-      <c r="H71" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="I71" s="15" t="n">
-        <f aca="false">IFERROR(G71/F71,0)</f>
-      </c>
-    </row>
-    <row r="72" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A72" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="B72" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="C72" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="D72" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="E72" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="F72" s="6" t="n">
-        <v>57</v>
-      </c>
-      <c r="G72" s="6" t="n">
-        <v>56</v>
-      </c>
-      <c r="H72" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I72" s="15" t="n">
-        <f aca="false">IFERROR(G72/F72,0)</f>
-      </c>
-    </row>
-    <row r="73" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A73" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="B73" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="C73" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="D73" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="E73" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="F73" s="6" t="n">
-        <v>45</v>
-      </c>
-      <c r="G73" s="6" t="n">
-        <v>41</v>
-      </c>
-      <c r="H73" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="I73" s="15" t="n">
-        <f aca="false">IFERROR(G73/F73,0)</f>
-      </c>
-    </row>
-    <row r="74" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A74" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="B74" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="C74" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="D74" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="E74" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="F74" s="6" t="n">
-        <v>62</v>
-      </c>
-      <c r="G74" s="6" t="n">
-        <v>58</v>
-      </c>
-      <c r="H74" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="I74" s="15" t="n">
-        <f aca="false">IFERROR(G74/F74,0)</f>
-      </c>
-    </row>
-    <row r="75" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A75" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="B75" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="C75" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="D75" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="E75" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="F75" s="6" t="n">
-        <v>73</v>
-      </c>
-      <c r="G75" s="6" t="n">
-        <v>71</v>
-      </c>
-      <c r="H75" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="I75" s="15" t="n">
-        <f aca="false">IFERROR(G75/F75,0)</f>
-      </c>
-    </row>
-    <row r="76" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A76" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="B76" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="C76" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="D76" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="E76" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="F76" s="6" t="n">
-        <v>93</v>
-      </c>
-      <c r="G76" s="6" t="n">
-        <v>87</v>
-      </c>
-      <c r="H76" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="I76" s="15" t="n">
-        <f aca="false">IFERROR(G76/F76,0)</f>
-      </c>
-    </row>
-    <row r="77" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A77" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="B77" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="C77" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="D77" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="E77" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="F77" s="6" t="n">
-        <v>39</v>
-      </c>
-      <c r="G77" s="6" t="n">
-        <v>36</v>
-      </c>
-      <c r="H77" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="I77" s="15" t="n">
-        <f aca="false">IFERROR(G77/F77,0)</f>
-      </c>
-    </row>
-    <row r="78" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A78" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="B78" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="C78" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="D78" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="E78" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="F78" s="6" t="n">
-        <v>16</v>
-      </c>
-      <c r="G78" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="H78" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="I78" s="15" t="n">
-        <f aca="false">IFERROR(G78/F78,0)</f>
       </c>
     </row>
     <row r="79" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="12" t="s">
-        <v>84</v>
+        <v>57</v>
       </c>
       <c r="B79" s="12" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C79" s="12" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="D79" s="12" t="s">
         <v>53</v>
       </c>
       <c r="E79" s="12" t="s">
-        <v>83</v>
+        <v>52</v>
       </c>
       <c r="F79" s="6" t="n">
-        <v>54</v>
+        <v>7</v>
       </c>
       <c r="G79" s="6" t="n">
-        <v>52</v>
+        <v>7</v>
       </c>
       <c r="H79" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I79" s="15" t="n">
         <f aca="false">IFERROR(G79/F79,0)</f>
@@ -10190,28 +10783,28 @@
     </row>
     <row r="80" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="12" t="s">
-        <v>85</v>
+        <v>56</v>
       </c>
       <c r="B80" s="12" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C80" s="12" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="D80" s="12" t="s">
         <v>53</v>
       </c>
       <c r="E80" s="12" t="s">
-        <v>83</v>
+        <v>52</v>
       </c>
       <c r="F80" s="6" t="n">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="G80" s="6" t="n">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="H80" s="6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I80" s="15" t="n">
         <f aca="false">IFERROR(G80/F80,0)</f>
@@ -10219,64 +10812,54 @@
     </row>
     <row r="81" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="12" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="B81" s="12" t="s">
-        <v>81</v>
+        <v>59</v>
       </c>
       <c r="C81" s="12" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="D81" s="12" t="s">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="E81" s="12" t="s">
-        <v>87</v>
+        <v>61</v>
       </c>
       <c r="F81" s="6" t="n">
-        <v>7</v>
+        <v>52</v>
       </c>
       <c r="G81" s="6" t="n">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="H81" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I81" s="15" t="n">
         <f aca="false">IFERROR(G81/F81,0)</f>
       </c>
     </row>
-    <row r="82" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="13.5" customHeight="true">
-      <c r="A82" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5502428786</t>
-        </is>
-      </c>
-      <c r="B82" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">666541</t>
-        </is>
-      </c>
-      <c r="C82" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Intact</t>
-        </is>
-      </c>
-      <c r="D82" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Martins</t>
-        </is>
-      </c>
-      <c r="E82" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-08</t>
-        </is>
+    <row r="82" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A82" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="B82" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="C82" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="D82" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="E82" s="12" t="s">
+        <v>61</v>
       </c>
       <c r="F82" s="6" t="n">
-        <v>17</v>
+        <v>57</v>
       </c>
       <c r="G82" s="6" t="n">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="H82" s="6" t="n">
         <v>1</v>
@@ -10285,310 +10868,230 @@
         <f aca="false">IFERROR(G82/F82,0)</f>
       </c>
     </row>
-    <row r="83" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="13.5" customHeight="true">
-      <c r="A83" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5502428782</t>
-        </is>
-      </c>
-      <c r="B83" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">666506</t>
-        </is>
-      </c>
-      <c r="C83" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Non-intact</t>
-        </is>
-      </c>
-      <c r="D83" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Martins</t>
-        </is>
-      </c>
-      <c r="E83" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-08</t>
-        </is>
+    <row r="83" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A83" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="B83" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="C83" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="D83" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="E83" s="12" t="s">
+        <v>65</v>
       </c>
       <c r="F83" s="6" t="n">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="G83" s="6" t="n">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="H83" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I83" s="15" t="n">
         <f aca="false">IFERROR(G83/F83,0)</f>
       </c>
     </row>
-    <row r="84" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="13.5" customHeight="true">
-      <c r="A84" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5502462845</t>
-        </is>
-      </c>
-      <c r="B84" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">666541</t>
-        </is>
-      </c>
-      <c r="C84" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Intact</t>
-        </is>
-      </c>
-      <c r="D84" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Martins</t>
-        </is>
-      </c>
-      <c r="E84" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-15</t>
-        </is>
+    <row r="84" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A84" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="B84" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="C84" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="D84" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="E84" s="12" t="s">
+        <v>65</v>
       </c>
       <c r="F84" s="6" t="n">
-        <v>31</v>
+        <v>62</v>
       </c>
       <c r="G84" s="6" t="n">
-        <v>30</v>
+        <v>58</v>
       </c>
       <c r="H84" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I84" s="15" t="n">
         <f aca="false">IFERROR(G84/F84,0)</f>
       </c>
     </row>
-    <row r="85" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="13.5" customHeight="true">
-      <c r="A85" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5502462845</t>
-        </is>
-      </c>
-      <c r="B85" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">666541</t>
-        </is>
-      </c>
-      <c r="C85" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Intact</t>
-        </is>
-      </c>
-      <c r="D85" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Martins</t>
-        </is>
-      </c>
-      <c r="E85" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-24</t>
-        </is>
+    <row r="85" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A85" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="B85" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="C85" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="D85" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="E85" s="12" t="s">
+        <v>69</v>
       </c>
       <c r="F85" s="6" t="n">
-        <v>34</v>
+        <v>73</v>
       </c>
       <c r="G85" s="6" t="n">
-        <v>30</v>
+        <v>71</v>
       </c>
       <c r="H85" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I85" s="15" t="n">
         <f aca="false">IFERROR(G85/F85,0)</f>
       </c>
     </row>
-    <row r="86" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="13.5" customHeight="true">
-      <c r="A86" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(no batch data)</t>
-        </is>
-      </c>
-      <c r="B86" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">666518</t>
-        </is>
-      </c>
-      <c r="C86" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Intact</t>
-        </is>
-      </c>
-      <c r="D86" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Parks Family Meats</t>
-        </is>
-      </c>
-      <c r="E86" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-16</t>
-        </is>
+    <row r="86" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A86" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="B86" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="C86" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="D86" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="E86" s="12" t="s">
+        <v>69</v>
       </c>
       <c r="F86" s="6" t="n">
-        <v>16</v>
+        <v>93</v>
       </c>
       <c r="G86" s="6" t="n">
-        <v>14</v>
+        <v>87</v>
       </c>
       <c r="H86" s="6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I86" s="15" t="n">
         <f aca="false">IFERROR(G86/F86,0)</f>
       </c>
     </row>
-    <row r="87" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="13.5" customHeight="true">
-      <c r="A87" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(no batch data)</t>
-        </is>
-      </c>
-      <c r="B87" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">666518</t>
-        </is>
-      </c>
-      <c r="C87" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Intact</t>
-        </is>
-      </c>
-      <c r="D87" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Parks Family Meats</t>
-        </is>
-      </c>
-      <c r="E87" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-22</t>
-        </is>
+    <row r="87" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A87" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="B87" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="C87" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="D87" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="E87" s="12" t="s">
+        <v>73</v>
       </c>
       <c r="F87" s="6" t="n">
+        <v>39</v>
+      </c>
+      <c r="G87" s="6" t="n">
         <v>36</v>
       </c>
-      <c r="G87" s="6" t="n">
-        <v>31</v>
-      </c>
       <c r="H87" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I87" s="15" t="n">
         <f aca="false">IFERROR(G87/F87,0)</f>
       </c>
     </row>
-    <row r="88" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="13.5" customHeight="true">
-      <c r="A88" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(no batch data)</t>
-        </is>
-      </c>
-      <c r="B88" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">666518</t>
-        </is>
-      </c>
-      <c r="C88" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Intact</t>
-        </is>
-      </c>
-      <c r="D88" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Parks Family Meats</t>
-        </is>
-      </c>
-      <c r="E88" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-25</t>
-        </is>
+    <row r="88" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A88" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="B88" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="C88" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="D88" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="E88" s="12" t="s">
+        <v>16</v>
       </c>
       <c r="F88" s="6" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G88" s="6" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H88" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I88" s="15" t="n">
         <f aca="false">IFERROR(G88/F88,0)</f>
       </c>
     </row>
-    <row r="89" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="13.5" customHeight="true">
-      <c r="A89" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5502471460</t>
-        </is>
-      </c>
-      <c r="B89" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">666541</t>
-        </is>
-      </c>
-      <c r="C89" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Intact</t>
-        </is>
-      </c>
-      <c r="D89" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Martins</t>
-        </is>
-      </c>
-      <c r="E89" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-29</t>
-        </is>
+    <row r="89" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A89" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="B89" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="C89" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="D89" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="E89" s="12" t="s">
+        <v>83</v>
       </c>
       <c r="F89" s="6" t="n">
-        <v>16</v>
+        <v>54</v>
       </c>
       <c r="G89" s="6" t="n">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="H89" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I89" s="15" t="n">
         <f aca="false">IFERROR(G89/F89,0)</f>
       </c>
     </row>
-    <row r="90" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="13.5" customHeight="true">
-      <c r="A90" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5502471457</t>
-        </is>
-      </c>
-      <c r="B90" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">666506</t>
-        </is>
-      </c>
-      <c r="C90" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Non-intact</t>
-        </is>
-      </c>
-      <c r="D90" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Martins</t>
-        </is>
-      </c>
-      <c r="E90" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-29</t>
-        </is>
+    <row r="90" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A90" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="B90" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="C90" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="D90" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="E90" s="12" t="s">
+        <v>83</v>
       </c>
       <c r="F90" s="6" t="n">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="G90" s="6" t="n">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="H90" s="6" t="n">
         <v>0</v>
@@ -10597,40 +11100,30 @@
         <f aca="false">IFERROR(G90/F90,0)</f>
       </c>
     </row>
-    <row r="91" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="13.5" customHeight="true">
-      <c r="A91" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(no batch data)</t>
-        </is>
-      </c>
-      <c r="B91" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">666518</t>
-        </is>
-      </c>
-      <c r="C91" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Intact</t>
-        </is>
-      </c>
-      <c r="D91" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Parks Family Meats</t>
-        </is>
-      </c>
-      <c r="E91" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-29</t>
-        </is>
+    <row r="91" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A91" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="B91" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="C91" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="D91" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="E91" s="12" t="s">
+        <v>87</v>
       </c>
       <c r="F91" s="6" t="n">
-        <v>50</v>
+        <v>7</v>
       </c>
       <c r="G91" s="6" t="n">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="H91" s="6" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="I91" s="15" t="n">
         <f aca="false">IFERROR(G91/F91,0)</f>
@@ -10639,7 +11132,7 @@
     <row r="92" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="13.5" customHeight="true">
       <c r="A92" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">5502471460</t>
+          <t xml:space="preserve">5502428786</t>
         </is>
       </c>
       <c r="B92" s="12" t="inlineStr">
@@ -10659,14 +11152,14 @@
       </c>
       <c r="E92" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-07-06</t>
+          <t xml:space="preserve">2026-06-08</t>
         </is>
       </c>
       <c r="F92" s="6" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G92" s="6" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H92" s="6" t="n">
         <v>1</v>
@@ -10678,7 +11171,7 @@
     <row r="93" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="13.5" customHeight="true">
       <c r="A93" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">5502471457</t>
+          <t xml:space="preserve">5502428782</t>
         </is>
       </c>
       <c r="B93" s="12" t="inlineStr">
@@ -10698,14 +11191,14 @@
       </c>
       <c r="E93" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-07-06</t>
+          <t xml:space="preserve">2026-06-08</t>
         </is>
       </c>
       <c r="F93" s="6" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G93" s="6" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H93" s="6" t="n">
         <v>1</v>
@@ -10717,7 +11210,7 @@
     <row r="94" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="13.5" customHeight="true">
       <c r="A94" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">5502495107</t>
+          <t xml:space="preserve">5502462845</t>
         </is>
       </c>
       <c r="B94" s="12" t="inlineStr">
@@ -10737,17 +11230,17 @@
       </c>
       <c r="E94" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-07-13</t>
+          <t xml:space="preserve">2026-06-15</t>
         </is>
       </c>
       <c r="F94" s="6" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="G94" s="6" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="H94" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I94" s="15" t="n">
         <f aca="false">IFERROR(G94/F94,0)</f>
@@ -10756,17 +11249,17 @@
     <row r="95" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="13.5" customHeight="true">
       <c r="A95" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">5502495104</t>
+          <t xml:space="preserve">5502462845</t>
         </is>
       </c>
       <c r="B95" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">666506</t>
+          <t xml:space="preserve">666541</t>
         </is>
       </c>
       <c r="C95" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Non-intact</t>
+          <t xml:space="preserve">Intact</t>
         </is>
       </c>
       <c r="D95" s="12" t="inlineStr">
@@ -10776,17 +11269,17 @@
       </c>
       <c r="E95" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-07-13</t>
+          <t xml:space="preserve">2026-06-24</t>
         </is>
       </c>
       <c r="F95" s="6" t="n">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="G95" s="6" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="H95" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I95" s="15" t="n">
         <f aca="false">IFERROR(G95/F95,0)</f>
@@ -10815,859 +11308,1170 @@
       </c>
       <c r="E96" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-07-13</t>
+          <t xml:space="preserve">2026-06-16</t>
         </is>
       </c>
       <c r="F96" s="6" t="n">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="G96" s="6" t="n">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="H96" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I96" s="15" t="n">
         <f aca="false">IFERROR(G96/F96,0)</f>
       </c>
     </row>
-    <row r="97" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A97" s="17" t="s">
+    <row r="97" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="13.5" customHeight="true">
+      <c r="A97" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(no batch data)</t>
+        </is>
+      </c>
+      <c r="B97" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">666518</t>
+        </is>
+      </c>
+      <c r="C97" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Intact</t>
+        </is>
+      </c>
+      <c r="D97" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Parks Family Meats</t>
+        </is>
+      </c>
+      <c r="E97" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-22</t>
+        </is>
+      </c>
+      <c r="F97" s="6" t="n">
+        <v>36</v>
+      </c>
+      <c r="G97" s="6" t="n">
+        <v>31</v>
+      </c>
+      <c r="H97" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="I97" s="15" t="n">
+        <f aca="false">IFERROR(G97/F97,0)</f>
+      </c>
+    </row>
+    <row r="98" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="13.5" customHeight="true">
+      <c r="A98" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(no batch data)</t>
+        </is>
+      </c>
+      <c r="B98" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">666518</t>
+        </is>
+      </c>
+      <c r="C98" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Intact</t>
+        </is>
+      </c>
+      <c r="D98" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Parks Family Meats</t>
+        </is>
+      </c>
+      <c r="E98" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-25</t>
+        </is>
+      </c>
+      <c r="F98" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="G98" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="H98" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I98" s="15" t="n">
+        <f aca="false">IFERROR(G98/F98,0)</f>
+      </c>
+    </row>
+    <row r="99" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="13.5" customHeight="true">
+      <c r="A99" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5502471460</t>
+        </is>
+      </c>
+      <c r="B99" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">666541</t>
+        </is>
+      </c>
+      <c r="C99" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Intact</t>
+        </is>
+      </c>
+      <c r="D99" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Martins</t>
+        </is>
+      </c>
+      <c r="E99" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-29</t>
+        </is>
+      </c>
+      <c r="F99" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="G99" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="H99" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I99" s="15" t="n">
+        <f aca="false">IFERROR(G99/F99,0)</f>
+      </c>
+    </row>
+    <row r="100" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="13.5" customHeight="true">
+      <c r="A100" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5502471457</t>
+        </is>
+      </c>
+      <c r="B100" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">666506</t>
+        </is>
+      </c>
+      <c r="C100" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non-intact</t>
+        </is>
+      </c>
+      <c r="D100" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Martins</t>
+        </is>
+      </c>
+      <c r="E100" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-29</t>
+        </is>
+      </c>
+      <c r="F100" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="G100" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="H100" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I100" s="15" t="n">
+        <f aca="false">IFERROR(G100/F100,0)</f>
+      </c>
+    </row>
+    <row r="101" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="13.5" customHeight="true">
+      <c r="A101" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(no batch data)</t>
+        </is>
+      </c>
+      <c r="B101" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">666518</t>
+        </is>
+      </c>
+      <c r="C101" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Intact</t>
+        </is>
+      </c>
+      <c r="D101" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Parks Family Meats</t>
+        </is>
+      </c>
+      <c r="E101" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-29</t>
+        </is>
+      </c>
+      <c r="F101" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="G101" s="6" t="n">
+        <v>38</v>
+      </c>
+      <c r="H101" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I101" s="15" t="n">
+        <f aca="false">IFERROR(G101/F101,0)</f>
+      </c>
+    </row>
+    <row r="102" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="13.5" customHeight="true">
+      <c r="A102" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5502471460</t>
+        </is>
+      </c>
+      <c r="B102" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">666541</t>
+        </is>
+      </c>
+      <c r="C102" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Intact</t>
+        </is>
+      </c>
+      <c r="D102" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Martins</t>
+        </is>
+      </c>
+      <c r="E102" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-07-06</t>
+        </is>
+      </c>
+      <c r="F102" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="G102" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="H102" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I102" s="15" t="n">
+        <f aca="false">IFERROR(G102/F102,0)</f>
+      </c>
+    </row>
+    <row r="103" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="13.5" customHeight="true">
+      <c r="A103" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5502471457</t>
+        </is>
+      </c>
+      <c r="B103" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">666506</t>
+        </is>
+      </c>
+      <c r="C103" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non-intact</t>
+        </is>
+      </c>
+      <c r="D103" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Martins</t>
+        </is>
+      </c>
+      <c r="E103" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-07-06</t>
+        </is>
+      </c>
+      <c r="F103" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G103" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H103" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I103" s="15" t="n">
+        <f aca="false">IFERROR(G103/F103,0)</f>
+      </c>
+    </row>
+    <row r="104" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="13.5" customHeight="true">
+      <c r="A104" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5502495107</t>
+        </is>
+      </c>
+      <c r="B104" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">666541</t>
+        </is>
+      </c>
+      <c r="C104" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Intact</t>
+        </is>
+      </c>
+      <c r="D104" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Martins</t>
+        </is>
+      </c>
+      <c r="E104" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-07-13</t>
+        </is>
+      </c>
+      <c r="F104" s="6" t="n">
+        <v>38</v>
+      </c>
+      <c r="G104" s="6" t="n">
+        <v>36</v>
+      </c>
+      <c r="H104" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I104" s="15" t="n">
+        <f aca="false">IFERROR(G104/F104,0)</f>
+      </c>
+    </row>
+    <row r="105" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="13.5" customHeight="true">
+      <c r="A105" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5502495104</t>
+        </is>
+      </c>
+      <c r="B105" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">666506</t>
+        </is>
+      </c>
+      <c r="C105" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non-intact</t>
+        </is>
+      </c>
+      <c r="D105" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Martins</t>
+        </is>
+      </c>
+      <c r="E105" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-07-13</t>
+        </is>
+      </c>
+      <c r="F105" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="G105" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="H105" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I105" s="15" t="n">
+        <f aca="false">IFERROR(G105/F105,0)</f>
+      </c>
+    </row>
+    <row r="106" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="13.5" customHeight="true">
+      <c r="A106" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(no batch data)</t>
+        </is>
+      </c>
+      <c r="B106" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">666518</t>
+        </is>
+      </c>
+      <c r="C106" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Intact</t>
+        </is>
+      </c>
+      <c r="D106" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Parks Family Meats</t>
+        </is>
+      </c>
+      <c r="E106" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-07-13</t>
+        </is>
+      </c>
+      <c r="F106" s="6" t="n">
+        <v>34</v>
+      </c>
+      <c r="G106" s="6" t="n">
+        <v>29</v>
+      </c>
+      <c r="H106" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="I106" s="15" t="n">
+        <f aca="false">IFERROR(G106/F106,0)</f>
+      </c>
+    </row>
+    <row r="107" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="13.5" customHeight="true">
+      <c r="A107" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5502495107</t>
+        </is>
+      </c>
+      <c r="B107" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">666541</t>
+        </is>
+      </c>
+      <c r="C107" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Intact</t>
+        </is>
+      </c>
+      <c r="D107" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Martins</t>
+        </is>
+      </c>
+      <c r="E107" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-07-20</t>
+        </is>
+      </c>
+      <c r="F107" s="6" t="n">
+        <v>65</v>
+      </c>
+      <c r="G107" s="6" t="n">
+        <v>63</v>
+      </c>
+      <c r="H107" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I107" s="15" t="n">
+        <f aca="false">IFERROR(G107/F107,0)</f>
+      </c>
+    </row>
+    <row r="108" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="13.5" customHeight="true">
+      <c r="A108" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5502495104</t>
+        </is>
+      </c>
+      <c r="B108" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">666506</t>
+        </is>
+      </c>
+      <c r="C108" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non-intact</t>
+        </is>
+      </c>
+      <c r="D108" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Martins</t>
+        </is>
+      </c>
+      <c r="E108" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-07-20</t>
+        </is>
+      </c>
+      <c r="F108" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="G108" s="6" t="n">
+        <v>29</v>
+      </c>
+      <c r="H108" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I108" s="15" t="n">
+        <f aca="false">IFERROR(G108/F108,0)</f>
+      </c>
+    </row>
+    <row r="109" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="13.5" customHeight="true">
+      <c r="A109" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5502512228</t>
+        </is>
+      </c>
+      <c r="B109" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">666541</t>
+        </is>
+      </c>
+      <c r="C109" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Intact</t>
+        </is>
+      </c>
+      <c r="D109" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Martins</t>
+        </is>
+      </c>
+      <c r="E109" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-07-27</t>
+        </is>
+      </c>
+      <c r="F109" s="6" t="n">
+        <v>46</v>
+      </c>
+      <c r="G109" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="H109" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I109" s="15" t="n">
+        <f aca="false">IFERROR(G109/F109,0)</f>
+      </c>
+    </row>
+    <row r="110" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="13.5" customHeight="true">
+      <c r="A110" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5502512225</t>
+        </is>
+      </c>
+      <c r="B110" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">666506</t>
+        </is>
+      </c>
+      <c r="C110" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Non-intact</t>
+        </is>
+      </c>
+      <c r="D110" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Martins</t>
+        </is>
+      </c>
+      <c r="E110" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-07-27</t>
+        </is>
+      </c>
+      <c r="F110" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="G110" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="H110" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I110" s="15" t="n">
+        <f aca="false">IFERROR(G110/F110,0)</f>
+      </c>
+    </row>
+    <row r="111" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="13.5" customHeight="true">
+      <c r="A111" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(no batch data)</t>
+        </is>
+      </c>
+      <c r="B111" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">666518</t>
+        </is>
+      </c>
+      <c r="C111" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Intact</t>
+        </is>
+      </c>
+      <c r="D111" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Parks Family Meats</t>
+        </is>
+      </c>
+      <c r="E111" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-07-30</t>
+        </is>
+      </c>
+      <c r="F111" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G111" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H111" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I111" s="15" t="n">
+        <f aca="false">IFERROR(G111/F111,0)</f>
+      </c>
+    </row>
+    <row r="112" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A112" s="17" t="s">
         <v>133</v>
       </c>
-      <c r="B97" s="17"/>
-      <c r="C97" s="17"/>
-      <c r="D97" s="17"/>
-      <c r="E97" s="17"/>
-      <c r="F97" s="8" t="n">
-        <f aca="false">SUM(F69:F96)</f>
-      </c>
-      <c r="G97" s="8" t="n">
-        <f aca="false">SUM(G69:G96)</f>
-      </c>
-      <c r="H97" s="8" t="n">
-        <f aca="false">SUM(H69:H96)</f>
-      </c>
-      <c r="I97" s="9" t="n">
-        <f aca="false">IFERROR(G97/F97,0)</f>
-      </c>
-    </row>
-    <row r="99" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A99" s="10" t="s">
+      <c r="B112" s="17"/>
+      <c r="C112" s="17"/>
+      <c r="D112" s="17"/>
+      <c r="E112" s="17"/>
+      <c r="F112" s="8" t="n">
+        <f aca="false">SUM(F79:F111)</f>
+      </c>
+      <c r="G112" s="8" t="n">
+        <f aca="false">SUM(G79:G111)</f>
+      </c>
+      <c r="H112" s="8" t="n">
+        <f aca="false">SUM(H79:H111)</f>
+      </c>
+      <c r="I112" s="9" t="n">
+        <f aca="false">IFERROR(G112/F112,0)</f>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A114" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="B99" s="10"/>
-      <c r="C99" s="10"/>
-      <c r="D99" s="10"/>
-      <c r="E99" s="10"/>
-      <c r="F99" s="10"/>
-      <c r="G99" s="10"/>
-      <c r="H99" s="10"/>
-      <c r="I99" s="10"/>
-      <c r="J99" s="10"/>
-      <c r="K99" s="10"/>
-      <c r="L99" s="10"/>
-    </row>
-    <row r="100" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A100" s="11" t="s">
+      <c r="B114" s="10"/>
+      <c r="C114" s="10"/>
+      <c r="D114" s="10"/>
+      <c r="E114" s="10"/>
+      <c r="F114" s="10"/>
+      <c r="G114" s="10"/>
+      <c r="H114" s="10"/>
+      <c r="I114" s="10"/>
+      <c r="J114" s="10"/>
+      <c r="K114" s="10"/>
+      <c r="L114" s="10"/>
+    </row>
+    <row r="115" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A115" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="B100" s="11" t="s">
+      <c r="B115" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="C100" s="11" t="s">
+      <c r="C115" s="11" t="s">
         <v>135</v>
       </c>
-      <c r="D100" s="11" t="s">
+      <c r="D115" s="11" t="s">
         <v>136</v>
       </c>
-      <c r="E100" s="11" t="s">
+      <c r="E115" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="F100" s="11" t="s">
+      <c r="F115" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="G100" s="11" t="s">
+      <c r="G115" s="11" t="s">
         <v>139</v>
       </c>
-      <c r="H100" s="11" t="s">
+      <c r="H115" s="11" t="s">
         <v>140</v>
       </c>
-      <c r="I100" s="11" t="s">
+      <c r="I115" s="11" t="s">
         <v>141</v>
       </c>
-      <c r="J100" s="11" t="s">
+      <c r="J115" s="11" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="101" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A101" s="18" t="s">
+    <row r="116" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A116" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="B101" s="18" t="s">
+      <c r="B116" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="C101" s="6" t="n">
+      <c r="C116" s="6" t="n">
         <v>65</v>
       </c>
-      <c r="D101" s="6" t="n">
+      <c r="D116" s="6" t="n">
         <v>60</v>
       </c>
-      <c r="E101" s="15" t="n">
-        <f aca="false">IFERROR(D101/C101,0)</f>
-      </c>
-      <c r="F101" s="6" t="n">
-        <f aca="false">SUMIFS('Receipt Summary'!F:F,'Receipt Summary'!E:E,A101)</f>
-      </c>
-      <c r="G101" s="6" t="n">
-        <f aca="false">SUMIFS('Receipt Summary'!G:G,'Receipt Summary'!E:E,A101)</f>
-      </c>
-      <c r="H101" s="15" t="n">
-        <f aca="false">IFERROR(G101/F101,0)</f>
-      </c>
-      <c r="I101" s="6" t="n">
-        <f aca="false">D101-F101</f>
-      </c>
-      <c r="J101" s="16" t="s">
+      <c r="E116" s="15" t="n">
+        <f aca="false">IFERROR(D116/C116,0)</f>
+      </c>
+      <c r="F116" s="6" t="n">
+        <f aca="false">SUMIFS('Receipt Summary'!F:F,'Receipt Summary'!E:E,A116)</f>
+      </c>
+      <c r="G116" s="6" t="n">
+        <f aca="false">SUMIFS('Receipt Summary'!G:G,'Receipt Summary'!E:E,A116)</f>
+      </c>
+      <c r="H116" s="15" t="n">
+        <f aca="false">IFERROR(G116/F116,0)</f>
+      </c>
+      <c r="I116" s="6" t="n">
+        <f aca="false">D116-F116</f>
+      </c>
+      <c r="J116" s="16" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="102" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A102" s="18" t="s">
+    <row r="117" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A117" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="B102" s="18" t="s">
+      <c r="B117" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="C102" s="6" t="n">
+      <c r="C117" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="D102" s="6" t="n">
+      <c r="D117" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="E102" s="15" t="n">
-        <f aca="false">IFERROR(D102/C102,0)</f>
-      </c>
-      <c r="F102" s="6" t="n">
-        <f aca="false">SUMIFS('Receipt Summary'!F:F,'Receipt Summary'!E:E,A102)</f>
-      </c>
-      <c r="G102" s="6" t="n">
-        <f aca="false">SUMIFS('Receipt Summary'!G:G,'Receipt Summary'!E:E,A102)</f>
-      </c>
-      <c r="H102" s="15" t="n">
-        <f aca="false">IFERROR(G102/F102,0)</f>
-      </c>
-      <c r="I102" s="6" t="n">
-        <f aca="false">D102-F102</f>
-      </c>
-      <c r="J102" s="16" t="s">
+      <c r="E117" s="15" t="n">
+        <f aca="false">IFERROR(D117/C117,0)</f>
+      </c>
+      <c r="F117" s="6" t="n">
+        <f aca="false">SUMIFS('Receipt Summary'!F:F,'Receipt Summary'!E:E,A117)</f>
+      </c>
+      <c r="G117" s="6" t="n">
+        <f aca="false">SUMIFS('Receipt Summary'!G:G,'Receipt Summary'!E:E,A117)</f>
+      </c>
+      <c r="H117" s="15" t="n">
+        <f aca="false">IFERROR(G117/F117,0)</f>
+      </c>
+      <c r="I117" s="6" t="n">
+        <f aca="false">D117-F117</f>
+      </c>
+      <c r="J117" s="16" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="103" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A103" s="18" t="s">
+    <row r="118" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A118" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="B103" s="18" t="s">
+      <c r="B118" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="C103" s="6" t="n">
+      <c r="C118" s="6" t="n">
         <v>57</v>
       </c>
-      <c r="D103" s="6" t="n">
+      <c r="D118" s="6" t="n">
         <v>56</v>
       </c>
-      <c r="E103" s="15" t="n">
-        <f aca="false">IFERROR(D103/C103,0)</f>
-      </c>
-      <c r="F103" s="6" t="n">
-        <f aca="false">SUMIFS('Receipt Summary'!F:F,'Receipt Summary'!E:E,A103)</f>
-      </c>
-      <c r="G103" s="6" t="n">
-        <f aca="false">SUMIFS('Receipt Summary'!G:G,'Receipt Summary'!E:E,A103)</f>
-      </c>
-      <c r="H103" s="15" t="n">
-        <f aca="false">IFERROR(G103/F103,0)</f>
-      </c>
-      <c r="I103" s="6" t="n">
-        <f aca="false">D103-F103</f>
-      </c>
-      <c r="J103" s="16" t="s">
+      <c r="E118" s="15" t="n">
+        <f aca="false">IFERROR(D118/C118,0)</f>
+      </c>
+      <c r="F118" s="6" t="n">
+        <f aca="false">SUMIFS('Receipt Summary'!F:F,'Receipt Summary'!E:E,A118)</f>
+      </c>
+      <c r="G118" s="6" t="n">
+        <f aca="false">SUMIFS('Receipt Summary'!G:G,'Receipt Summary'!E:E,A118)</f>
+      </c>
+      <c r="H118" s="15" t="n">
+        <f aca="false">IFERROR(G118/F118,0)</f>
+      </c>
+      <c r="I118" s="6" t="n">
+        <f aca="false">D118-F118</f>
+      </c>
+      <c r="J118" s="16" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="104" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A104" s="18" t="s">
+    <row r="119" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A119" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="B104" s="18" t="s">
+      <c r="B119" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="C104" s="6" t="n">
+      <c r="C119" s="6" t="n">
         <v>52</v>
       </c>
-      <c r="D104" s="6" t="n">
+      <c r="D119" s="6" t="n">
         <v>48</v>
       </c>
-      <c r="E104" s="15" t="n">
-        <f aca="false">IFERROR(D104/C104,0)</f>
-      </c>
-      <c r="F104" s="6" t="n">
-        <f aca="false">SUMIFS('Receipt Summary'!F:F,'Receipt Summary'!E:E,A104)</f>
-      </c>
-      <c r="G104" s="6" t="n">
-        <f aca="false">SUMIFS('Receipt Summary'!G:G,'Receipt Summary'!E:E,A104)</f>
-      </c>
-      <c r="H104" s="15" t="n">
-        <f aca="false">IFERROR(G104/F104,0)</f>
-      </c>
-      <c r="I104" s="6" t="n">
-        <f aca="false">D104-F104</f>
-      </c>
-      <c r="J104" s="16" t="s">
+      <c r="E119" s="15" t="n">
+        <f aca="false">IFERROR(D119/C119,0)</f>
+      </c>
+      <c r="F119" s="6" t="n">
+        <f aca="false">SUMIFS('Receipt Summary'!F:F,'Receipt Summary'!E:E,A119)</f>
+      </c>
+      <c r="G119" s="6" t="n">
+        <f aca="false">SUMIFS('Receipt Summary'!G:G,'Receipt Summary'!E:E,A119)</f>
+      </c>
+      <c r="H119" s="15" t="n">
+        <f aca="false">IFERROR(G119/F119,0)</f>
+      </c>
+      <c r="I119" s="6" t="n">
+        <f aca="false">D119-F119</f>
+      </c>
+      <c r="J119" s="16" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="105" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A105" s="18" t="s">
+    <row r="120" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A120" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="B105" s="18" t="s">
+      <c r="B120" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="C105" s="6" t="n">
+      <c r="C120" s="6" t="n">
         <v>62</v>
       </c>
-      <c r="D105" s="6" t="n">
+      <c r="D120" s="6" t="n">
         <v>58</v>
       </c>
-      <c r="E105" s="15" t="n">
-        <f aca="false">IFERROR(D105/C105,0)</f>
-      </c>
-      <c r="F105" s="6" t="n">
-        <f aca="false">SUMIFS('Receipt Summary'!F:F,'Receipt Summary'!E:E,A105)</f>
-      </c>
-      <c r="G105" s="6" t="n">
-        <f aca="false">SUMIFS('Receipt Summary'!G:G,'Receipt Summary'!E:E,A105)</f>
-      </c>
-      <c r="H105" s="15" t="n">
-        <f aca="false">IFERROR(G105/F105,0)</f>
-      </c>
-      <c r="I105" s="6" t="n">
-        <f aca="false">D105-F105</f>
-      </c>
-      <c r="J105" s="16" t="s">
+      <c r="E120" s="15" t="n">
+        <f aca="false">IFERROR(D120/C120,0)</f>
+      </c>
+      <c r="F120" s="6" t="n">
+        <f aca="false">SUMIFS('Receipt Summary'!F:F,'Receipt Summary'!E:E,A120)</f>
+      </c>
+      <c r="G120" s="6" t="n">
+        <f aca="false">SUMIFS('Receipt Summary'!G:G,'Receipt Summary'!E:E,A120)</f>
+      </c>
+      <c r="H120" s="15" t="n">
+        <f aca="false">IFERROR(G120/F120,0)</f>
+      </c>
+      <c r="I120" s="6" t="n">
+        <f aca="false">D120-F120</f>
+      </c>
+      <c r="J120" s="16" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="106" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A106" s="18" t="s">
+    <row r="121" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A121" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="B106" s="18" t="s">
+      <c r="B121" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="C106" s="6" t="n">
+      <c r="C121" s="6" t="n">
         <v>45</v>
       </c>
-      <c r="D106" s="6" t="n">
+      <c r="D121" s="6" t="n">
         <v>41</v>
       </c>
-      <c r="E106" s="15" t="n">
-        <f aca="false">IFERROR(D106/C106,0)</f>
-      </c>
-      <c r="F106" s="6" t="n">
-        <f aca="false">SUMIFS('Receipt Summary'!F:F,'Receipt Summary'!E:E,A106)</f>
-      </c>
-      <c r="G106" s="6" t="n">
-        <f aca="false">SUMIFS('Receipt Summary'!G:G,'Receipt Summary'!E:E,A106)</f>
-      </c>
-      <c r="H106" s="15" t="n">
-        <f aca="false">IFERROR(G106/F106,0)</f>
-      </c>
-      <c r="I106" s="6" t="n">
-        <f aca="false">D106-F106</f>
-      </c>
-      <c r="J106" s="16" t="s">
+      <c r="E121" s="15" t="n">
+        <f aca="false">IFERROR(D121/C121,0)</f>
+      </c>
+      <c r="F121" s="6" t="n">
+        <f aca="false">SUMIFS('Receipt Summary'!F:F,'Receipt Summary'!E:E,A121)</f>
+      </c>
+      <c r="G121" s="6" t="n">
+        <f aca="false">SUMIFS('Receipt Summary'!G:G,'Receipt Summary'!E:E,A121)</f>
+      </c>
+      <c r="H121" s="15" t="n">
+        <f aca="false">IFERROR(G121/F121,0)</f>
+      </c>
+      <c r="I121" s="6" t="n">
+        <f aca="false">D121-F121</f>
+      </c>
+      <c r="J121" s="16" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="107" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A107" s="18" t="s">
+    <row r="122" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A122" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="B107" s="18" t="s">
+      <c r="B122" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="C107" s="6" t="n">
+      <c r="C122" s="6" t="n">
         <v>93</v>
       </c>
-      <c r="D107" s="6" t="n">
+      <c r="D122" s="6" t="n">
         <v>87</v>
       </c>
-      <c r="E107" s="15" t="n">
-        <f aca="false">IFERROR(D107/C107,0)</f>
-      </c>
-      <c r="F107" s="6" t="n">
-        <f aca="false">SUMIFS('Receipt Summary'!F:F,'Receipt Summary'!E:E,A107)</f>
-      </c>
-      <c r="G107" s="6" t="n">
-        <f aca="false">SUMIFS('Receipt Summary'!G:G,'Receipt Summary'!E:E,A107)</f>
-      </c>
-      <c r="H107" s="15" t="n">
-        <f aca="false">IFERROR(G107/F107,0)</f>
-      </c>
-      <c r="I107" s="6" t="n">
-        <f aca="false">D107-F107</f>
-      </c>
-      <c r="J107" s="16" t="s">
+      <c r="E122" s="15" t="n">
+        <f aca="false">IFERROR(D122/C122,0)</f>
+      </c>
+      <c r="F122" s="6" t="n">
+        <f aca="false">SUMIFS('Receipt Summary'!F:F,'Receipt Summary'!E:E,A122)</f>
+      </c>
+      <c r="G122" s="6" t="n">
+        <f aca="false">SUMIFS('Receipt Summary'!G:G,'Receipt Summary'!E:E,A122)</f>
+      </c>
+      <c r="H122" s="15" t="n">
+        <f aca="false">IFERROR(G122/F122,0)</f>
+      </c>
+      <c r="I122" s="6" t="n">
+        <f aca="false">D122-F122</f>
+      </c>
+      <c r="J122" s="16" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="108" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A108" s="18" t="s">
+    <row r="123" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A123" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="B108" s="18" t="s">
+      <c r="B123" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="C108" s="6" t="n">
+      <c r="C123" s="6" t="n">
         <v>73</v>
       </c>
-      <c r="D108" s="6" t="n">
+      <c r="D123" s="6" t="n">
         <v>71</v>
       </c>
-      <c r="E108" s="15" t="n">
-        <f aca="false">IFERROR(D108/C108,0)</f>
-      </c>
-      <c r="F108" s="6" t="n">
-        <f aca="false">SUMIFS('Receipt Summary'!F:F,'Receipt Summary'!E:E,A108)</f>
-      </c>
-      <c r="G108" s="6" t="n">
-        <f aca="false">SUMIFS('Receipt Summary'!G:G,'Receipt Summary'!E:E,A108)</f>
-      </c>
-      <c r="H108" s="15" t="n">
-        <f aca="false">IFERROR(G108/F108,0)</f>
-      </c>
-      <c r="I108" s="6" t="n">
-        <f aca="false">D108-F108</f>
-      </c>
-      <c r="J108" s="16" t="s">
+      <c r="E123" s="15" t="n">
+        <f aca="false">IFERROR(D123/C123,0)</f>
+      </c>
+      <c r="F123" s="6" t="n">
+        <f aca="false">SUMIFS('Receipt Summary'!F:F,'Receipt Summary'!E:E,A123)</f>
+      </c>
+      <c r="G123" s="6" t="n">
+        <f aca="false">SUMIFS('Receipt Summary'!G:G,'Receipt Summary'!E:E,A123)</f>
+      </c>
+      <c r="H123" s="15" t="n">
+        <f aca="false">IFERROR(G123/F123,0)</f>
+      </c>
+      <c r="I123" s="6" t="n">
+        <f aca="false">D123-F123</f>
+      </c>
+      <c r="J123" s="16" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="109" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A109" s="18" t="s">
+    <row r="124" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A124" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="B109" s="18" t="s">
+      <c r="B124" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="C109" s="6" t="n">
+      <c r="C124" s="6" t="n">
         <v>54</v>
       </c>
-      <c r="D109" s="6" t="n">
+      <c r="D124" s="6" t="n">
         <v>52</v>
       </c>
-      <c r="E109" s="15" t="n">
-        <f aca="false">IFERROR(D109/C109,0)</f>
-      </c>
-      <c r="F109" s="6" t="n">
-        <f aca="false">SUMIFS('Receipt Summary'!F:F,'Receipt Summary'!E:E,A109)</f>
-      </c>
-      <c r="G109" s="6" t="n">
-        <f aca="false">SUMIFS('Receipt Summary'!G:G,'Receipt Summary'!E:E,A109)</f>
-      </c>
-      <c r="H109" s="15" t="n">
-        <f aca="false">IFERROR(G109/F109,0)</f>
-      </c>
-      <c r="I109" s="6" t="n">
-        <f aca="false">D109-F109</f>
-      </c>
-      <c r="J109" s="16" t="s">
+      <c r="E124" s="15" t="n">
+        <f aca="false">IFERROR(D124/C124,0)</f>
+      </c>
+      <c r="F124" s="6" t="n">
+        <f aca="false">SUMIFS('Receipt Summary'!F:F,'Receipt Summary'!E:E,A124)</f>
+      </c>
+      <c r="G124" s="6" t="n">
+        <f aca="false">SUMIFS('Receipt Summary'!G:G,'Receipt Summary'!E:E,A124)</f>
+      </c>
+      <c r="H124" s="15" t="n">
+        <f aca="false">IFERROR(G124/F124,0)</f>
+      </c>
+      <c r="I124" s="6" t="n">
+        <f aca="false">D124-F124</f>
+      </c>
+      <c r="J124" s="16" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="110" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A110" s="18" t="s">
+    <row r="125" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A125" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="B110" s="18" t="s">
+      <c r="B125" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="C110" s="6" t="n">
+      <c r="C125" s="6" t="n">
         <v>36</v>
       </c>
-      <c r="D110" s="6" t="n">
+      <c r="D125" s="6" t="n">
         <v>36</v>
       </c>
-      <c r="E110" s="15" t="n">
-        <f aca="false">IFERROR(D110/C110,0)</f>
-      </c>
-      <c r="F110" s="6" t="n">
-        <f aca="false">SUMIFS('Receipt Summary'!F:F,'Receipt Summary'!E:E,A110)</f>
-      </c>
-      <c r="G110" s="6" t="n">
-        <f aca="false">SUMIFS('Receipt Summary'!G:G,'Receipt Summary'!E:E,A110)</f>
-      </c>
-      <c r="H110" s="15" t="n">
-        <f aca="false">IFERROR(G110/F110,0)</f>
-      </c>
-      <c r="I110" s="6" t="n">
-        <f aca="false">D110-F110</f>
-      </c>
-      <c r="J110" s="16" t="s">
+      <c r="E125" s="15" t="n">
+        <f aca="false">IFERROR(D125/C125,0)</f>
+      </c>
+      <c r="F125" s="6" t="n">
+        <f aca="false">SUMIFS('Receipt Summary'!F:F,'Receipt Summary'!E:E,A125)</f>
+      </c>
+      <c r="G125" s="6" t="n">
+        <f aca="false">SUMIFS('Receipt Summary'!G:G,'Receipt Summary'!E:E,A125)</f>
+      </c>
+      <c r="H125" s="15" t="n">
+        <f aca="false">IFERROR(G125/F125,0)</f>
+      </c>
+      <c r="I125" s="6" t="n">
+        <f aca="false">D125-F125</f>
+      </c>
+      <c r="J125" s="16" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="111" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="72.0" customHeight="true">
-      <c r="A111" s="18" t="inlineStr">
+    <row r="126" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="72.0" customHeight="true">
+      <c r="A126" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">5502462845</t>
         </is>
       </c>
-      <c r="B111" s="18" t="inlineStr">
+      <c r="B126" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">666541</t>
         </is>
       </c>
-      <c r="C111" s="6" t="n">
+      <c r="C126" s="6" t="n">
         <v>31</v>
       </c>
-      <c r="D111" s="6" t="n">
+      <c r="D126" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="E111" s="15" t="n">
-        <f aca="false">IFERROR(D111/C111,0)</f>
-      </c>
-      <c r="F111" s="6" t="n">
-        <f aca="false">SUMIFS('Receipt Summary'!F:F,'Receipt Summary'!E:E,A111)</f>
-      </c>
-      <c r="G111" s="6" t="n">
-        <f aca="false">SUMIFS('Receipt Summary'!G:G,'Receipt Summary'!E:E,A111)</f>
-      </c>
-      <c r="H111" s="15" t="n">
-        <f aca="false">IFERROR(G111/F111,0)</f>
-      </c>
-      <c r="I111" s="6" t="n">
-        <f aca="false">D111-F111</f>
-      </c>
-      <c r="J111" s="16" t="inlineStr">
+      <c r="E126" s="15" t="n">
+        <f aca="false">IFERROR(D126/C126,0)</f>
+      </c>
+      <c r="F126" s="6" t="n">
+        <f aca="false">SUMIFS('Receipt Summary'!F:F,'Receipt Summary'!E:E,A126)</f>
+      </c>
+      <c r="G126" s="6" t="n">
+        <f aca="false">SUMIFS('Receipt Summary'!G:G,'Receipt Summary'!E:E,A126)</f>
+      </c>
+      <c r="H126" s="15" t="n">
+        <f aca="false">IFERROR(G126/F126,0)</f>
+      </c>
+      <c r="I126" s="6" t="n">
+        <f aca="false">D126-F126</f>
+      </c>
+      <c r="J126" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">Newly harvested 06/15. SH sampled 31 intact, passed 30 (96.8%). Lot # reappears on the 06/24 tally (34 inspected / 30 passed) — recorded as a separate Visit 12, likely a tally-sheet lot carry-over (see notes). Not yet at ATM; expected in coming weeks.</t>
         </is>
       </c>
     </row>
-    <row r="112" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="72.0" customHeight="true">
-      <c r="A112" s="18" t="inlineStr">
+    <row r="127" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="72.0" customHeight="true">
+      <c r="A127" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">5502471460</t>
         </is>
       </c>
-      <c r="B112" s="18" t="inlineStr">
+      <c r="B127" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">666541</t>
         </is>
       </c>
-      <c r="C112" s="6" t="n">
+      <c r="C127" s="6" t="n">
         <v>16</v>
       </c>
-      <c r="D112" s="6" t="n">
+      <c r="D127" s="6" t="n">
         <v>16</v>
       </c>
-      <c r="E112" s="15" t="n">
-        <f aca="false">IFERROR(D112/C112,0)</f>
-      </c>
-      <c r="F112" s="6" t="n">
-        <f aca="false">SUMIFS('Receipt Summary'!F:F,'Receipt Summary'!E:E,A112)</f>
-      </c>
-      <c r="G112" s="6" t="n">
-        <f aca="false">SUMIFS('Receipt Summary'!G:G,'Receipt Summary'!E:E,A112)</f>
-      </c>
-      <c r="H112" s="15" t="n">
-        <f aca="false">IFERROR(G112/F112,0)</f>
-      </c>
-      <c r="I112" s="6" t="n">
-        <f aca="false">D112-F112</f>
-      </c>
-      <c r="J112" s="16" t="inlineStr">
+      <c r="E127" s="15" t="n">
+        <f aca="false">IFERROR(D127/C127,0)</f>
+      </c>
+      <c r="F127" s="6" t="n">
+        <f aca="false">SUMIFS('Receipt Summary'!F:F,'Receipt Summary'!E:E,A127)</f>
+      </c>
+      <c r="G127" s="6" t="n">
+        <f aca="false">SUMIFS('Receipt Summary'!G:G,'Receipt Summary'!E:E,A127)</f>
+      </c>
+      <c r="H127" s="15" t="n">
+        <f aca="false">IFERROR(G127/F127,0)</f>
+      </c>
+      <c r="I127" s="6" t="n">
+        <f aca="false">D127-F127</f>
+      </c>
+      <c r="J127" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">Newly harvested 06/29. SH sampled 16 intact, all passed (100%). Lot # reused on the 07/06 tally (12 inspected / 11 passed) — recorded as a separate Visit 17, likely a tally-sheet lot carry-over. Not yet at ATM; expected in coming weeks.</t>
         </is>
       </c>
     </row>
-    <row r="113" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="72.0" customHeight="true">
-      <c r="A113" s="18" t="inlineStr">
+    <row r="128" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="72.0" customHeight="true">
+      <c r="A128" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">5502495107</t>
         </is>
       </c>
-      <c r="B113" s="18" t="inlineStr">
+      <c r="B128" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">666541</t>
         </is>
       </c>
-      <c r="C113" s="6" t="n">
+      <c r="C128" s="6" t="n">
         <v>38</v>
       </c>
-      <c r="D113" s="6" t="n">
+      <c r="D128" s="6" t="n">
         <v>36</v>
       </c>
-      <c r="E113" s="15" t="n">
-        <f aca="false">IFERROR(D113/C113,0)</f>
-      </c>
-      <c r="F113" s="6" t="n">
-        <f aca="false">SUMIFS('Receipt Summary'!F:F,'Receipt Summary'!E:E,A113)</f>
-      </c>
-      <c r="G113" s="6" t="n">
-        <f aca="false">SUMIFS('Receipt Summary'!G:G,'Receipt Summary'!E:E,A113)</f>
-      </c>
-      <c r="H113" s="15" t="n">
-        <f aca="false">IFERROR(G113/F113,0)</f>
-      </c>
-      <c r="I113" s="6" t="n">
-        <f aca="false">D113-F113</f>
-      </c>
-      <c r="J113" s="16" t="inlineStr">
+      <c r="E128" s="15" t="n">
+        <f aca="false">IFERROR(D128/C128,0)</f>
+      </c>
+      <c r="F128" s="6" t="n">
+        <f aca="false">SUMIFS('Receipt Summary'!F:F,'Receipt Summary'!E:E,A128)</f>
+      </c>
+      <c r="G128" s="6" t="n">
+        <f aca="false">SUMIFS('Receipt Summary'!G:G,'Receipt Summary'!E:E,A128)</f>
+      </c>
+      <c r="H128" s="15" t="n">
+        <f aca="false">IFERROR(G128/F128,0)</f>
+      </c>
+      <c r="I128" s="6" t="n">
+        <f aca="false">D128-F128</f>
+      </c>
+      <c r="J128" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">Newly harvested 07/13. SH sampled 38 intact, passed 36 (94.7%). Not yet at ATM; expected in coming weeks.</t>
         </is>
       </c>
     </row>
-    <row r="115" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A115" s="3" t="s">
+    <row r="129" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="72.0" customHeight="true">
+      <c r="A129" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5502512228</t>
+        </is>
+      </c>
+      <c r="B129" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">666541</t>
+        </is>
+      </c>
+      <c r="C129" s="6" t="n">
+        <v>46</v>
+      </c>
+      <c r="D129" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="E129" s="15" t="n">
+        <f aca="false">IFERROR(D129/C129,0)</f>
+      </c>
+      <c r="F129" s="6" t="n">
+        <f aca="false">SUMIFS('Receipt Summary'!F:F,'Receipt Summary'!E:E,A129)</f>
+      </c>
+      <c r="G129" s="6" t="n">
+        <f aca="false">SUMIFS('Receipt Summary'!G:G,'Receipt Summary'!E:E,A129)</f>
+      </c>
+      <c r="H129" s="15" t="n">
+        <f aca="false">IFERROR(G129/F129,0)</f>
+      </c>
+      <c r="I129" s="6" t="n">
+        <f aca="false">D129-F129</f>
+      </c>
+      <c r="J129" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Newly harvested 07/27. SH sampled 46 intact, passed 45 (97.8%). Not yet at ATM; expected in coming weeks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A131" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="B115" s="3"/>
-      <c r="C115" s="3"/>
-      <c r="D115" s="3"/>
-      <c r="E115" s="3"/>
-      <c r="F115" s="3"/>
-      <c r="G115" s="3"/>
-      <c r="H115" s="3"/>
-      <c r="I115" s="3"/>
-      <c r="J115" s="3"/>
-      <c r="K115" s="3"/>
-      <c r="L115" s="3"/>
-    </row>
-    <row r="116" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A116" s="19" t="s">
+      <c r="B131" s="3"/>
+      <c r="C131" s="3"/>
+      <c r="D131" s="3"/>
+      <c r="E131" s="3"/>
+      <c r="F131" s="3"/>
+      <c r="G131" s="3"/>
+      <c r="H131" s="3"/>
+      <c r="I131" s="3"/>
+      <c r="J131" s="3"/>
+      <c r="K131" s="3"/>
+      <c r="L131" s="3"/>
+    </row>
+    <row r="132" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A132" s="19" t="s">
         <v>152</v>
       </c>
-      <c r="B116" s="20" t="s">
+      <c r="B132" s="20" t="s">
         <v>153</v>
-      </c>
-      <c r="C116" s="20"/>
-      <c r="D116" s="20"/>
-      <c r="E116" s="20"/>
-      <c r="F116" s="20"/>
-      <c r="G116" s="20"/>
-      <c r="H116" s="20"/>
-      <c r="I116" s="20"/>
-      <c r="J116" s="20"/>
-      <c r="K116" s="20"/>
-      <c r="L116" s="20"/>
-    </row>
-    <row r="117" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A117" s="19" t="s">
-        <v>154</v>
-      </c>
-      <c r="B117" s="20" t="s">
-        <v>155</v>
-      </c>
-      <c r="C117" s="20"/>
-      <c r="D117" s="20"/>
-      <c r="E117" s="20"/>
-      <c r="F117" s="20"/>
-      <c r="G117" s="20"/>
-      <c r="H117" s="20"/>
-      <c r="I117" s="20"/>
-      <c r="J117" s="20"/>
-      <c r="K117" s="20"/>
-      <c r="L117" s="20"/>
-    </row>
-    <row r="118" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A118" s="19" t="s">
-        <v>156</v>
-      </c>
-      <c r="B118" s="20" t="s">
-        <v>157</v>
-      </c>
-      <c r="C118" s="20"/>
-      <c r="D118" s="20"/>
-      <c r="E118" s="20"/>
-      <c r="F118" s="20"/>
-      <c r="G118" s="20"/>
-      <c r="H118" s="20"/>
-      <c r="I118" s="20"/>
-      <c r="J118" s="20"/>
-      <c r="K118" s="20"/>
-      <c r="L118" s="20"/>
-    </row>
-    <row r="119" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A119" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="B119" s="20" t="s">
-        <v>159</v>
-      </c>
-      <c r="C119" s="20"/>
-      <c r="D119" s="20"/>
-      <c r="E119" s="20"/>
-      <c r="F119" s="20"/>
-      <c r="G119" s="20"/>
-      <c r="H119" s="20"/>
-      <c r="I119" s="20"/>
-      <c r="J119" s="20"/>
-      <c r="K119" s="20"/>
-      <c r="L119" s="20"/>
-    </row>
-    <row r="120" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A120" s="19" t="s">
-        <v>160</v>
-      </c>
-      <c r="B120" s="20" t="s">
-        <v>161</v>
-      </c>
-      <c r="C120" s="20"/>
-      <c r="D120" s="20"/>
-      <c r="E120" s="20"/>
-      <c r="F120" s="20"/>
-      <c r="G120" s="20"/>
-      <c r="H120" s="20"/>
-      <c r="I120" s="20"/>
-      <c r="J120" s="20"/>
-      <c r="K120" s="20"/>
-      <c r="L120" s="20"/>
-    </row>
-    <row r="121" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A121" s="19" t="s">
-        <v>162</v>
-      </c>
-      <c r="B121" s="20" t="s">
-        <v>163</v>
-      </c>
-      <c r="C121" s="20"/>
-      <c r="D121" s="20"/>
-      <c r="E121" s="20"/>
-      <c r="F121" s="20"/>
-      <c r="G121" s="20"/>
-      <c r="H121" s="20"/>
-      <c r="I121" s="20"/>
-      <c r="J121" s="20"/>
-      <c r="K121" s="20"/>
-      <c r="L121" s="20"/>
-    </row>
-    <row r="122" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A122" s="19" t="s">
-        <v>164</v>
-      </c>
-      <c r="B122" s="20" t="s">
-        <v>165</v>
-      </c>
-      <c r="C122" s="20"/>
-      <c r="D122" s="20"/>
-      <c r="E122" s="20"/>
-      <c r="F122" s="20"/>
-      <c r="G122" s="20"/>
-      <c r="H122" s="20"/>
-      <c r="I122" s="20"/>
-      <c r="J122" s="20"/>
-      <c r="K122" s="20"/>
-      <c r="L122" s="20"/>
-    </row>
-    <row r="123" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A123" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8. Nineteen inspection visits so far</t>
-        </is>
-      </c>
-      <c r="B123" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Nineteen inspection visits so far. Twelve at Martins (Visits 1–5, 7, 9, 10, 12, 15, 17, 18) and seven at Parks (Visits 6, 8, 11, 13, 14, 16, 19). To extend, append new visit metadata, raw-data rows, and rollup rows; the TOTAL and SH→ATM sections then need refreshing.</t>
-        </is>
-      </c>
-      <c r="C123" s="20"/>
-      <c r="D123" s="20"/>
-      <c r="E123" s="20"/>
-      <c r="F123" s="20"/>
-      <c r="G123" s="20"/>
-      <c r="H123" s="20"/>
-      <c r="I123" s="20"/>
-      <c r="J123" s="20"/>
-      <c r="K123" s="20"/>
-      <c r="L123" s="20"/>
-    </row>
-    <row r="124" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A124" s="19" t="s">
-        <v>168</v>
-      </c>
-      <c r="B124" s="20" t="s">
-        <v>169</v>
-      </c>
-      <c r="C124" s="20"/>
-      <c r="D124" s="20"/>
-      <c r="E124" s="20"/>
-      <c r="F124" s="20"/>
-      <c r="G124" s="20"/>
-      <c r="H124" s="20"/>
-      <c r="I124" s="20"/>
-      <c r="J124" s="20"/>
-      <c r="K124" s="20"/>
-      <c r="L124" s="20"/>
-    </row>
-    <row r="125" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A125" s="19" t="s">
-        <v>170</v>
-      </c>
-      <c r="B125" s="20" t="s">
-        <v>171</v>
-      </c>
-      <c r="C125" s="20"/>
-      <c r="D125" s="20"/>
-      <c r="E125" s="20"/>
-      <c r="F125" s="20"/>
-      <c r="G125" s="20"/>
-      <c r="H125" s="20"/>
-      <c r="I125" s="20"/>
-      <c r="J125" s="20"/>
-      <c r="K125" s="20"/>
-      <c r="L125" s="20"/>
-    </row>
-    <row r="126" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A126" s="19" t="s">
-        <v>172</v>
-      </c>
-      <c r="B126" s="20" t="s">
-        <v>173</v>
-      </c>
-      <c r="C126" s="20"/>
-      <c r="D126" s="20"/>
-      <c r="E126" s="20"/>
-      <c r="F126" s="20"/>
-      <c r="G126" s="20"/>
-      <c r="H126" s="20"/>
-      <c r="I126" s="20"/>
-      <c r="J126" s="20"/>
-      <c r="K126" s="20"/>
-      <c r="L126" s="20"/>
-    </row>
-    <row r="127" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A127" s="19" t="s">
-        <v>174</v>
-      </c>
-      <c r="B127" s="20" t="s">
-        <v>175</v>
-      </c>
-      <c r="C127" s="20"/>
-      <c r="D127" s="20"/>
-      <c r="E127" s="20"/>
-      <c r="F127" s="20"/>
-      <c r="G127" s="20"/>
-      <c r="H127" s="20"/>
-      <c r="I127" s="20"/>
-      <c r="J127" s="20"/>
-      <c r="K127" s="20"/>
-      <c r="L127" s="20"/>
-    </row>
-    <row r="128" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="48.0" customHeight="true">
-      <c r="A128" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13. New visits 9–12 (06/08–06/24)</t>
-        </is>
-      </c>
-      <c r="B128" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Visit 9 = 06/08 Martins; Visit 10 = 06/15 Martins; Visit 11 = 06/16 Parks (intact-only); Visit 12 = 06/24 Martins (intact-only). Source date/kill fields on several incoming sheets are volatile =NOW() captures (e.g. the Parks sheet sent 06/17 reads 06/16); the hand-entered harvest-date fields were used as the authoritative visit dates.</t>
-        </is>
-      </c>
-      <c r="C128" s="20"/>
-      <c r="D128" s="20"/>
-      <c r="E128" s="20"/>
-      <c r="F128" s="20"/>
-      <c r="G128" s="20"/>
-      <c r="H128" s="20"/>
-      <c r="I128" s="20"/>
-      <c r="J128" s="20"/>
-      <c r="K128" s="20"/>
-      <c r="L128" s="20"/>
-    </row>
-    <row r="129" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="48.0" customHeight="true">
-      <c r="A129" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14. Lot-number carry-over recurs (Visits 9 &amp; 12)</t>
-        </is>
-      </c>
-      <c r="B129" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Visit 9 (06/08) reuses Visit 7’s lots 5502428786/5502428782, and Visit 12 (06/24) reuses Visit 10’s intact lot 5502462845 — the same template carry-over pattern documented in note 9 for lot 5502421192. Each is recorded as its own visit with its own raw and rollup rows, but per the note-9 precedent only the FIRST occurrence of each lot is reconciled in the SH→ATM section, so the reused-lot inspections do not generate duplicate SH→ATM rows.</t>
-        </is>
-      </c>
-      <c r="C129" s="20"/>
-      <c r="D129" s="20"/>
-      <c r="E129" s="20"/>
-      <c r="F129" s="20"/>
-      <c r="G129" s="20"/>
-      <c r="H129" s="20"/>
-      <c r="I129" s="20"/>
-      <c r="J129" s="20"/>
-      <c r="K129" s="20"/>
-      <c r="L129" s="20"/>
-    </row>
-    <row r="130" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="48.0" customHeight="true">
-      <c r="A130" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15. Visit 10 (06/15) — two intact tally lines combined; no non-intact</t>
-        </is>
-      </c>
-      <c r="B130" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The source recorded two intact 666541 lines on 06/15 (13/12/1 and 18/18/0); they share date, lot and condition, so they are combined into a single raw row (31/30/1). No non-intact units were collected (the SH had met its non-intact quota and run low on labels), so lot 5502462842 appears in the metadata but has no raw/rollup row.</t>
-        </is>
-      </c>
-      <c r="C130" s="20"/>
-      <c r="D130" s="20"/>
-      <c r="E130" s="20"/>
-      <c r="F130" s="20"/>
-      <c r="G130" s="20"/>
-      <c r="H130" s="20"/>
-      <c r="I130" s="20"/>
-      <c r="J130" s="20"/>
-      <c r="K130" s="20"/>
-      <c r="L130" s="20"/>
-    </row>
-    <row r="131" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="48.0" customHeight="true">
-      <c r="A131" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16. Visit 11 (06/16 Parks) — heavy upstream miscut losses</t>
-        </is>
-      </c>
-      <c r="B131" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The inspector noted ~100 pigs slaughtered, with the majority of blocks failing BEFORE reaching IQC due to miscuts during block removal. Of the 16 that reached inspection, 14 passed (1 bladder hole, 1 ureter damage). That upstream loss is a Parks harvest-technique signal not captured in the pass/fail counts here. PN normalized 668518 → 666518 per note 10. Separately, the “PARKS0603” sheet (internal date 06/02, 7/7 intact, no batch) is the SAME inspection already recorded as Visit 8 and was not re-added.</t>
-        </is>
-      </c>
-      <c r="C131" s="20"/>
-      <c r="D131" s="20"/>
-      <c r="E131" s="20"/>
-      <c r="F131" s="20"/>
-      <c r="G131" s="20"/>
-      <c r="H131" s="20"/>
-      <c r="I131" s="20"/>
-      <c r="J131" s="20"/>
-      <c r="K131" s="20"/>
-      <c r="L131" s="20"/>
-    </row>
-    <row r="132" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="48.0" customHeight="true">
-      <c r="A132" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17. New Parks visits 13 (06/22) &amp; 14 (06/25)</t>
-        </is>
-      </c>
-      <c r="B132" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Two more intact-only Parks inspections (no batch data; PN normalized 668518 → 666518). Visit 13 (06/22) = 36 inspected / 31 pass / 5 fail (1 bladder hole, 2 critical-area lacerations, 2 short blocks); Visit 14 (06/25) = 19 inspected / 16 pass / 3 fail (1 bladder hole, 1 ureter laceration, 1 short block). Both were received after Visit 12, so Visit 13’s harvest date (06/22) precedes Visit 12’s (06/24 Martins) — visit numbers reflect processing order, as with the existing Visit 7/8 overlap. No batch on either, so neither has an SH→ATM link (consistent with Visits 6, 8 and 11). Short blocks and critical-zone mesentery damage continue to dominate Parks scrap.</t>
-        </is>
       </c>
       <c r="C132" s="20"/>
       <c r="D132" s="20"/>
@@ -11679,27 +12483,13 @@
       <c r="J132" s="20"/>
       <c r="K132" s="20"/>
       <c r="L132" s="20"/>
-      <c r="C132" s="20"/>
-      <c r="D132" s="20"/>
-      <c r="E132" s="20"/>
-      <c r="F132" s="20"/>
-      <c r="G132" s="20"/>
-      <c r="H132" s="20"/>
-      <c r="I132" s="20"/>
-      <c r="J132" s="20"/>
-      <c r="K132" s="20"/>
-      <c r="L132" s="20"/>
-    </row>
-    <row r="133" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="48.0" customHeight="true">
-      <c r="A133" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18. New visits 15–19 (06/29–07/13); two Parks fail-count corrections</t>
-        </is>
-      </c>
-      <c r="B133" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Visit 15 = 06/29 Martins; Visit 16 = 06/29 Parks; Visit 17 = 07/06 Martins; Visit 18 = 07/13 Martins; Visit 19 = 07/13 Parks. DATA-ACCURACY FIX: on both Parks sheets the source “# Fail” cell undercounted because blocks damaged during bowel-cleaning were written in the notes but not added to the fail tally. Corrected to inspected − pass, which matches the scrap breakdown — Visit 16 (06/29) = 50/38/12 (source cell read 10; 2 cleaning-damage + 2 short + 1 critical + 7 urethra/bladder = 12); Visit 19 (07/13) = 34/29/5 (source cell read 3; 2 cleaning-damage + 3 short = 5). Visit 17 (07/06) reuses Visit 15’s lots 5502471460/5502471457 — a tally-sheet carry-over recorded as a separate visit (see note 9). Visit 18’s inspector field was blank on the source; recorded as Toni Cruz, the standing Martins inspector.</t>
-        </is>
+    </row>
+    <row r="133" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A133" s="19" t="s">
+        <v>154</v>
+      </c>
+      <c r="B133" s="20" t="s">
+        <v>155</v>
       </c>
       <c r="C133" s="20"/>
       <c r="D133" s="20"/>
@@ -11712,16 +12502,12 @@
       <c r="K133" s="20"/>
       <c r="L133" s="20"/>
     </row>
-    <row r="134" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="48.0" customHeight="true">
-      <c r="A134" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19. Visit 19 (Parks) harvest-date ambiguity</t>
-        </is>
-      </c>
-      <c r="B134" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The source file is named “PARKS_0713” (→ 07/13), was sent as a most-recent inspection, and a Martins 07/13 sheet arrived in the same batch — so Visit 19 is recorded as harvest 07/13/2026. However, all three internal date fields on that sheet (Date, Kill, Harvest) read 06/13/2026, likely a month typo. If 06/13 was intended, flip Visit 19’s date; the counts (34/29/5) are unaffected either way.</t>
-        </is>
+    <row r="134" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A134" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="B134" s="20" t="s">
+        <v>157</v>
       </c>
       <c r="C134" s="20"/>
       <c r="D134" s="20"/>
@@ -11734,36 +12520,412 @@
       <c r="K134" s="20"/>
       <c r="L134" s="20"/>
     </row>
+    <row r="135" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A135" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="B135" s="20" t="s">
+        <v>159</v>
+      </c>
+      <c r="C135" s="20"/>
+      <c r="D135" s="20"/>
+      <c r="E135" s="20"/>
+      <c r="F135" s="20"/>
+      <c r="G135" s="20"/>
+      <c r="H135" s="20"/>
+      <c r="I135" s="20"/>
+      <c r="J135" s="20"/>
+      <c r="K135" s="20"/>
+      <c r="L135" s="20"/>
+    </row>
+    <row r="136" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A136" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="B136" s="20" t="s">
+        <v>161</v>
+      </c>
+      <c r="C136" s="20"/>
+      <c r="D136" s="20"/>
+      <c r="E136" s="20"/>
+      <c r="F136" s="20"/>
+      <c r="G136" s="20"/>
+      <c r="H136" s="20"/>
+      <c r="I136" s="20"/>
+      <c r="J136" s="20"/>
+      <c r="K136" s="20"/>
+      <c r="L136" s="20"/>
+    </row>
+    <row r="137" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A137" s="19" t="s">
+        <v>162</v>
+      </c>
+      <c r="B137" s="20" t="s">
+        <v>163</v>
+      </c>
+      <c r="C137" s="20"/>
+      <c r="D137" s="20"/>
+      <c r="E137" s="20"/>
+      <c r="F137" s="20"/>
+      <c r="G137" s="20"/>
+      <c r="H137" s="20"/>
+      <c r="I137" s="20"/>
+      <c r="J137" s="20"/>
+      <c r="K137" s="20"/>
+      <c r="L137" s="20"/>
+    </row>
+    <row r="138" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A138" s="19" t="s">
+        <v>164</v>
+      </c>
+      <c r="B138" s="20" t="s">
+        <v>165</v>
+      </c>
+      <c r="C138" s="20"/>
+      <c r="D138" s="20"/>
+      <c r="E138" s="20"/>
+      <c r="F138" s="20"/>
+      <c r="G138" s="20"/>
+      <c r="H138" s="20"/>
+      <c r="I138" s="20"/>
+      <c r="J138" s="20"/>
+      <c r="K138" s="20"/>
+      <c r="L138" s="20"/>
+    </row>
+    <row r="139" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A139" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8. Twenty-three inspection visits so far</t>
+        </is>
+      </c>
+      <c r="B139" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Twenty-three SH-floor inspection visits so far — 22 pelvic-block plus 1 thoracic (Visit 22). Pelvic visits: Martins ×13 and Parks ×8; the thoracic is at Nahunta. To extend, append metadata, raw-data and (for pelvic) rollup rows; the TOTAL and SH→ATM sections then need refreshing.</t>
+        </is>
+      </c>
+      <c r="C139" s="20"/>
+      <c r="D139" s="20"/>
+      <c r="E139" s="20"/>
+      <c r="F139" s="20"/>
+      <c r="G139" s="20"/>
+      <c r="H139" s="20"/>
+      <c r="I139" s="20"/>
+      <c r="J139" s="20"/>
+      <c r="K139" s="20"/>
+      <c r="L139" s="20"/>
+    </row>
+    <row r="140" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A140" s="19" t="s">
+        <v>168</v>
+      </c>
+      <c r="B140" s="20" t="s">
+        <v>169</v>
+      </c>
+      <c r="C140" s="20"/>
+      <c r="D140" s="20"/>
+      <c r="E140" s="20"/>
+      <c r="F140" s="20"/>
+      <c r="G140" s="20"/>
+      <c r="H140" s="20"/>
+      <c r="I140" s="20"/>
+      <c r="J140" s="20"/>
+      <c r="K140" s="20"/>
+      <c r="L140" s="20"/>
+    </row>
+    <row r="141" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A141" s="19" t="s">
+        <v>170</v>
+      </c>
+      <c r="B141" s="20" t="s">
+        <v>171</v>
+      </c>
+      <c r="C141" s="20"/>
+      <c r="D141" s="20"/>
+      <c r="E141" s="20"/>
+      <c r="F141" s="20"/>
+      <c r="G141" s="20"/>
+      <c r="H141" s="20"/>
+      <c r="I141" s="20"/>
+      <c r="J141" s="20"/>
+      <c r="K141" s="20"/>
+      <c r="L141" s="20"/>
+    </row>
+    <row r="142" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A142" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="B142" s="20" t="s">
+        <v>173</v>
+      </c>
+      <c r="C142" s="20"/>
+      <c r="D142" s="20"/>
+      <c r="E142" s="20"/>
+      <c r="F142" s="20"/>
+      <c r="G142" s="20"/>
+      <c r="H142" s="20"/>
+      <c r="I142" s="20"/>
+      <c r="J142" s="20"/>
+      <c r="K142" s="20"/>
+      <c r="L142" s="20"/>
+    </row>
+    <row r="143" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A143" s="19" t="s">
+        <v>174</v>
+      </c>
+      <c r="B143" s="20" t="s">
+        <v>175</v>
+      </c>
+      <c r="C143" s="20"/>
+      <c r="D143" s="20"/>
+      <c r="E143" s="20"/>
+      <c r="F143" s="20"/>
+      <c r="G143" s="20"/>
+      <c r="H143" s="20"/>
+      <c r="I143" s="20"/>
+      <c r="J143" s="20"/>
+      <c r="K143" s="20"/>
+      <c r="L143" s="20"/>
+    </row>
+    <row r="144" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="48.0" customHeight="true">
+      <c r="A144" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13. New visits 9–12 (06/08–06/24)</t>
+        </is>
+      </c>
+      <c r="B144" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Visit 9 = 06/08 Martins; Visit 10 = 06/15 Martins; Visit 11 = 06/16 Parks (intact-only); Visit 12 = 06/24 Martins (intact-only). Source date/kill fields on several incoming sheets are volatile =NOW() captures (e.g. the Parks sheet sent 06/17 reads 06/16); the hand-entered harvest-date fields were used as the authoritative visit dates.</t>
+        </is>
+      </c>
+      <c r="C144" s="20"/>
+      <c r="D144" s="20"/>
+      <c r="E144" s="20"/>
+      <c r="F144" s="20"/>
+      <c r="G144" s="20"/>
+      <c r="H144" s="20"/>
+      <c r="I144" s="20"/>
+      <c r="J144" s="20"/>
+      <c r="K144" s="20"/>
+      <c r="L144" s="20"/>
+    </row>
+    <row r="145" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="48.0" customHeight="true">
+      <c r="A145" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14. Lot-number carry-over recurs (Visits 9 &amp; 12)</t>
+        </is>
+      </c>
+      <c r="B145" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Visit 9 (06/08) reuses Visit 7’s lots 5502428786/5502428782, and Visit 12 (06/24) reuses Visit 10’s intact lot 5502462845 — the same template carry-over pattern documented in note 9 for lot 5502421192. Each is recorded as its own visit with its own raw and rollup rows, but per the note-9 precedent only the FIRST occurrence of each lot is reconciled in the SH→ATM section, so the reused-lot inspections do not generate duplicate SH→ATM rows.</t>
+        </is>
+      </c>
+      <c r="C145" s="20"/>
+      <c r="D145" s="20"/>
+      <c r="E145" s="20"/>
+      <c r="F145" s="20"/>
+      <c r="G145" s="20"/>
+      <c r="H145" s="20"/>
+      <c r="I145" s="20"/>
+      <c r="J145" s="20"/>
+      <c r="K145" s="20"/>
+      <c r="L145" s="20"/>
+    </row>
+    <row r="146" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="48.0" customHeight="true">
+      <c r="A146" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15. Visit 10 (06/15) — two intact tally lines combined; no non-intact</t>
+        </is>
+      </c>
+      <c r="B146" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The source recorded two intact 666541 lines on 06/15 (13/12/1 and 18/18/0); they share date, lot and condition, so they are combined into a single raw row (31/30/1). No non-intact units were collected (the SH had met its non-intact quota and run low on labels), so lot 5502462842 appears in the metadata but has no raw/rollup row.</t>
+        </is>
+      </c>
+      <c r="C146" s="20"/>
+      <c r="D146" s="20"/>
+      <c r="E146" s="20"/>
+      <c r="F146" s="20"/>
+      <c r="G146" s="20"/>
+      <c r="H146" s="20"/>
+      <c r="I146" s="20"/>
+      <c r="J146" s="20"/>
+      <c r="K146" s="20"/>
+      <c r="L146" s="20"/>
+    </row>
+    <row r="147" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="48.0" customHeight="true">
+      <c r="A147" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16. Visit 11 (06/16 Parks) — heavy upstream miscut losses</t>
+        </is>
+      </c>
+      <c r="B147" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The inspector noted ~100 pigs slaughtered, with the majority of blocks failing BEFORE reaching IQC due to miscuts during block removal. Of the 16 that reached inspection, 14 passed (1 bladder hole, 1 ureter damage). That upstream loss is a Parks harvest-technique signal not captured in the pass/fail counts here. PN normalized 668518 → 666518 per note 10. Separately, the “PARKS0603” sheet (internal date 06/02, 7/7 intact, no batch) is the SAME inspection already recorded as Visit 8 and was not re-added.</t>
+        </is>
+      </c>
+      <c r="C147" s="20"/>
+      <c r="D147" s="20"/>
+      <c r="E147" s="20"/>
+      <c r="F147" s="20"/>
+      <c r="G147" s="20"/>
+      <c r="H147" s="20"/>
+      <c r="I147" s="20"/>
+      <c r="J147" s="20"/>
+      <c r="K147" s="20"/>
+      <c r="L147" s="20"/>
+    </row>
+    <row r="148" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="48.0" customHeight="true">
+      <c r="A148" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17. New Parks visits 13 (06/22) &amp; 14 (06/25)</t>
+        </is>
+      </c>
+      <c r="B148" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Two more intact-only Parks inspections (no batch data; PN normalized 668518 → 666518). Visit 13 (06/22) = 36 inspected / 31 pass / 5 fail (1 bladder hole, 2 critical-area lacerations, 2 short blocks); Visit 14 (06/25) = 19 inspected / 16 pass / 3 fail (1 bladder hole, 1 ureter laceration, 1 short block). Both were received after Visit 12, so Visit 13’s harvest date (06/22) precedes Visit 12’s (06/24 Martins) — visit numbers reflect processing order, as with the existing Visit 7/8 overlap. No batch on either, so neither has an SH→ATM link (consistent with Visits 6, 8 and 11). Short blocks and critical-zone mesentery damage continue to dominate Parks scrap.</t>
+        </is>
+      </c>
+      <c r="C148" s="20"/>
+      <c r="D148" s="20"/>
+      <c r="E148" s="20"/>
+      <c r="F148" s="20"/>
+      <c r="G148" s="20"/>
+      <c r="H148" s="20"/>
+      <c r="I148" s="20"/>
+      <c r="J148" s="20"/>
+      <c r="K148" s="20"/>
+      <c r="L148" s="20"/>
+      <c r="C148" s="20"/>
+      <c r="D148" s="20"/>
+      <c r="E148" s="20"/>
+      <c r="F148" s="20"/>
+      <c r="G148" s="20"/>
+      <c r="H148" s="20"/>
+      <c r="I148" s="20"/>
+      <c r="J148" s="20"/>
+      <c r="K148" s="20"/>
+      <c r="L148" s="20"/>
+    </row>
+    <row r="149" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="48.0" customHeight="true">
+      <c r="A149" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18. New visits 15–19 (06/29–07/13); two Parks fail-count corrections</t>
+        </is>
+      </c>
+      <c r="B149" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Visit 15 = 06/29 Martins; Visit 16 = 06/29 Parks; Visit 17 = 07/06 Martins; Visit 18 = 07/13 Martins; Visit 19 = 07/13 Parks. DATA-ACCURACY FIX: on both Parks sheets the source “# Fail” cell undercounted because blocks damaged during bowel-cleaning were written in the notes but not added to the fail tally. Corrected to inspected − pass, which matches the scrap breakdown — Visit 16 (06/29) = 50/38/12 (source cell read 10; 2 cleaning-damage + 2 short + 1 critical + 7 urethra/bladder = 12); Visit 19 (07/13) = 34/29/5 (source cell read 3; 2 cleaning-damage + 3 short = 5). Visit 17 (07/06) reuses Visit 15’s lots 5502471460/5502471457 — a tally-sheet carry-over recorded as a separate visit (see note 9). Visit 18’s inspector field was blank on the source; recorded as Toni Cruz, the standing Martins inspector.</t>
+        </is>
+      </c>
+      <c r="C149" s="20"/>
+      <c r="D149" s="20"/>
+      <c r="E149" s="20"/>
+      <c r="F149" s="20"/>
+      <c r="G149" s="20"/>
+      <c r="H149" s="20"/>
+      <c r="I149" s="20"/>
+      <c r="J149" s="20"/>
+      <c r="K149" s="20"/>
+      <c r="L149" s="20"/>
+    </row>
+    <row r="150" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="48.0" customHeight="true">
+      <c r="A150" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19. Visit 19 (Parks) harvest-date ambiguity</t>
+        </is>
+      </c>
+      <c r="B150" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The source file is named “PARKS_0713” (→ 07/13), was sent as a most-recent inspection, and a Martins 07/13 sheet arrived in the same batch — so Visit 19 is recorded as harvest 07/13/2026. However, all three internal date fields on that sheet (Date, Kill, Harvest) read 06/13/2026, likely a month typo. If 06/13 was intended, flip Visit 19’s date; the counts (34/29/5) are unaffected either way.</t>
+        </is>
+      </c>
+      <c r="C150" s="20"/>
+      <c r="D150" s="20"/>
+      <c r="E150" s="20"/>
+      <c r="F150" s="20"/>
+      <c r="G150" s="20"/>
+      <c r="H150" s="20"/>
+      <c r="I150" s="20"/>
+      <c r="J150" s="20"/>
+      <c r="K150" s="20"/>
+      <c r="L150" s="20"/>
+    </row>
+    <row r="151" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="48.0" customHeight="true">
+      <c r="A151" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20. New visits 20–23 (07/20–07/30); first thoracic &amp; new slaughterhouse</t>
+        </is>
+      </c>
+      <c r="B151" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Visit 20 = 07/20 Martins (reuses Visit 18 lots 5502495107 / 5502495104 — carry-over); Visit 21 = 07/27 Martins (new lots 5502512228 / 5502512225); Visit 22 = 07/29 Nahunta — the first THORACIC (PN 666521, lot 5502512218), a new product family at a new slaughterhouse with a new inspector/tech (Kris / Jordan Guthrie), 19 inspected / 6 pass / 13 fail (31.6%); Visit 23 = 07/30 Parks (666518, majority-male pigs noted). The thoracic is logged in the raw data and summarized on the "Quality Summary by Part" tab, but is EXCLUDED from the pelvic-block rollup, TOTAL and SH→ATM sections so pelvic yield stays comparable across a single product family.</t>
+        </is>
+      </c>
+      <c r="C151" s="20"/>
+      <c r="D151" s="20"/>
+      <c r="E151" s="20"/>
+      <c r="F151" s="20"/>
+      <c r="G151" s="20"/>
+      <c r="H151" s="20"/>
+      <c r="I151" s="20"/>
+      <c r="J151" s="20"/>
+      <c r="K151" s="20"/>
+      <c r="L151" s="20"/>
+    </row>
+    <row r="152" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="48.0" customHeight="true">
+      <c r="A152" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21. Visit 20 (07/20 Martins 666541) count discrepancy</t>
+        </is>
+      </c>
+      <c r="B152" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The source tally read 65 inspected / 63 pass / 1 fail, which does not foot (65 − 63 = 2), and only one defect (deformed bladder) was written in. Recorded here as 65 / 63 / 2 to preserve the two counted columns and the workbook’s fail = inspected − pass convention. If the true fail is 1, correct the pass to 64 (or inspected to 64) and the second reject’s reason. Confirm with the tech.</t>
+        </is>
+      </c>
+      <c r="C152" s="20"/>
+      <c r="D152" s="20"/>
+      <c r="E152" s="20"/>
+      <c r="F152" s="20"/>
+      <c r="G152" s="20"/>
+      <c r="H152" s="20"/>
+      <c r="I152" s="20"/>
+      <c r="J152" s="20"/>
+      <c r="K152" s="20"/>
+      <c r="L152" s="20"/>
+    </row>
   </sheetData>
-  <mergeCells count="26">
+  <mergeCells count="28">
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A2:L2"/>
     <mergeCell ref="A4:L4"/>
-    <mergeCell ref="A26:L26"/>
-    <mergeCell ref="A67:L67"/>
-    <mergeCell ref="A99:L99"/>
-    <mergeCell ref="A115:L115"/>
-    <mergeCell ref="B116:L116"/>
-    <mergeCell ref="B117:L117"/>
-    <mergeCell ref="B118:L118"/>
-    <mergeCell ref="B119:L119"/>
-    <mergeCell ref="B120:L120"/>
-    <mergeCell ref="B121:L121"/>
-    <mergeCell ref="B122:L122"/>
-    <mergeCell ref="B123:L123"/>
-    <mergeCell ref="B124:L124"/>
-    <mergeCell ref="B125:L125"/>
-    <mergeCell ref="B126:L126"/>
-    <mergeCell ref="B127:L127"/>
-    <mergeCell ref="B128:L128"/>
-    <mergeCell ref="B129:L129"/>
-    <mergeCell ref="B130:L130"/>
-    <mergeCell ref="B131:L131"/>
+    <mergeCell ref="A30:L30"/>
+    <mergeCell ref="A77:L77"/>
+    <mergeCell ref="A114:L114"/>
+    <mergeCell ref="A131:L131"/>
     <mergeCell ref="B132:L132"/>
     <mergeCell ref="B133:L133"/>
     <mergeCell ref="B134:L134"/>
+    <mergeCell ref="B135:L135"/>
+    <mergeCell ref="B136:L136"/>
+    <mergeCell ref="B137:L137"/>
+    <mergeCell ref="B138:L138"/>
+    <mergeCell ref="B139:L139"/>
+    <mergeCell ref="B140:L140"/>
+    <mergeCell ref="B141:L141"/>
+    <mergeCell ref="B142:L142"/>
+    <mergeCell ref="B143:L143"/>
+    <mergeCell ref="B144:L144"/>
+    <mergeCell ref="B145:L145"/>
+    <mergeCell ref="B146:L146"/>
+    <mergeCell ref="B147:L147"/>
+    <mergeCell ref="B148:L148"/>
+    <mergeCell ref="B149:L149"/>
+    <mergeCell ref="B150:L150"/>
+    <mergeCell ref="B151:L151"/>
+    <mergeCell ref="B152:L152"/>
   </mergeCells>
-  <conditionalFormatting sqref="J28:J65">
+  <conditionalFormatting sqref="J32:J75">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="num" val="0.7"/>
@@ -11775,7 +12937,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I69:I96">
+  <conditionalFormatting sqref="I79:I111">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="num" val="0.7"/>
@@ -11787,7 +12949,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E101:E113">
+  <conditionalFormatting sqref="E116:E129">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="num" val="0.7"/>
@@ -11799,7 +12961,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H101:H113">
+  <conditionalFormatting sqref="H116:H129">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="num" val="0.7"/>
